--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -8890,7 +8890,7 @@
         <v>2</v>
       </c>
       <c r="J111" t="n">
-        <v>6043.06</v>
+        <v>6043.05</v>
       </c>
       <c r="K111" t="n">
         <v>5748.09</v>
@@ -30647,7 +30647,7 @@
         <v>2</v>
       </c>
       <c r="J400" t="n">
-        <v>7668.84</v>
+        <v>7668.83</v>
       </c>
       <c r="K400" t="n">
         <v>7536.22</v>
@@ -31575,6 +31575,79 @@
         <v>154.5</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>7611.44</v>
+      </c>
+      <c r="D413" t="n">
+        <v>7647.99</v>
+      </c>
+      <c r="E413" t="n">
+        <v>7592.28</v>
+      </c>
+      <c r="F413" t="n">
+        <v>7634.23</v>
+      </c>
+      <c r="G413" t="n">
+        <v>1637222000</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2</v>
+      </c>
+      <c r="J413" t="n">
+        <v>7677.61</v>
+      </c>
+      <c r="K413" t="n">
+        <v>7580.55</v>
+      </c>
+      <c r="L413" t="n">
+        <v>7376.25</v>
+      </c>
+      <c r="M413" t="n">
+        <v>7167.2</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="O413" t="n">
+        <v>31</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -8890,7 +8890,7 @@
         <v>2</v>
       </c>
       <c r="J111" t="n">
-        <v>6043.05</v>
+        <v>6043.06</v>
       </c>
       <c r="K111" t="n">
         <v>5748.09</v>
@@ -30800,7 +30800,7 @@
         <v>7701.48</v>
       </c>
       <c r="K402" t="n">
-        <v>7539.5</v>
+        <v>7539.51</v>
       </c>
       <c r="L402" t="n">
         <v>7284.89</v>
@@ -31596,31 +31596,31 @@
         <v>7592.28</v>
       </c>
       <c r="F413" t="n">
-        <v>7634.23</v>
+        <v>7619.98</v>
       </c>
       <c r="G413" t="n">
-        <v>1637222000</v>
+        <v>2897149000</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.48</v>
       </c>
       <c r="I413" t="n">
         <v>2</v>
       </c>
       <c r="J413" t="n">
-        <v>7677.61</v>
+        <v>7676.9</v>
       </c>
       <c r="K413" t="n">
-        <v>7580.55</v>
+        <v>7580.31</v>
       </c>
       <c r="L413" t="n">
-        <v>7376.25</v>
+        <v>7376.13</v>
       </c>
       <c r="M413" t="n">
-        <v>7167.2</v>
+        <v>7167.13</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>48.28</v>
+        <v>47.04</v>
       </c>
       <c r="O413" t="n">
         <v>31</v>
@@ -31637,16 +31637,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>152.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31524,7 +31524,7 @@
         <v>7619.98</v>
       </c>
       <c r="G412" t="n">
-        <v>2897149000</v>
+        <v>4963750000</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>-0.48</v>
@@ -31548,7 +31548,7 @@
         <v>47.04</v>
       </c>
       <c r="O412" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31567,9 +31567,7 @@
       <c r="T412" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U412" s="2" t="n">
-        <v>12</v>
-      </c>
+      <c r="U412" s="2" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="n">
         <v>152.1</v>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31548,7 +31548,7 @@
         <v>47.04</v>
       </c>
       <c r="O412" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31573,6 +31573,79 @@
         <v>152.1</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>7612.3</v>
+      </c>
+      <c r="D413" t="n">
+        <v>7617.26</v>
+      </c>
+      <c r="E413" t="n">
+        <v>7572.69</v>
+      </c>
+      <c r="F413" t="n">
+        <v>7583.51</v>
+      </c>
+      <c r="G413" t="n">
+        <v>1416902000</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2</v>
+      </c>
+      <c r="J413" t="n">
+        <v>7668.82</v>
+      </c>
+      <c r="K413" t="n">
+        <v>7581.69</v>
+      </c>
+      <c r="L413" t="n">
+        <v>7384.69</v>
+      </c>
+      <c r="M413" t="n">
+        <v>7171.21</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>41.74</v>
+      </c>
+      <c r="O413" t="n">
+        <v>29</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -645,9 +645,7 @@
       <c r="T2" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U2" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="U2" s="2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" s="1" t="n">
         <v>173.2</v>
@@ -720,9 +718,7 @@
       <c r="T3" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U3" s="2" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U3" s="2" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" s="1" t="n">
         <v>168.6</v>
@@ -795,9 +791,7 @@
       <c r="T4" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U4" s="2" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="U4" s="2" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="1" t="n">
         <v>163.6</v>
@@ -870,9 +864,7 @@
       <c r="T5" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U5" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U5" s="2" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="1" t="n">
         <v>157.4</v>
@@ -945,9 +937,7 @@
       <c r="T6" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U6" s="2" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U6" s="2" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="1" t="n">
         <v>156.7</v>
@@ -1020,9 +1010,7 @@
       <c r="T7" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U7" s="2" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U7" s="2" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="1" t="n">
         <v>158.5</v>
@@ -1095,9 +1083,7 @@
       <c r="T8" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U8" s="2" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U8" s="2" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="1" t="n">
         <v>155.4</v>
@@ -1170,9 +1156,7 @@
       <c r="T9" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U9" s="2" t="n">
-        <v>15</v>
-      </c>
+      <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="1" t="n">
         <v>159.4</v>
@@ -1245,9 +1229,7 @@
       <c r="T10" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U10" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" s="1" t="n">
         <v>162.6</v>
@@ -1320,9 +1302,7 @@
       <c r="T11" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U11" s="2" t="n">
-        <v>15.8</v>
-      </c>
+      <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" s="1" t="n">
         <v>163.6</v>
@@ -1395,9 +1375,7 @@
       <c r="T12" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U12" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" s="1" t="n">
         <v>166.5</v>
@@ -1470,9 +1448,7 @@
       <c r="T13" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U13" s="2" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" s="1" t="n">
         <v>166.9</v>
@@ -1545,9 +1521,7 @@
       <c r="T14" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U14" s="2" t="n">
-        <v>14.1</v>
-      </c>
+      <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" s="1" t="n">
         <v>168.8</v>
@@ -1620,9 +1594,7 @@
       <c r="T15" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U15" s="2" t="n">
-        <v>12.8</v>
-      </c>
+      <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" s="1" t="n">
         <v>166.1</v>
@@ -1695,9 +1667,7 @@
       <c r="T16" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U16" s="2" t="n">
-        <v>11</v>
-      </c>
+      <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" s="1" t="n">
         <v>163.4</v>
@@ -1770,9 +1740,7 @@
       <c r="T17" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U17" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" s="1" t="n">
         <v>168</v>
@@ -1845,9 +1813,7 @@
       <c r="T18" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U18" s="2" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" s="1" t="n">
         <v>183.1</v>
@@ -1920,9 +1886,7 @@
       <c r="T19" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U19" s="2" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" s="1" t="n">
         <v>175.8</v>
@@ -1995,9 +1959,7 @@
       <c r="T20" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U20" s="2" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" s="1" t="n">
         <v>178.6</v>
@@ -2074,9 +2036,7 @@
       <c r="T21" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U21" s="2" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" s="1" t="n">
         <v>165</v>
@@ -2149,9 +2109,7 @@
       <c r="T22" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U22" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" s="1" t="n">
         <v>156.9</v>
@@ -2224,9 +2182,7 @@
       <c r="T23" s="2" t="n">
         <v>19.4</v>
       </c>
-      <c r="U23" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" s="1" t="n">
         <v>157.6</v>
@@ -2299,9 +2255,7 @@
       <c r="T24" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U24" s="2" t="n">
-        <v>20.5</v>
-      </c>
+      <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" s="2" t="n">
         <v>153.4</v>
@@ -2378,9 +2332,7 @@
       <c r="T25" s="2" t="n">
         <v>21.1</v>
       </c>
-      <c r="U25" s="2" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
       <c r="W25" s="2" t="n">
         <v>149.3</v>
@@ -2453,9 +2405,7 @@
       <c r="T26" s="2" t="n">
         <v>19.6</v>
       </c>
-      <c r="U26" s="2" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" s="1" t="n">
         <v>157.9</v>
@@ -2532,9 +2482,7 @@
       <c r="T27" s="2" t="n">
         <v>22.8</v>
       </c>
-      <c r="U27" s="2" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" s="2" t="n">
         <v>154.3</v>
@@ -2607,9 +2555,7 @@
       <c r="T28" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U28" s="2" t="n">
-        <v>24.6</v>
-      </c>
+      <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" s="2" t="n">
         <v>151.4</v>
@@ -2682,9 +2628,7 @@
       <c r="T29" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="U29" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" s="2" t="n">
         <v>138.9</v>
@@ -2757,9 +2701,7 @@
       <c r="T30" s="2" t="n">
         <v>24.9</v>
       </c>
-      <c r="U30" s="3" t="n">
-        <v>31.1</v>
-      </c>
+      <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" s="2" t="n">
         <v>137.6</v>
@@ -2832,9 +2774,7 @@
       <c r="T31" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="U31" s="2" t="n">
-        <v>24.7</v>
-      </c>
+      <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" s="2" t="n">
         <v>139.9</v>
@@ -2911,14 +2851,8 @@
       <c r="T32" s="6" t="n">
         <v>27.9</v>
       </c>
-      <c r="U32" s="6" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="V32" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U32" s="7" t="inlineStr"/>
+      <c r="V32" s="4" t="inlineStr"/>
       <c r="W32" s="7" t="n">
         <v>146</v>
       </c>
@@ -2994,14 +2928,8 @@
       <c r="T33" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="U33" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="V33" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" s="2" t="n">
         <v>132.8</v>
       </c>
@@ -3077,9 +3005,7 @@
       <c r="T34" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U34" s="2" t="n">
-        <v>23.2</v>
-      </c>
+      <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
       <c r="W34" s="2" t="n">
         <v>128.7</v>
@@ -3156,9 +3082,7 @@
       <c r="T35" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U35" s="2" t="n">
-        <v>23.4</v>
-      </c>
+      <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
       <c r="W35" s="2" t="n">
         <v>128.9</v>
@@ -3231,9 +3155,7 @@
       <c r="T36" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U36" s="2" t="n">
-        <v>21.4</v>
-      </c>
+      <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" s="2" t="n">
         <v>130.3</v>
@@ -3306,9 +3228,7 @@
       <c r="T37" s="2" t="n">
         <v>20.5</v>
       </c>
-      <c r="U37" s="2" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" s="2" t="n">
         <v>133.9</v>
@@ -3381,9 +3301,7 @@
       <c r="T38" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="U38" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" s="2" t="n">
         <v>136.8</v>
@@ -3456,9 +3374,7 @@
       <c r="T39" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U39" s="2" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
       <c r="W39" s="2" t="n">
         <v>136.4</v>
@@ -3531,9 +3447,7 @@
       <c r="T40" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U40" s="2" t="n">
-        <v>18.6</v>
-      </c>
+      <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" s="2" t="n">
         <v>140.8</v>
@@ -3606,9 +3520,7 @@
       <c r="T41" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U41" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
       <c r="W41" s="2" t="n">
         <v>141.7</v>
@@ -3681,9 +3593,7 @@
       <c r="T42" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U42" s="2" t="n">
-        <v>13</v>
-      </c>
+      <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
       <c r="W42" s="2" t="n">
         <v>144</v>
@@ -3756,9 +3666,7 @@
       <c r="T43" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U43" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
       <c r="W43" s="2" t="n">
         <v>148.7</v>
@@ -3835,9 +3743,7 @@
       <c r="T44" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="U44" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
       <c r="W44" s="2" t="n">
         <v>144.8</v>
@@ -3910,9 +3816,7 @@
       <c r="T45" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U45" s="2" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
       <c r="W45" s="2" t="n">
         <v>140.9</v>
@@ -3985,9 +3889,7 @@
       <c r="T46" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="U46" s="3" t="n">
-        <v>25.4</v>
-      </c>
+      <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
       <c r="W46" s="2" t="n">
         <v>139</v>
@@ -4060,9 +3962,7 @@
       <c r="T47" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="U47" s="2" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" t="inlineStr"/>
       <c r="W47" s="2" t="n">
         <v>148.6</v>
@@ -4135,9 +4035,7 @@
       <c r="T48" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U48" s="2" t="n">
-        <v>20.1</v>
-      </c>
+      <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" t="inlineStr"/>
       <c r="W48" s="2" t="n">
         <v>143</v>
@@ -4210,9 +4108,7 @@
       <c r="T49" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="U49" s="3" t="n">
-        <v>26.7</v>
-      </c>
+      <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" t="inlineStr"/>
       <c r="W49" s="2" t="n">
         <v>144.3</v>
@@ -4289,14 +4185,8 @@
       <c r="T50" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="U50" s="6" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="V50" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U50" s="7" t="inlineStr"/>
+      <c r="V50" s="4" t="inlineStr"/>
       <c r="W50" s="7" t="n">
         <v>139.2</v>
       </c>
@@ -4372,14 +4262,8 @@
       <c r="T51" s="6" t="n">
         <v>45.3</v>
       </c>
-      <c r="U51" s="6" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="V51" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U51" s="7" t="inlineStr"/>
+      <c r="V51" s="4" t="inlineStr"/>
       <c r="W51" s="7" t="n">
         <v>136.5</v>
       </c>
@@ -4455,14 +4339,8 @@
       <c r="T52" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="U52" s="3" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="V52" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" s="2" t="n">
         <v>133.8</v>
       </c>
@@ -4538,14 +4416,8 @@
       <c r="T53" s="3" t="n">
         <v>52.3</v>
       </c>
-      <c r="U53" s="3" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="V53" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" s="2" t="n">
         <v>135.7</v>
       </c>
@@ -4617,14 +4489,8 @@
       <c r="T54" s="3" t="n">
         <v>33.6</v>
       </c>
-      <c r="U54" s="3" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="V54" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" s="2" t="n">
         <v>142.2</v>
       </c>
@@ -4696,14 +4562,8 @@
       <c r="T55" s="6" t="n">
         <v>40.7</v>
       </c>
-      <c r="U55" s="6" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="V55" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U55" s="7" t="inlineStr"/>
+      <c r="V55" s="4" t="inlineStr"/>
       <c r="W55" s="7" t="n">
         <v>127.5</v>
       </c>
@@ -4775,14 +4635,8 @@
       <c r="T56" s="3" t="n">
         <v>37.6</v>
       </c>
-      <c r="U56" s="3" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="V56" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" s="2" t="n">
         <v>128.6</v>
       </c>
@@ -4854,9 +4708,7 @@
       <c r="T57" s="3" t="n">
         <v>30.9</v>
       </c>
-      <c r="U57" s="3" t="n">
-        <v>28.5</v>
-      </c>
+      <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
       <c r="W57" s="2" t="n">
         <v>135.7</v>
@@ -4929,9 +4781,7 @@
       <c r="T58" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="U58" s="3" t="n">
-        <v>26</v>
-      </c>
+      <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
       <c r="W58" s="2" t="n">
         <v>135.8</v>
@@ -5004,14 +4854,8 @@
       <c r="T59" s="6" t="n">
         <v>32.6</v>
       </c>
-      <c r="U59" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="V59" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U59" s="7" t="inlineStr"/>
+      <c r="V59" s="4" t="inlineStr"/>
       <c r="W59" s="7" t="n">
         <v>131.3</v>
       </c>
@@ -5083,14 +4927,8 @@
       <c r="T60" s="3" t="n">
         <v>29.6</v>
       </c>
-      <c r="U60" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="V60" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" s="2" t="n">
         <v>130</v>
       </c>
@@ -5162,9 +5000,7 @@
       <c r="T61" s="6" t="n">
         <v>33.8</v>
       </c>
-      <c r="U61" s="6" t="n">
-        <v>30.6</v>
-      </c>
+      <c r="U61" s="7" t="inlineStr"/>
       <c r="V61" s="4" t="inlineStr"/>
       <c r="W61" s="6" t="n">
         <v>125.8</v>
@@ -5237,9 +5073,7 @@
       <c r="T62" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="U62" s="3" t="n">
-        <v>29.1</v>
-      </c>
+      <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" t="inlineStr"/>
       <c r="W62" s="3" t="n">
         <v>125.9</v>
@@ -5312,14 +5146,8 @@
       <c r="T63" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="U63" s="3" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="V63" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
       <c r="W63" s="3" t="n">
         <v>126.7</v>
       </c>
@@ -5391,9 +5219,7 @@
       <c r="T64" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="U64" s="3" t="n">
-        <v>25.7</v>
-      </c>
+      <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
       <c r="W64" s="2" t="n">
         <v>129</v>
@@ -5466,9 +5292,7 @@
       <c r="T65" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="U65" s="2" t="n">
-        <v>23.6</v>
-      </c>
+      <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" t="inlineStr"/>
       <c r="W65" s="2" t="n">
         <v>132.4</v>
@@ -5541,9 +5365,7 @@
       <c r="T66" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="U66" s="2" t="n">
-        <v>21.4</v>
-      </c>
+      <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
       <c r="W66" s="2" t="n">
         <v>131.3</v>
@@ -5616,9 +5438,7 @@
       <c r="T67" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U67" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" s="2" t="n">
         <v>134.3</v>
@@ -5691,9 +5511,7 @@
       <c r="T68" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U68" s="2" t="n">
-        <v>22.9</v>
-      </c>
+      <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" s="2" t="n">
         <v>132.7</v>
@@ -5766,9 +5584,7 @@
       <c r="T69" s="2" t="n">
         <v>24.6</v>
       </c>
-      <c r="U69" s="3" t="n">
-        <v>27.5</v>
-      </c>
+      <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
       <c r="W69" s="2" t="n">
         <v>134.1</v>
@@ -5841,9 +5657,7 @@
       <c r="T70" s="2" t="n">
         <v>22.7</v>
       </c>
-      <c r="U70" s="2" t="n">
-        <v>20</v>
-      </c>
+      <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
       <c r="W70" s="2" t="n">
         <v>134.8</v>
@@ -5920,9 +5734,7 @@
       <c r="T71" s="2" t="n">
         <v>23.6</v>
       </c>
-      <c r="U71" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" t="inlineStr"/>
       <c r="W71" s="2" t="n">
         <v>134.1</v>
@@ -5995,9 +5807,7 @@
       <c r="T72" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="U72" s="2" t="n">
-        <v>22.2</v>
-      </c>
+      <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
       <c r="W72" s="2" t="n">
         <v>133.2</v>
@@ -6070,9 +5880,7 @@
       <c r="T73" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U73" s="2" t="n">
-        <v>19.8</v>
-      </c>
+      <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" t="inlineStr"/>
       <c r="W73" s="2" t="n">
         <v>132.2</v>
@@ -6145,9 +5953,7 @@
       <c r="T74" s="2" t="n">
         <v>22.5</v>
       </c>
-      <c r="U74" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" t="inlineStr"/>
       <c r="W74" s="2" t="n">
         <v>131.5</v>
@@ -6220,9 +6026,7 @@
       <c r="T75" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="U75" s="3" t="n">
-        <v>26.9</v>
-      </c>
+      <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
       <c r="W75" s="2" t="n">
         <v>128.4</v>
@@ -6295,9 +6099,7 @@
       <c r="T76" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U76" s="2" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
       <c r="W76" s="2" t="n">
         <v>137.7</v>
@@ -6370,9 +6172,7 @@
       <c r="T77" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U77" s="2" t="n">
-        <v>15.4</v>
-      </c>
+      <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
       <c r="W77" s="2" t="n">
         <v>140.5</v>
@@ -6445,9 +6245,7 @@
       <c r="T78" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U78" s="2" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
       <c r="W78" s="2" t="n">
         <v>138.9</v>
@@ -6520,9 +6318,7 @@
       <c r="T79" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U79" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" t="inlineStr"/>
       <c r="W79" s="2" t="n">
         <v>140.9</v>
@@ -6595,9 +6391,7 @@
       <c r="T80" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U80" s="2" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
       <c r="W80" s="2" t="n">
         <v>136</v>
@@ -6670,9 +6464,7 @@
       <c r="T81" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U81" s="2" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" t="inlineStr"/>
       <c r="W81" s="2" t="n">
         <v>135.9</v>
@@ -6745,9 +6537,7 @@
       <c r="T82" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U82" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" t="inlineStr"/>
       <c r="W82" s="2" t="n">
         <v>137.3</v>
@@ -6820,9 +6610,7 @@
       <c r="T83" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="U83" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" t="inlineStr"/>
       <c r="W83" s="2" t="n">
         <v>137.3</v>
@@ -6895,9 +6683,7 @@
       <c r="T84" s="2" t="n">
         <v>20.3</v>
       </c>
-      <c r="U84" s="2" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
       <c r="W84" s="2" t="n">
         <v>139</v>
@@ -6974,9 +6760,7 @@
       <c r="T85" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="U85" s="2" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" t="inlineStr"/>
       <c r="W85" s="2" t="n">
         <v>139.3</v>
@@ -7049,9 +6833,7 @@
       <c r="T86" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U86" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" t="inlineStr"/>
       <c r="W86" s="2" t="n">
         <v>140.9</v>
@@ -7124,9 +6906,7 @@
       <c r="T87" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U87" s="2" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" t="inlineStr"/>
       <c r="W87" s="2" t="n">
         <v>137.6</v>
@@ -7199,9 +6979,7 @@
       <c r="T88" s="2" t="n">
         <v>19.2</v>
       </c>
-      <c r="U88" s="2" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" t="inlineStr"/>
       <c r="W88" s="2" t="n">
         <v>137.3</v>
@@ -7274,9 +7052,7 @@
       <c r="T89" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U89" s="2" t="n">
-        <v>17</v>
-      </c>
+      <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" t="inlineStr"/>
       <c r="W89" s="2" t="n">
         <v>138.2</v>
@@ -7349,9 +7125,7 @@
       <c r="T90" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U90" s="2" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" t="inlineStr"/>
       <c r="W90" s="2" t="n">
         <v>141</v>
@@ -7424,9 +7198,7 @@
       <c r="T91" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U91" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" t="inlineStr"/>
       <c r="W91" s="2" t="n">
         <v>141.6</v>
@@ -7499,9 +7271,7 @@
       <c r="T92" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U92" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" t="inlineStr"/>
       <c r="W92" s="2" t="n">
         <v>137.5</v>
@@ -7574,9 +7344,7 @@
       <c r="T93" s="2" t="n">
         <v>18.5</v>
       </c>
-      <c r="U93" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" t="inlineStr"/>
       <c r="W93" s="2" t="n">
         <v>140.1</v>
@@ -7649,9 +7417,7 @@
       <c r="T94" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U94" s="2" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" t="inlineStr"/>
       <c r="W94" s="2" t="n">
         <v>138.9</v>
@@ -7724,9 +7490,7 @@
       <c r="T95" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U95" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" t="inlineStr"/>
       <c r="W95" s="2" t="n">
         <v>139.2</v>
@@ -7799,9 +7563,7 @@
       <c r="T96" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U96" s="2" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U96" s="2" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
       <c r="W96" s="2" t="n">
         <v>141.2</v>
@@ -7874,9 +7636,7 @@
       <c r="T97" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U97" s="2" t="n">
-        <v>13.9</v>
-      </c>
+      <c r="U97" s="2" t="inlineStr"/>
       <c r="V97" t="inlineStr"/>
       <c r="W97" s="2" t="n">
         <v>141.4</v>
@@ -7949,9 +7709,7 @@
       <c r="T98" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U98" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U98" s="2" t="inlineStr"/>
       <c r="V98" t="inlineStr"/>
       <c r="W98" s="2" t="n">
         <v>145.6</v>
@@ -8024,9 +7782,7 @@
       <c r="T99" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U99" s="2" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="U99" s="2" t="inlineStr"/>
       <c r="V99" t="inlineStr"/>
       <c r="W99" s="2" t="n">
         <v>149.6</v>
@@ -8099,9 +7855,7 @@
       <c r="T100" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U100" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U100" s="2" t="inlineStr"/>
       <c r="V100" t="inlineStr"/>
       <c r="W100" s="1" t="n">
         <v>156.6</v>
@@ -8174,9 +7928,7 @@
       <c r="T101" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="U101" s="2" t="n">
-        <v>21</v>
-      </c>
+      <c r="U101" s="2" t="inlineStr"/>
       <c r="V101" t="inlineStr"/>
       <c r="W101" s="2" t="n">
         <v>154.4</v>
@@ -8249,9 +8001,7 @@
       <c r="T102" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="U102" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U102" s="2" t="inlineStr"/>
       <c r="V102" t="inlineStr"/>
       <c r="W102" s="2" t="n">
         <v>148.4</v>
@@ -8324,9 +8074,7 @@
       <c r="T103" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U103" s="2" t="n">
-        <v>18.4</v>
-      </c>
+      <c r="U103" s="2" t="inlineStr"/>
       <c r="V103" t="inlineStr"/>
       <c r="W103" s="2" t="n">
         <v>149.2</v>
@@ -8399,9 +8147,7 @@
       <c r="T104" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U104" s="2" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U104" s="2" t="inlineStr"/>
       <c r="V104" t="inlineStr"/>
       <c r="W104" s="2" t="n">
         <v>154.8</v>
@@ -8474,9 +8220,7 @@
       <c r="T105" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U105" s="2" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U105" s="2" t="inlineStr"/>
       <c r="V105" t="inlineStr"/>
       <c r="W105" s="1" t="n">
         <v>155</v>
@@ -8549,9 +8293,7 @@
       <c r="T106" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U106" s="2" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="U106" s="2" t="inlineStr"/>
       <c r="V106" t="inlineStr"/>
       <c r="W106" s="2" t="n">
         <v>152.2</v>
@@ -8624,9 +8366,7 @@
       <c r="T107" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U107" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U107" s="2" t="inlineStr"/>
       <c r="V107" t="inlineStr"/>
       <c r="W107" s="2" t="n">
         <v>147.5</v>
@@ -8699,9 +8439,7 @@
       <c r="T108" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U108" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U108" s="2" t="inlineStr"/>
       <c r="V108" t="inlineStr"/>
       <c r="W108" s="2" t="n">
         <v>143.4</v>
@@ -8774,9 +8512,7 @@
       <c r="T109" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U109" s="2" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U109" s="2" t="inlineStr"/>
       <c r="V109" t="inlineStr"/>
       <c r="W109" s="2" t="n">
         <v>139.6</v>
@@ -8815,7 +8551,7 @@
         <v>2</v>
       </c>
       <c r="J110" t="n">
-        <v>6043.06</v>
+        <v>6043.05</v>
       </c>
       <c r="K110" t="n">
         <v>5748.09</v>
@@ -8849,9 +8585,7 @@
       <c r="T110" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U110" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="U110" s="2" t="inlineStr"/>
       <c r="V110" t="inlineStr"/>
       <c r="W110" s="2" t="n">
         <v>140.1</v>
@@ -8924,9 +8658,7 @@
       <c r="T111" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U111" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U111" s="2" t="inlineStr"/>
       <c r="V111" t="inlineStr"/>
       <c r="W111" s="2" t="n">
         <v>139.3</v>
@@ -8999,9 +8731,7 @@
       <c r="T112" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U112" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U112" s="2" t="inlineStr"/>
       <c r="V112" t="inlineStr"/>
       <c r="W112" s="2" t="n">
         <v>141.4</v>
@@ -9074,9 +8804,7 @@
       <c r="T113" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U113" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U113" s="2" t="inlineStr"/>
       <c r="V113" t="inlineStr"/>
       <c r="W113" s="2" t="n">
         <v>138</v>
@@ -9149,9 +8877,7 @@
       <c r="T114" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U114" s="2" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="U114" s="2" t="inlineStr"/>
       <c r="V114" t="inlineStr"/>
       <c r="W114" s="2" t="n">
         <v>140.8</v>
@@ -9224,9 +8950,7 @@
       <c r="T115" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U115" s="2" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U115" s="2" t="inlineStr"/>
       <c r="V115" t="inlineStr"/>
       <c r="W115" s="2" t="n">
         <v>141.8</v>
@@ -9299,9 +9023,7 @@
       <c r="T116" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U116" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U116" s="2" t="inlineStr"/>
       <c r="V116" t="inlineStr"/>
       <c r="W116" s="2" t="n">
         <v>143.3</v>
@@ -9374,9 +9096,7 @@
       <c r="T117" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U117" s="2" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U117" s="2" t="inlineStr"/>
       <c r="V117" t="inlineStr"/>
       <c r="W117" s="2" t="n">
         <v>145</v>
@@ -9449,9 +9169,7 @@
       <c r="T118" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U118" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U118" s="2" t="inlineStr"/>
       <c r="V118" t="inlineStr"/>
       <c r="W118" s="2" t="n">
         <v>147</v>
@@ -9524,9 +9242,7 @@
       <c r="T119" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U119" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U119" s="2" t="inlineStr"/>
       <c r="V119" t="inlineStr"/>
       <c r="W119" s="2" t="n">
         <v>143.7</v>
@@ -9599,9 +9315,7 @@
       <c r="T120" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U120" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U120" s="2" t="inlineStr"/>
       <c r="V120" t="inlineStr"/>
       <c r="W120" s="2" t="n">
         <v>146.7</v>
@@ -9674,9 +9388,7 @@
       <c r="T121" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U121" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U121" s="2" t="inlineStr"/>
       <c r="V121" t="inlineStr"/>
       <c r="W121" s="2" t="n">
         <v>151.1</v>
@@ -9749,9 +9461,7 @@
       <c r="T122" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U122" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U122" s="2" t="inlineStr"/>
       <c r="V122" t="inlineStr"/>
       <c r="W122" s="2" t="n">
         <v>150.4</v>
@@ -9824,9 +9534,7 @@
       <c r="T123" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U123" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U123" s="2" t="inlineStr"/>
       <c r="V123" t="inlineStr"/>
       <c r="W123" s="2" t="n">
         <v>154.8</v>
@@ -9899,9 +9607,7 @@
       <c r="T124" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U124" s="2" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="U124" s="2" t="inlineStr"/>
       <c r="V124" t="inlineStr"/>
       <c r="W124" s="2" t="n">
         <v>153.4</v>
@@ -9974,9 +9680,7 @@
       <c r="T125" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U125" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U125" s="2" t="inlineStr"/>
       <c r="V125" t="inlineStr"/>
       <c r="W125" s="1" t="n">
         <v>159.3</v>
@@ -10049,9 +9753,7 @@
       <c r="T126" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U126" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U126" s="2" t="inlineStr"/>
       <c r="V126" t="inlineStr"/>
       <c r="W126" s="1" t="n">
         <v>159.4</v>
@@ -10124,9 +9826,7 @@
       <c r="T127" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U127" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U127" s="2" t="inlineStr"/>
       <c r="V127" t="inlineStr"/>
       <c r="W127" s="2" t="n">
         <v>145.6</v>
@@ -10199,9 +9899,7 @@
       <c r="T128" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U128" s="2" t="n">
-        <v>7.9</v>
-      </c>
+      <c r="U128" s="2" t="inlineStr"/>
       <c r="V128" t="inlineStr"/>
       <c r="W128" s="2" t="n">
         <v>147.6</v>
@@ -10274,9 +9972,7 @@
       <c r="T129" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U129" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U129" s="2" t="inlineStr"/>
       <c r="V129" t="inlineStr"/>
       <c r="W129" s="2" t="n">
         <v>149.1</v>
@@ -10349,9 +10045,7 @@
       <c r="T130" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U130" s="2" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U130" s="2" t="inlineStr"/>
       <c r="V130" t="inlineStr"/>
       <c r="W130" s="2" t="n">
         <v>154.1</v>
@@ -10424,9 +10118,7 @@
       <c r="T131" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U131" s="2" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U131" s="2" t="inlineStr"/>
       <c r="V131" t="inlineStr"/>
       <c r="W131" s="2" t="n">
         <v>152.3</v>
@@ -10503,9 +10195,7 @@
       <c r="T132" s="2" t="n">
         <v>20.4</v>
       </c>
-      <c r="U132" s="2" t="n">
-        <v>20</v>
-      </c>
+      <c r="U132" s="2" t="inlineStr"/>
       <c r="V132" t="inlineStr"/>
       <c r="W132" s="1" t="n">
         <v>155.5</v>
@@ -10578,9 +10268,7 @@
       <c r="T133" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U133" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U133" s="2" t="inlineStr"/>
       <c r="V133" t="inlineStr"/>
       <c r="W133" s="1" t="n">
         <v>159.3</v>
@@ -10657,9 +10345,7 @@
       <c r="T134" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U134" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U134" s="2" t="inlineStr"/>
       <c r="V134" t="inlineStr"/>
       <c r="W134" s="2" t="n">
         <v>149.9</v>
@@ -10732,9 +10418,7 @@
       <c r="T135" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U135" s="2" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="U135" s="2" t="inlineStr"/>
       <c r="V135" t="inlineStr"/>
       <c r="W135" s="2" t="n">
         <v>149.7</v>
@@ -10807,9 +10491,7 @@
       <c r="T136" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U136" s="2" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U136" s="2" t="inlineStr"/>
       <c r="V136" t="inlineStr"/>
       <c r="W136" s="2" t="n">
         <v>147</v>
@@ -10882,9 +10564,7 @@
       <c r="T137" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U137" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U137" s="2" t="inlineStr"/>
       <c r="V137" t="inlineStr"/>
       <c r="W137" s="2" t="n">
         <v>147.5</v>
@@ -10957,9 +10637,7 @@
       <c r="T138" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U138" s="2" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U138" s="2" t="inlineStr"/>
       <c r="V138" t="inlineStr"/>
       <c r="W138" s="2" t="n">
         <v>148.6</v>
@@ -11032,9 +10710,7 @@
       <c r="T139" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="U139" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U139" s="2" t="inlineStr"/>
       <c r="V139" t="inlineStr"/>
       <c r="W139" s="2" t="n">
         <v>151.4</v>
@@ -11107,9 +10783,7 @@
       <c r="T140" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U140" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U140" s="2" t="inlineStr"/>
       <c r="V140" t="inlineStr"/>
       <c r="W140" s="2" t="n">
         <v>153.1</v>
@@ -11182,9 +10856,7 @@
       <c r="T141" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U141" s="2" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U141" s="2" t="inlineStr"/>
       <c r="V141" t="inlineStr"/>
       <c r="W141" s="2" t="n">
         <v>150.6</v>
@@ -11257,9 +10929,7 @@
       <c r="T142" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U142" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U142" s="2" t="inlineStr"/>
       <c r="V142" t="inlineStr"/>
       <c r="W142" s="2" t="n">
         <v>153.8</v>
@@ -11332,9 +11002,7 @@
       <c r="T143" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U143" s="2" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="U143" s="2" t="inlineStr"/>
       <c r="V143" t="inlineStr"/>
       <c r="W143" s="2" t="n">
         <v>153.9</v>
@@ -11407,9 +11075,7 @@
       <c r="T144" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U144" s="2" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U144" s="2" t="inlineStr"/>
       <c r="V144" t="inlineStr"/>
       <c r="W144" s="2" t="n">
         <v>153.2</v>
@@ -11482,9 +11148,7 @@
       <c r="T145" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U145" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U145" s="2" t="inlineStr"/>
       <c r="V145" t="inlineStr"/>
       <c r="W145" s="2" t="n">
         <v>144.6</v>
@@ -11561,9 +11225,7 @@
       <c r="T146" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U146" s="2" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U146" s="2" t="inlineStr"/>
       <c r="V146" t="inlineStr"/>
       <c r="W146" s="2" t="n">
         <v>144.3</v>
@@ -11608,7 +11270,7 @@
         <v>6219.75</v>
       </c>
       <c r="L147" t="n">
-        <v>5913.87</v>
+        <v>5913.86</v>
       </c>
       <c r="M147" t="n">
         <v>5944.69</v>
@@ -11636,9 +11298,7 @@
       <c r="T147" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U147" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U147" s="2" t="inlineStr"/>
       <c r="V147" t="inlineStr"/>
       <c r="W147" s="2" t="n">
         <v>146.4</v>
@@ -11711,9 +11371,7 @@
       <c r="T148" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U148" s="2" t="n">
-        <v>8.1</v>
-      </c>
+      <c r="U148" s="2" t="inlineStr"/>
       <c r="V148" t="inlineStr"/>
       <c r="W148" s="2" t="n">
         <v>150</v>
@@ -11786,9 +11444,7 @@
       <c r="T149" s="2" t="n">
         <v>14.6</v>
       </c>
-      <c r="U149" s="2" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="U149" s="2" t="inlineStr"/>
       <c r="V149" t="inlineStr"/>
       <c r="W149" s="1" t="n">
         <v>156.5</v>
@@ -11861,9 +11517,7 @@
       <c r="T150" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U150" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U150" s="2" t="inlineStr"/>
       <c r="V150" t="inlineStr"/>
       <c r="W150" s="2" t="n">
         <v>150.9</v>
@@ -11936,9 +11590,7 @@
       <c r="T151" s="2" t="n">
         <v>14.4</v>
       </c>
-      <c r="U151" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U151" s="2" t="inlineStr"/>
       <c r="V151" t="inlineStr"/>
       <c r="W151" s="2" t="n">
         <v>152.5</v>
@@ -12011,9 +11663,7 @@
       <c r="T152" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U152" s="2" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U152" s="2" t="inlineStr"/>
       <c r="V152" t="inlineStr"/>
       <c r="W152" s="2" t="n">
         <v>152.1</v>
@@ -12090,9 +11740,7 @@
       <c r="T153" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U153" s="2" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="U153" s="2" t="inlineStr"/>
       <c r="V153" t="inlineStr"/>
       <c r="W153" s="2" t="n">
         <v>151.5</v>
@@ -12165,9 +11813,7 @@
       <c r="T154" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U154" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U154" s="2" t="inlineStr"/>
       <c r="V154" t="inlineStr"/>
       <c r="W154" s="2" t="n">
         <v>150.2</v>
@@ -12240,9 +11886,7 @@
       <c r="T155" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U155" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U155" s="2" t="inlineStr"/>
       <c r="V155" t="inlineStr"/>
       <c r="W155" s="2" t="n">
         <v>154</v>
@@ -12315,9 +11959,7 @@
       <c r="T156" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U156" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U156" s="2" t="inlineStr"/>
       <c r="V156" t="inlineStr"/>
       <c r="W156" s="2" t="n">
         <v>148.2</v>
@@ -12390,9 +12032,7 @@
       <c r="T157" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U157" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="U157" s="2" t="inlineStr"/>
       <c r="V157" t="inlineStr"/>
       <c r="W157" s="2" t="n">
         <v>148.8</v>
@@ -12465,9 +12105,7 @@
       <c r="T158" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U158" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U158" s="2" t="inlineStr"/>
       <c r="V158" t="inlineStr"/>
       <c r="W158" s="2" t="n">
         <v>150.9</v>
@@ -12540,9 +12178,7 @@
       <c r="T159" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U159" s="2" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U159" s="2" t="inlineStr"/>
       <c r="V159" t="inlineStr"/>
       <c r="W159" s="2" t="n">
         <v>151.9</v>
@@ -12615,9 +12251,7 @@
       <c r="T160" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="U160" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U160" s="2" t="inlineStr"/>
       <c r="V160" t="inlineStr"/>
       <c r="W160" s="2" t="n">
         <v>147.6</v>
@@ -12690,9 +12324,7 @@
       <c r="T161" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U161" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U161" s="2" t="inlineStr"/>
       <c r="V161" t="inlineStr"/>
       <c r="W161" s="2" t="n">
         <v>149.5</v>
@@ -12765,9 +12397,7 @@
       <c r="T162" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U162" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="U162" s="2" t="inlineStr"/>
       <c r="V162" t="inlineStr"/>
       <c r="W162" s="2" t="n">
         <v>152.1</v>
@@ -12840,9 +12470,7 @@
       <c r="T163" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U163" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U163" s="2" t="inlineStr"/>
       <c r="V163" t="inlineStr"/>
       <c r="W163" s="2" t="n">
         <v>148.2</v>
@@ -12915,9 +12543,7 @@
       <c r="T164" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U164" s="2" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="U164" s="2" t="inlineStr"/>
       <c r="V164" t="inlineStr"/>
       <c r="W164" s="2" t="n">
         <v>146.4</v>
@@ -12990,9 +12616,7 @@
       <c r="T165" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U165" s="2" t="n">
-        <v>14.4</v>
-      </c>
+      <c r="U165" s="2" t="inlineStr"/>
       <c r="V165" t="inlineStr"/>
       <c r="W165" s="2" t="n">
         <v>148.2</v>
@@ -13065,9 +12689,7 @@
       <c r="T166" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U166" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U166" s="2" t="inlineStr"/>
       <c r="V166" t="inlineStr"/>
       <c r="W166" s="2" t="n">
         <v>147</v>
@@ -13140,9 +12762,7 @@
       <c r="T167" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U167" s="2" t="n">
-        <v>9.1</v>
-      </c>
+      <c r="U167" s="2" t="inlineStr"/>
       <c r="V167" t="inlineStr"/>
       <c r="W167" s="2" t="n">
         <v>145.5</v>
@@ -13215,9 +12835,7 @@
       <c r="T168" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U168" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="U168" s="2" t="inlineStr"/>
       <c r="V168" t="inlineStr"/>
       <c r="W168" s="2" t="n">
         <v>146.5</v>
@@ -13290,9 +12908,7 @@
       <c r="T169" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U169" s="2" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="U169" s="2" t="inlineStr"/>
       <c r="V169" t="inlineStr"/>
       <c r="W169" s="2" t="n">
         <v>145.9</v>
@@ -13365,9 +12981,7 @@
       <c r="T170" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U170" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U170" s="2" t="inlineStr"/>
       <c r="V170" t="inlineStr"/>
       <c r="W170" s="2" t="n">
         <v>145.9</v>
@@ -13440,9 +13054,7 @@
       <c r="T171" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U171" s="2" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U171" s="2" t="inlineStr"/>
       <c r="V171" t="inlineStr"/>
       <c r="W171" s="2" t="n">
         <v>141.5</v>
@@ -13515,9 +13127,7 @@
       <c r="T172" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U172" s="2" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U172" s="2" t="inlineStr"/>
       <c r="V172" t="inlineStr"/>
       <c r="W172" s="2" t="n">
         <v>143</v>
@@ -13590,9 +13200,7 @@
       <c r="T173" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U173" s="2" t="n">
-        <v>12</v>
-      </c>
+      <c r="U173" s="2" t="inlineStr"/>
       <c r="V173" t="inlineStr"/>
       <c r="W173" s="2" t="n">
         <v>143.4</v>
@@ -13665,9 +13273,7 @@
       <c r="T174" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U174" s="2" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U174" s="2" t="inlineStr"/>
       <c r="V174" t="inlineStr"/>
       <c r="W174" s="2" t="n">
         <v>143.7</v>
@@ -13740,9 +13346,7 @@
       <c r="T175" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U175" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U175" s="2" t="inlineStr"/>
       <c r="V175" t="inlineStr"/>
       <c r="W175" s="2" t="n">
         <v>145.9</v>
@@ -13815,9 +13419,7 @@
       <c r="T176" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U176" s="2" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U176" s="2" t="inlineStr"/>
       <c r="V176" t="inlineStr"/>
       <c r="W176" s="2" t="n">
         <v>144.6</v>
@@ -13890,9 +13492,7 @@
       <c r="T177" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U177" s="2" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="U177" s="2" t="inlineStr"/>
       <c r="V177" t="inlineStr"/>
       <c r="W177" s="2" t="n">
         <v>142.5</v>
@@ -13965,9 +13565,7 @@
       <c r="T178" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U178" s="2" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U178" s="2" t="inlineStr"/>
       <c r="V178" t="inlineStr"/>
       <c r="W178" s="2" t="n">
         <v>145.2</v>
@@ -14040,9 +13638,7 @@
       <c r="T179" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U179" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U179" s="2" t="inlineStr"/>
       <c r="V179" t="inlineStr"/>
       <c r="W179" s="2" t="n">
         <v>145.8</v>
@@ -14115,9 +13711,7 @@
       <c r="T180" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U180" s="2" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U180" s="2" t="inlineStr"/>
       <c r="V180" t="inlineStr"/>
       <c r="W180" s="2" t="n">
         <v>145.3</v>
@@ -14194,9 +13788,7 @@
       <c r="T181" s="7" t="n">
         <v>21.7</v>
       </c>
-      <c r="U181" s="6" t="n">
-        <v>25.7</v>
-      </c>
+      <c r="U181" s="7" t="inlineStr"/>
       <c r="V181" s="4" t="inlineStr"/>
       <c r="W181" s="7" t="n">
         <v>138.9</v>
@@ -14269,9 +13861,7 @@
       <c r="T182" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U182" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U182" s="2" t="inlineStr"/>
       <c r="V182" t="inlineStr"/>
       <c r="W182" s="2" t="n">
         <v>142.8</v>
@@ -14344,9 +13934,7 @@
       <c r="T183" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U183" s="2" t="n">
-        <v>17.7</v>
-      </c>
+      <c r="U183" s="2" t="inlineStr"/>
       <c r="V183" t="inlineStr"/>
       <c r="W183" s="2" t="n">
         <v>146.5</v>
@@ -14419,9 +14007,7 @@
       <c r="T184" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U184" s="2" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U184" s="2" t="inlineStr"/>
       <c r="V184" t="inlineStr"/>
       <c r="W184" s="2" t="n">
         <v>145</v>
@@ -14494,9 +14080,7 @@
       <c r="T185" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="U185" s="2" t="n">
-        <v>23.8</v>
-      </c>
+      <c r="U185" s="2" t="inlineStr"/>
       <c r="V185" t="inlineStr"/>
       <c r="W185" s="2" t="n">
         <v>147.1</v>
@@ -14569,9 +14153,7 @@
       <c r="T186" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U186" s="2" t="n">
-        <v>17.9</v>
-      </c>
+      <c r="U186" s="2" t="inlineStr"/>
       <c r="V186" t="inlineStr"/>
       <c r="W186" s="2" t="n">
         <v>147.6</v>
@@ -14644,9 +14226,7 @@
       <c r="T187" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U187" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U187" s="2" t="inlineStr"/>
       <c r="V187" t="inlineStr"/>
       <c r="W187" s="2" t="n">
         <v>151.3</v>
@@ -14719,9 +14299,7 @@
       <c r="T188" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U188" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U188" s="2" t="inlineStr"/>
       <c r="V188" t="inlineStr"/>
       <c r="W188" s="2" t="n">
         <v>149.9</v>
@@ -14794,9 +14372,7 @@
       <c r="T189" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U189" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U189" s="2" t="inlineStr"/>
       <c r="V189" t="inlineStr"/>
       <c r="W189" s="2" t="n">
         <v>152.9</v>
@@ -14869,9 +14445,7 @@
       <c r="T190" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U190" s="2" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U190" s="2" t="inlineStr"/>
       <c r="V190" t="inlineStr"/>
       <c r="W190" s="2" t="n">
         <v>154.3</v>
@@ -14944,9 +14518,7 @@
       <c r="T191" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U191" s="2" t="n">
-        <v>14.5</v>
-      </c>
+      <c r="U191" s="2" t="inlineStr"/>
       <c r="V191" t="inlineStr"/>
       <c r="W191" s="2" t="n">
         <v>153.5</v>
@@ -15019,9 +14591,7 @@
       <c r="T192" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U192" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U192" s="2" t="inlineStr"/>
       <c r="V192" t="inlineStr"/>
       <c r="W192" s="2" t="n">
         <v>148.5</v>
@@ -15094,9 +14664,7 @@
       <c r="T193" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U193" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U193" s="2" t="inlineStr"/>
       <c r="V193" t="inlineStr"/>
       <c r="W193" s="2" t="n">
         <v>140.4</v>
@@ -15169,9 +14737,7 @@
       <c r="T194" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U194" s="2" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U194" s="2" t="inlineStr"/>
       <c r="V194" t="inlineStr"/>
       <c r="W194" s="2" t="n">
         <v>139.4</v>
@@ -15244,9 +14810,7 @@
       <c r="T195" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U195" s="2" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="U195" s="2" t="inlineStr"/>
       <c r="V195" t="inlineStr"/>
       <c r="W195" s="2" t="n">
         <v>141.1</v>
@@ -15319,9 +14883,7 @@
       <c r="T196" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U196" s="2" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U196" s="2" t="inlineStr"/>
       <c r="V196" t="inlineStr"/>
       <c r="W196" s="2" t="n">
         <v>142.8</v>
@@ -15394,9 +14956,7 @@
       <c r="T197" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U197" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U197" s="2" t="inlineStr"/>
       <c r="V197" t="inlineStr"/>
       <c r="W197" s="2" t="n">
         <v>142</v>
@@ -15469,9 +15029,7 @@
       <c r="T198" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U198" s="2" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U198" s="2" t="inlineStr"/>
       <c r="V198" t="inlineStr"/>
       <c r="W198" s="2" t="n">
         <v>144</v>
@@ -15544,9 +15102,7 @@
       <c r="T199" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U199" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U199" s="2" t="inlineStr"/>
       <c r="V199" t="inlineStr"/>
       <c r="W199" s="2" t="n">
         <v>143.6</v>
@@ -15623,9 +15179,7 @@
       <c r="T200" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U200" s="2" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U200" s="2" t="inlineStr"/>
       <c r="V200" t="inlineStr"/>
       <c r="W200" s="2" t="n">
         <v>143.5</v>
@@ -15698,9 +15252,7 @@
       <c r="T201" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U201" s="2" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U201" s="2" t="inlineStr"/>
       <c r="V201" t="inlineStr"/>
       <c r="W201" s="2" t="n">
         <v>141.3</v>
@@ -15773,9 +15325,7 @@
       <c r="T202" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U202" s="2" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U202" s="2" t="inlineStr"/>
       <c r="V202" t="inlineStr"/>
       <c r="W202" s="2" t="n">
         <v>142.9</v>
@@ -15848,9 +15398,7 @@
       <c r="T203" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U203" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U203" s="2" t="inlineStr"/>
       <c r="V203" t="inlineStr"/>
       <c r="W203" s="2" t="n">
         <v>143.4</v>
@@ -15923,9 +15471,7 @@
       <c r="T204" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U204" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U204" s="2" t="inlineStr"/>
       <c r="V204" t="inlineStr"/>
       <c r="W204" s="2" t="n">
         <v>138.6</v>
@@ -16002,9 +15548,7 @@
       <c r="T205" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="U205" s="2" t="n">
-        <v>17</v>
-      </c>
+      <c r="U205" s="2" t="inlineStr"/>
       <c r="V205" t="inlineStr"/>
       <c r="W205" s="2" t="n">
         <v>142.5</v>
@@ -16077,9 +15621,7 @@
       <c r="T206" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U206" s="2" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="U206" s="2" t="inlineStr"/>
       <c r="V206" t="inlineStr"/>
       <c r="W206" s="2" t="n">
         <v>137.9</v>
@@ -16152,9 +15694,7 @@
       <c r="T207" s="2" t="n">
         <v>22.4</v>
       </c>
-      <c r="U207" s="2" t="n">
-        <v>19.4</v>
-      </c>
+      <c r="U207" s="2" t="inlineStr"/>
       <c r="V207" t="inlineStr"/>
       <c r="W207" s="2" t="n">
         <v>140.9</v>
@@ -16231,9 +15771,7 @@
       <c r="T208" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U208" s="2" t="n">
-        <v>20.9</v>
-      </c>
+      <c r="U208" s="2" t="inlineStr"/>
       <c r="V208" t="inlineStr"/>
       <c r="W208" s="2" t="n">
         <v>143</v>
@@ -16306,9 +15844,7 @@
       <c r="T209" s="2" t="n">
         <v>23.7</v>
       </c>
-      <c r="U209" s="3" t="n">
-        <v>26.9</v>
-      </c>
+      <c r="U209" s="2" t="inlineStr"/>
       <c r="V209" t="inlineStr"/>
       <c r="W209" s="2" t="n">
         <v>143.1</v>
@@ -16381,14 +15917,8 @@
       <c r="T210" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="U210" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="V210" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U210" s="2" t="inlineStr"/>
+      <c r="V210" t="inlineStr"/>
       <c r="W210" s="2" t="n">
         <v>145</v>
       </c>
@@ -16460,9 +15990,7 @@
       <c r="T211" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="U211" s="2" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="U211" s="2" t="inlineStr"/>
       <c r="V211" t="inlineStr"/>
       <c r="W211" s="2" t="n">
         <v>148.3</v>
@@ -16535,9 +16063,7 @@
       <c r="T212" s="2" t="n">
         <v>20.5</v>
       </c>
-      <c r="U212" s="2" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="U212" s="2" t="inlineStr"/>
       <c r="V212" t="inlineStr"/>
       <c r="W212" s="2" t="n">
         <v>148.6</v>
@@ -16610,9 +16136,7 @@
       <c r="T213" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U213" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U213" s="2" t="inlineStr"/>
       <c r="V213" t="inlineStr"/>
       <c r="W213" s="2" t="n">
         <v>151.7</v>
@@ -16685,9 +16209,7 @@
       <c r="T214" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U214" s="2" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U214" s="2" t="inlineStr"/>
       <c r="V214" t="inlineStr"/>
       <c r="W214" s="2" t="n">
         <v>145</v>
@@ -16760,9 +16282,7 @@
       <c r="T215" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U215" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U215" s="2" t="inlineStr"/>
       <c r="V215" t="inlineStr"/>
       <c r="W215" s="2" t="n">
         <v>143</v>
@@ -16835,9 +16355,7 @@
       <c r="T216" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U216" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U216" s="2" t="inlineStr"/>
       <c r="V216" t="inlineStr"/>
       <c r="W216" s="2" t="n">
         <v>144.9</v>
@@ -16910,9 +16428,7 @@
       <c r="T217" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U217" s="2" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="U217" s="2" t="inlineStr"/>
       <c r="V217" t="inlineStr"/>
       <c r="W217" s="2" t="n">
         <v>144.9</v>
@@ -16985,9 +16501,7 @@
       <c r="T218" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U218" s="2" t="n">
-        <v>9.800000000000001</v>
-      </c>
+      <c r="U218" s="2" t="inlineStr"/>
       <c r="V218" t="inlineStr"/>
       <c r="W218" s="2" t="n">
         <v>149.2</v>
@@ -17060,9 +16574,7 @@
       <c r="T219" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U219" s="2" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U219" s="2" t="inlineStr"/>
       <c r="V219" t="inlineStr"/>
       <c r="W219" s="2" t="n">
         <v>148.9</v>
@@ -17135,9 +16647,7 @@
       <c r="T220" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U220" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U220" s="2" t="inlineStr"/>
       <c r="V220" t="inlineStr"/>
       <c r="W220" s="2" t="n">
         <v>148.8</v>
@@ -17210,9 +16720,7 @@
       <c r="T221" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U221" s="2" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="U221" s="2" t="inlineStr"/>
       <c r="V221" t="inlineStr"/>
       <c r="W221" s="2" t="n">
         <v>150.6</v>
@@ -17285,9 +16793,7 @@
       <c r="T222" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U222" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U222" s="2" t="inlineStr"/>
       <c r="V222" t="inlineStr"/>
       <c r="W222" s="2" t="n">
         <v>150.3</v>
@@ -17360,9 +16866,7 @@
       <c r="T223" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U223" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U223" s="2" t="inlineStr"/>
       <c r="V223" t="inlineStr"/>
       <c r="W223" s="2" t="n">
         <v>147.6</v>
@@ -17435,9 +16939,7 @@
       <c r="T224" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U224" s="2" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U224" s="2" t="inlineStr"/>
       <c r="V224" t="inlineStr"/>
       <c r="W224" s="2" t="n">
         <v>148.3</v>
@@ -17510,9 +17012,7 @@
       <c r="T225" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U225" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U225" s="2" t="inlineStr"/>
       <c r="V225" t="inlineStr"/>
       <c r="W225" s="2" t="n">
         <v>153.6</v>
@@ -17585,9 +17085,7 @@
       <c r="T226" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U226" s="2" t="n">
-        <v>12.9</v>
-      </c>
+      <c r="U226" s="2" t="inlineStr"/>
       <c r="V226" t="inlineStr"/>
       <c r="W226" s="1" t="n">
         <v>161.9</v>
@@ -17660,9 +17158,7 @@
       <c r="T227" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U227" s="2" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U227" s="2" t="inlineStr"/>
       <c r="V227" t="inlineStr"/>
       <c r="W227" s="1" t="n">
         <v>157</v>
@@ -17739,9 +17235,7 @@
       <c r="T228" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U228" s="2" t="n">
-        <v>16.9</v>
-      </c>
+      <c r="U228" s="2" t="inlineStr"/>
       <c r="V228" t="inlineStr"/>
       <c r="W228" s="2" t="n">
         <v>153.5</v>
@@ -17814,9 +17308,7 @@
       <c r="T229" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U229" s="2" t="n">
-        <v>15.8</v>
-      </c>
+      <c r="U229" s="2" t="inlineStr"/>
       <c r="V229" t="inlineStr"/>
       <c r="W229" s="1" t="n">
         <v>155.4</v>
@@ -17889,9 +17381,7 @@
       <c r="T230" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U230" s="2" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="U230" s="2" t="inlineStr"/>
       <c r="V230" t="inlineStr"/>
       <c r="W230" s="1" t="n">
         <v>155.9</v>
@@ -17964,9 +17454,7 @@
       <c r="T231" s="2" t="n">
         <v>14.1</v>
       </c>
-      <c r="U231" s="2" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="U231" s="2" t="inlineStr"/>
       <c r="V231" t="inlineStr"/>
       <c r="W231" s="1" t="n">
         <v>159.9</v>
@@ -18039,9 +17527,7 @@
       <c r="T232" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="U232" s="2" t="n">
-        <v>7.6</v>
-      </c>
+      <c r="U232" s="2" t="inlineStr"/>
       <c r="V232" t="inlineStr"/>
       <c r="W232" s="1" t="n">
         <v>160.5</v>
@@ -18114,9 +17600,7 @@
       <c r="T233" s="2" t="n">
         <v>13.5</v>
       </c>
-      <c r="U233" s="2" t="n">
-        <v>7.4</v>
-      </c>
+      <c r="U233" s="2" t="inlineStr"/>
       <c r="V233" t="inlineStr"/>
       <c r="W233" s="1" t="n">
         <v>160.5</v>
@@ -18189,9 +17673,7 @@
       <c r="T234" s="2" t="n">
         <v>13.6</v>
       </c>
-      <c r="U234" s="2" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="U234" s="2" t="inlineStr"/>
       <c r="V234" t="inlineStr"/>
       <c r="W234" s="2" t="n">
         <v>151.4</v>
@@ -18264,9 +17746,7 @@
       <c r="T235" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U235" s="2" t="n">
-        <v>8.800000000000001</v>
-      </c>
+      <c r="U235" s="2" t="inlineStr"/>
       <c r="V235" t="inlineStr"/>
       <c r="W235" s="2" t="n">
         <v>150.5</v>
@@ -18339,9 +17819,7 @@
       <c r="T236" s="2" t="n">
         <v>14.3</v>
       </c>
-      <c r="U236" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U236" s="2" t="inlineStr"/>
       <c r="V236" t="inlineStr"/>
       <c r="W236" s="2" t="n">
         <v>148.3</v>
@@ -18418,9 +17896,7 @@
       <c r="T237" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U237" s="2" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U237" s="2" t="inlineStr"/>
       <c r="V237" t="inlineStr"/>
       <c r="W237" s="2" t="n">
         <v>148.7</v>
@@ -18493,9 +17969,7 @@
       <c r="T238" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U238" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U238" s="2" t="inlineStr"/>
       <c r="V238" t="inlineStr"/>
       <c r="W238" s="2" t="n">
         <v>141.9</v>
@@ -18568,9 +18042,7 @@
       <c r="T239" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U239" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="U239" s="2" t="inlineStr"/>
       <c r="V239" t="inlineStr"/>
       <c r="W239" s="2" t="n">
         <v>142.4</v>
@@ -18643,9 +18115,7 @@
       <c r="T240" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U240" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="U240" s="2" t="inlineStr"/>
       <c r="V240" t="inlineStr"/>
       <c r="W240" s="2" t="n">
         <v>146.2</v>
@@ -18718,9 +18188,7 @@
       <c r="T241" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U241" s="2" t="n">
-        <v>9.199999999999999</v>
-      </c>
+      <c r="U241" s="2" t="inlineStr"/>
       <c r="V241" t="inlineStr"/>
       <c r="W241" s="2" t="n">
         <v>143.6</v>
@@ -18793,9 +18261,7 @@
       <c r="T242" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U242" s="2" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U242" s="2" t="inlineStr"/>
       <c r="V242" t="inlineStr"/>
       <c r="W242" s="2" t="n">
         <v>147.1</v>
@@ -18868,9 +18334,7 @@
       <c r="T243" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U243" s="2" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="U243" s="2" t="inlineStr"/>
       <c r="V243" t="inlineStr"/>
       <c r="W243" s="2" t="n">
         <v>146</v>
@@ -18943,9 +18407,7 @@
       <c r="T244" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U244" s="2" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U244" s="2" t="inlineStr"/>
       <c r="V244" t="inlineStr"/>
       <c r="W244" s="2" t="n">
         <v>149.8</v>
@@ -19018,9 +18480,7 @@
       <c r="T245" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U245" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U245" s="2" t="inlineStr"/>
       <c r="V245" t="inlineStr"/>
       <c r="W245" s="2" t="n">
         <v>151.6</v>
@@ -19093,9 +18553,7 @@
       <c r="T246" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U246" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U246" s="2" t="inlineStr"/>
       <c r="V246" t="inlineStr"/>
       <c r="W246" s="2" t="n">
         <v>152.5</v>
@@ -19168,9 +18626,7 @@
       <c r="T247" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U247" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U247" s="2" t="inlineStr"/>
       <c r="V247" t="inlineStr"/>
       <c r="W247" s="2" t="n">
         <v>151.6</v>
@@ -19243,9 +18699,7 @@
       <c r="T248" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U248" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U248" s="2" t="inlineStr"/>
       <c r="V248" t="inlineStr"/>
       <c r="W248" s="2" t="n">
         <v>153.6</v>
@@ -19322,9 +18776,7 @@
       <c r="T249" s="7" t="n">
         <v>20.1</v>
       </c>
-      <c r="U249" s="7" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U249" s="7" t="inlineStr"/>
       <c r="V249" s="4" t="inlineStr"/>
       <c r="W249" s="5" t="n">
         <v>155</v>
@@ -19397,9 +18849,7 @@
       <c r="T250" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U250" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U250" s="2" t="inlineStr"/>
       <c r="V250" t="inlineStr"/>
       <c r="W250" s="2" t="n">
         <v>144.4</v>
@@ -19472,9 +18922,7 @@
       <c r="T251" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U251" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U251" s="2" t="inlineStr"/>
       <c r="V251" t="inlineStr"/>
       <c r="W251" s="2" t="n">
         <v>141.3</v>
@@ -19547,9 +18995,7 @@
       <c r="T252" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U252" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U252" s="2" t="inlineStr"/>
       <c r="V252" t="inlineStr"/>
       <c r="W252" s="2" t="n">
         <v>144</v>
@@ -19622,9 +19068,7 @@
       <c r="T253" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U253" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="U253" s="2" t="inlineStr"/>
       <c r="V253" t="inlineStr"/>
       <c r="W253" s="2" t="n">
         <v>148.1</v>
@@ -19697,9 +19141,7 @@
       <c r="T254" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U254" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U254" s="2" t="inlineStr"/>
       <c r="V254" t="inlineStr"/>
       <c r="W254" s="2" t="n">
         <v>147.2</v>
@@ -19772,9 +19214,7 @@
       <c r="T255" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U255" s="2" t="n">
-        <v>13.2</v>
-      </c>
+      <c r="U255" s="2" t="inlineStr"/>
       <c r="V255" t="inlineStr"/>
       <c r="W255" s="2" t="n">
         <v>145</v>
@@ -19847,9 +19287,7 @@
       <c r="T256" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U256" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U256" s="2" t="inlineStr"/>
       <c r="V256" t="inlineStr"/>
       <c r="W256" s="2" t="n">
         <v>143.7</v>
@@ -19922,9 +19360,7 @@
       <c r="T257" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U257" s="2" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="U257" s="2" t="inlineStr"/>
       <c r="V257" t="inlineStr"/>
       <c r="W257" s="2" t="n">
         <v>143.6</v>
@@ -19997,9 +19433,7 @@
       <c r="T258" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U258" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U258" s="2" t="inlineStr"/>
       <c r="V258" t="inlineStr"/>
       <c r="W258" s="2" t="n">
         <v>146.6</v>
@@ -20076,9 +19510,7 @@
       <c r="T259" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U259" s="2" t="n">
-        <v>14.5</v>
-      </c>
+      <c r="U259" s="2" t="inlineStr"/>
       <c r="V259" t="inlineStr"/>
       <c r="W259" s="2" t="n">
         <v>143.9</v>
@@ -20151,9 +19583,7 @@
       <c r="T260" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U260" s="2" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="U260" s="2" t="inlineStr"/>
       <c r="V260" t="inlineStr"/>
       <c r="W260" s="2" t="n">
         <v>143.2</v>
@@ -20230,9 +19660,7 @@
       <c r="T261" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U261" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U261" s="2" t="inlineStr"/>
       <c r="V261" t="inlineStr"/>
       <c r="W261" s="2" t="n">
         <v>137.2</v>
@@ -20305,9 +19733,7 @@
       <c r="T262" s="2" t="n">
         <v>20.4</v>
       </c>
-      <c r="U262" s="2" t="n">
-        <v>15</v>
-      </c>
+      <c r="U262" s="2" t="inlineStr"/>
       <c r="V262" t="inlineStr"/>
       <c r="W262" s="2" t="n">
         <v>140.3</v>
@@ -20380,9 +19806,7 @@
       <c r="T263" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U263" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U263" s="2" t="inlineStr"/>
       <c r="V263" t="inlineStr"/>
       <c r="W263" s="2" t="n">
         <v>145.2</v>
@@ -20455,9 +19879,7 @@
       <c r="T264" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U264" s="2" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U264" s="2" t="inlineStr"/>
       <c r="V264" t="inlineStr"/>
       <c r="W264" s="2" t="n">
         <v>145.7</v>
@@ -20530,9 +19952,7 @@
       <c r="T265" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U265" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U265" s="2" t="inlineStr"/>
       <c r="V265" t="inlineStr"/>
       <c r="W265" s="2" t="n">
         <v>143.8</v>
@@ -20609,9 +20029,7 @@
       <c r="T266" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U266" s="2" t="n">
-        <v>21.5</v>
-      </c>
+      <c r="U266" s="2" t="inlineStr"/>
       <c r="V266" t="inlineStr"/>
       <c r="W266" s="2" t="n">
         <v>142.5</v>
@@ -20684,9 +20102,7 @@
       <c r="T267" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U267" s="2" t="n">
-        <v>22.4</v>
-      </c>
+      <c r="U267" s="2" t="inlineStr"/>
       <c r="V267" t="inlineStr"/>
       <c r="W267" s="2" t="n">
         <v>139.4</v>
@@ -20759,9 +20175,7 @@
       <c r="T268" s="2" t="n">
         <v>20.3</v>
       </c>
-      <c r="U268" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U268" s="2" t="inlineStr"/>
       <c r="V268" t="inlineStr"/>
       <c r="W268" s="2" t="n">
         <v>140.3</v>
@@ -20834,9 +20248,7 @@
       <c r="T269" s="2" t="n">
         <v>19.6</v>
       </c>
-      <c r="U269" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U269" s="2" t="inlineStr"/>
       <c r="V269" t="inlineStr"/>
       <c r="W269" s="2" t="n">
         <v>139.2</v>
@@ -20913,9 +20325,7 @@
       <c r="T270" s="2" t="n">
         <v>20.2</v>
       </c>
-      <c r="U270" s="2" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="U270" s="2" t="inlineStr"/>
       <c r="V270" t="inlineStr"/>
       <c r="W270" s="2" t="n">
         <v>141.2</v>
@@ -20988,9 +20398,7 @@
       <c r="T271" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U271" s="2" t="n">
-        <v>17.8</v>
-      </c>
+      <c r="U271" s="2" t="inlineStr"/>
       <c r="V271" t="inlineStr"/>
       <c r="W271" s="2" t="n">
         <v>145.5</v>
@@ -21067,9 +20475,7 @@
       <c r="T272" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="U272" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U272" s="2" t="inlineStr"/>
       <c r="V272" t="inlineStr"/>
       <c r="W272" s="2" t="n">
         <v>141.4</v>
@@ -21142,9 +20548,7 @@
       <c r="T273" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U273" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U273" s="2" t="inlineStr"/>
       <c r="V273" t="inlineStr"/>
       <c r="W273" s="2" t="n">
         <v>141.9</v>
@@ -21217,9 +20621,7 @@
       <c r="T274" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U274" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U274" s="2" t="inlineStr"/>
       <c r="V274" t="inlineStr"/>
       <c r="W274" s="2" t="n">
         <v>146.1</v>
@@ -21292,9 +20694,7 @@
       <c r="T275" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U275" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U275" s="2" t="inlineStr"/>
       <c r="V275" t="inlineStr"/>
       <c r="W275" s="2" t="n">
         <v>146.6</v>
@@ -21371,9 +20771,7 @@
       <c r="T276" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U276" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="U276" s="2" t="inlineStr"/>
       <c r="V276" t="inlineStr"/>
       <c r="W276" s="2" t="n">
         <v>146.7</v>
@@ -21446,9 +20844,7 @@
       <c r="T277" s="2" t="n">
         <v>21.4</v>
       </c>
-      <c r="U277" s="2" t="n">
-        <v>16.3</v>
-      </c>
+      <c r="U277" s="2" t="inlineStr"/>
       <c r="V277" t="inlineStr"/>
       <c r="W277" s="2" t="n">
         <v>151.8</v>
@@ -21521,9 +20917,7 @@
       <c r="T278" s="2" t="n">
         <v>23.6</v>
       </c>
-      <c r="U278" s="2" t="n">
-        <v>20.3</v>
-      </c>
+      <c r="U278" s="2" t="inlineStr"/>
       <c r="V278" t="inlineStr"/>
       <c r="W278" s="2" t="n">
         <v>152.8</v>
@@ -21596,9 +20990,7 @@
       <c r="T279" s="2" t="n">
         <v>21.1</v>
       </c>
-      <c r="U279" s="2" t="n">
-        <v>17.8</v>
-      </c>
+      <c r="U279" s="2" t="inlineStr"/>
       <c r="V279" t="inlineStr"/>
       <c r="W279" s="2" t="n">
         <v>152.9</v>
@@ -21671,9 +21063,7 @@
       <c r="T280" s="2" t="n">
         <v>23.8</v>
       </c>
-      <c r="U280" s="2" t="n">
-        <v>21.9</v>
-      </c>
+      <c r="U280" s="2" t="inlineStr"/>
       <c r="V280" t="inlineStr"/>
       <c r="W280" s="2" t="n">
         <v>153.9</v>
@@ -21750,14 +21140,8 @@
       <c r="T281" s="3" t="n">
         <v>29.5</v>
       </c>
-      <c r="U281" s="3" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="V281" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U281" s="2" t="inlineStr"/>
+      <c r="V281" t="inlineStr"/>
       <c r="W281" s="2" t="n">
         <v>151.8</v>
       </c>
@@ -21829,9 +21213,7 @@
       <c r="T282" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="U282" s="2" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="U282" s="2" t="inlineStr"/>
       <c r="V282" t="inlineStr"/>
       <c r="W282" s="1" t="n">
         <v>158</v>
@@ -21904,9 +21286,7 @@
       <c r="T283" s="2" t="n">
         <v>24.9</v>
       </c>
-      <c r="U283" s="2" t="n">
-        <v>21.3</v>
-      </c>
+      <c r="U283" s="2" t="inlineStr"/>
       <c r="V283" t="inlineStr"/>
       <c r="W283" s="2" t="n">
         <v>154.5</v>
@@ -21979,9 +21359,7 @@
       <c r="T284" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U284" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="U284" s="2" t="inlineStr"/>
       <c r="V284" t="inlineStr"/>
       <c r="W284" s="2" t="n">
         <v>152.4</v>
@@ -22048,9 +21426,7 @@
       <c r="T285" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="U285" s="2" t="n">
-        <v>24.2</v>
-      </c>
+      <c r="U285" s="2" t="inlineStr"/>
       <c r="V285" t="inlineStr"/>
       <c r="W285" s="2" t="n">
         <v>139.9</v>
@@ -22123,14 +21499,8 @@
       <c r="T286" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="U286" s="3" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="V286" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U286" s="2" t="inlineStr"/>
+      <c r="V286" t="inlineStr"/>
       <c r="W286" s="2" t="n">
         <v>137.8</v>
       </c>
@@ -22202,9 +21572,7 @@
       <c r="T287" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U287" s="2" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U287" s="2" t="inlineStr"/>
       <c r="V287" t="inlineStr"/>
       <c r="W287" s="2" t="n">
         <v>141.5</v>
@@ -22277,9 +21645,7 @@
       <c r="T288" s="2" t="n">
         <v>22.4</v>
       </c>
-      <c r="U288" s="2" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="U288" s="2" t="inlineStr"/>
       <c r="V288" t="inlineStr"/>
       <c r="W288" s="2" t="n">
         <v>145</v>
@@ -22352,9 +21718,7 @@
       <c r="T289" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="U289" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U289" s="2" t="inlineStr"/>
       <c r="V289" t="inlineStr"/>
       <c r="W289" s="2" t="n">
         <v>136.5</v>
@@ -22431,9 +21795,7 @@
       <c r="T290" s="2" t="n">
         <v>24.1</v>
       </c>
-      <c r="U290" s="2" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U290" s="2" t="inlineStr"/>
       <c r="V290" t="inlineStr"/>
       <c r="W290" s="2" t="n">
         <v>138.3</v>
@@ -22510,14 +21872,8 @@
       <c r="T291" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="U291" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="V291" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U291" s="2" t="inlineStr"/>
+      <c r="V291" t="inlineStr"/>
       <c r="W291" s="2" t="n">
         <v>139.1</v>
       </c>
@@ -22589,9 +21945,7 @@
       <c r="T292" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="U292" s="2" t="n">
-        <v>23.2</v>
-      </c>
+      <c r="U292" s="2" t="inlineStr"/>
       <c r="V292" t="inlineStr"/>
       <c r="W292" s="2" t="n">
         <v>142</v>
@@ -22668,9 +22022,7 @@
       <c r="T293" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="U293" s="2" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U293" s="2" t="inlineStr"/>
       <c r="V293" t="inlineStr"/>
       <c r="W293" s="2" t="n">
         <v>142.6</v>
@@ -22743,9 +22095,7 @@
       <c r="T294" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="U294" s="2" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U294" s="2" t="inlineStr"/>
       <c r="V294" t="inlineStr"/>
       <c r="W294" s="2" t="n">
         <v>140.9</v>
@@ -22818,9 +22168,7 @@
       <c r="T295" s="3" t="n">
         <v>27.4</v>
       </c>
-      <c r="U295" s="2" t="n">
-        <v>23.9</v>
-      </c>
+      <c r="U295" s="2" t="inlineStr"/>
       <c r="V295" t="inlineStr"/>
       <c r="W295" s="2" t="n">
         <v>144</v>
@@ -22897,14 +22245,8 @@
       <c r="T296" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="U296" s="3" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="V296" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U296" s="2" t="inlineStr"/>
+      <c r="V296" t="inlineStr"/>
       <c r="W296" s="2" t="n">
         <v>139</v>
       </c>
@@ -22980,9 +22322,7 @@
       <c r="T297" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="U297" s="2" t="n">
-        <v>23</v>
-      </c>
+      <c r="U297" s="2" t="inlineStr"/>
       <c r="V297" t="inlineStr"/>
       <c r="W297" s="2" t="n">
         <v>142.2</v>
@@ -23055,9 +22395,7 @@
       <c r="T298" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="U298" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="U298" s="2" t="inlineStr"/>
       <c r="V298" t="inlineStr"/>
       <c r="W298" s="2" t="n">
         <v>145.4</v>
@@ -23130,9 +22468,7 @@
       <c r="T299" s="2" t="n">
         <v>24.5</v>
       </c>
-      <c r="U299" s="2" t="n">
-        <v>23</v>
-      </c>
+      <c r="U299" s="2" t="inlineStr"/>
       <c r="V299" t="inlineStr"/>
       <c r="W299" s="2" t="n">
         <v>143.8</v>
@@ -23205,9 +22541,7 @@
       <c r="T300" s="2" t="n">
         <v>23.9</v>
       </c>
-      <c r="U300" s="3" t="n">
-        <v>27.6</v>
-      </c>
+      <c r="U300" s="2" t="inlineStr"/>
       <c r="V300" t="inlineStr"/>
       <c r="W300" s="2" t="n">
         <v>146.9</v>
@@ -23280,9 +22614,7 @@
       <c r="T301" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U301" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U301" s="2" t="inlineStr"/>
       <c r="V301" t="inlineStr"/>
       <c r="W301" s="2" t="n">
         <v>147.6</v>
@@ -23355,14 +22687,8 @@
       <c r="T302" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="U302" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="V302" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U302" s="2" t="inlineStr"/>
+      <c r="V302" t="inlineStr"/>
       <c r="W302" s="2" t="n">
         <v>148.4</v>
       </c>
@@ -23434,9 +22760,7 @@
       <c r="T303" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="U303" s="2" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U303" s="2" t="inlineStr"/>
       <c r="V303" t="inlineStr"/>
       <c r="W303" s="2" t="n">
         <v>150.4</v>
@@ -23509,9 +22833,7 @@
       <c r="T304" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U304" s="2" t="n">
-        <v>14.1</v>
-      </c>
+      <c r="U304" s="2" t="inlineStr"/>
       <c r="V304" t="inlineStr"/>
       <c r="W304" s="2" t="n">
         <v>143.3</v>
@@ -23584,9 +22906,7 @@
       <c r="T305" s="2" t="n">
         <v>19.2</v>
       </c>
-      <c r="U305" s="2" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U305" s="2" t="inlineStr"/>
       <c r="V305" t="inlineStr"/>
       <c r="W305" s="2" t="n">
         <v>144.2</v>
@@ -23659,9 +22979,7 @@
       <c r="T306" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U306" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U306" s="2" t="inlineStr"/>
       <c r="V306" t="inlineStr"/>
       <c r="W306" s="1" t="n">
         <v>156.9</v>
@@ -23734,9 +23052,7 @@
       <c r="T307" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U307" s="2" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U307" s="2" t="inlineStr"/>
       <c r="V307" t="inlineStr"/>
       <c r="W307" s="2" t="n">
         <v>149.9</v>
@@ -23809,9 +23125,7 @@
       <c r="T308" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U308" s="2" t="n">
-        <v>12.6</v>
-      </c>
+      <c r="U308" s="2" t="inlineStr"/>
       <c r="V308" t="inlineStr"/>
       <c r="W308" s="2" t="n">
         <v>139.2</v>
@@ -23884,9 +23198,7 @@
       <c r="T309" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U309" s="2" t="n">
-        <v>12</v>
-      </c>
+      <c r="U309" s="2" t="inlineStr"/>
       <c r="V309" t="inlineStr"/>
       <c r="W309" s="2" t="n">
         <v>140.7</v>
@@ -23959,9 +23271,7 @@
       <c r="T310" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U310" s="2" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="U310" s="2" t="inlineStr"/>
       <c r="V310" t="inlineStr"/>
       <c r="W310" s="2" t="n">
         <v>141.8</v>
@@ -24034,9 +23344,7 @@
       <c r="T311" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U311" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U311" s="2" t="inlineStr"/>
       <c r="V311" t="inlineStr"/>
       <c r="W311" s="2" t="n">
         <v>141.9</v>
@@ -24109,9 +23417,7 @@
       <c r="T312" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U312" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U312" s="2" t="inlineStr"/>
       <c r="V312" t="inlineStr"/>
       <c r="W312" s="2" t="n">
         <v>140.9</v>
@@ -24184,9 +23490,7 @@
       <c r="T313" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U313" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U313" s="2" t="inlineStr"/>
       <c r="V313" t="inlineStr"/>
       <c r="W313" s="2" t="n">
         <v>140.8</v>
@@ -24259,9 +23563,7 @@
       <c r="T314" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U314" s="2" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="U314" s="2" t="inlineStr"/>
       <c r="V314" t="inlineStr"/>
       <c r="W314" s="2" t="n">
         <v>139.6</v>
@@ -24334,9 +23636,7 @@
       <c r="T315" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U315" s="2" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="U315" s="2" t="inlineStr"/>
       <c r="V315" t="inlineStr"/>
       <c r="W315" s="2" t="n">
         <v>139.1</v>
@@ -24409,9 +23709,7 @@
       <c r="T316" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U316" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U316" s="2" t="inlineStr"/>
       <c r="V316" t="inlineStr"/>
       <c r="W316" s="2" t="n">
         <v>139.6</v>
@@ -24484,9 +23782,7 @@
       <c r="T317" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U317" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U317" s="2" t="inlineStr"/>
       <c r="V317" t="inlineStr"/>
       <c r="W317" s="2" t="n">
         <v>138.2</v>
@@ -24559,9 +23855,7 @@
       <c r="T318" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="U318" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U318" s="2" t="inlineStr"/>
       <c r="V318" t="inlineStr"/>
       <c r="W318" s="2" t="n">
         <v>141.9</v>
@@ -24634,9 +23928,7 @@
       <c r="T319" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U319" s="2" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U319" s="2" t="inlineStr"/>
       <c r="V319" t="inlineStr"/>
       <c r="W319" s="2" t="n">
         <v>143.3</v>
@@ -24709,9 +24001,7 @@
       <c r="T320" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U320" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U320" s="2" t="inlineStr"/>
       <c r="V320" t="inlineStr"/>
       <c r="W320" s="2" t="n">
         <v>141.4</v>
@@ -24784,9 +24074,7 @@
       <c r="T321" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="U321" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U321" s="2" t="inlineStr"/>
       <c r="V321" t="inlineStr"/>
       <c r="W321" s="2" t="n">
         <v>141.7</v>
@@ -24859,9 +24147,7 @@
       <c r="T322" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U322" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U322" s="2" t="inlineStr"/>
       <c r="V322" t="inlineStr"/>
       <c r="W322" s="2" t="n">
         <v>138.7</v>
@@ -24934,9 +24220,7 @@
       <c r="T323" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U323" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U323" s="2" t="inlineStr"/>
       <c r="V323" t="inlineStr"/>
       <c r="W323" s="2" t="n">
         <v>135.4</v>
@@ -25009,9 +24293,7 @@
       <c r="T324" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U324" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U324" s="2" t="inlineStr"/>
       <c r="V324" t="inlineStr"/>
       <c r="W324" s="2" t="n">
         <v>136.1</v>
@@ -25084,9 +24366,7 @@
       <c r="T325" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U325" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U325" s="2" t="inlineStr"/>
       <c r="V325" t="inlineStr"/>
       <c r="W325" s="2" t="n">
         <v>138.2</v>
@@ -25159,9 +24439,7 @@
       <c r="T326" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U326" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U326" s="2" t="inlineStr"/>
       <c r="V326" t="inlineStr"/>
       <c r="W326" s="2" t="n">
         <v>140.2</v>
@@ -25234,9 +24512,7 @@
       <c r="T327" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U327" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U327" s="2" t="inlineStr"/>
       <c r="V327" t="inlineStr"/>
       <c r="W327" s="2" t="n">
         <v>139.4</v>
@@ -25309,9 +24585,7 @@
       <c r="T328" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U328" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U328" s="2" t="inlineStr"/>
       <c r="V328" t="inlineStr"/>
       <c r="W328" s="2" t="n">
         <v>141.5</v>
@@ -25384,9 +24658,7 @@
       <c r="T329" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U329" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U329" s="2" t="inlineStr"/>
       <c r="V329" t="inlineStr"/>
       <c r="W329" s="2" t="n">
         <v>139.3</v>
@@ -25459,9 +24731,7 @@
       <c r="T330" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U330" s="2" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U330" s="2" t="inlineStr"/>
       <c r="V330" t="inlineStr"/>
       <c r="W330" s="2" t="n">
         <v>145.8</v>
@@ -25534,9 +24804,7 @@
       <c r="T331" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U331" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U331" s="2" t="inlineStr"/>
       <c r="V331" t="inlineStr"/>
       <c r="W331" s="2" t="n">
         <v>138.4</v>
@@ -25609,9 +24877,7 @@
       <c r="T332" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U332" s="2" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="U332" s="2" t="inlineStr"/>
       <c r="V332" t="inlineStr"/>
       <c r="W332" s="2" t="n">
         <v>135.5</v>
@@ -25684,9 +24950,7 @@
       <c r="T333" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U333" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U333" s="2" t="inlineStr"/>
       <c r="V333" t="inlineStr"/>
       <c r="W333" s="2" t="n">
         <v>132.3</v>
@@ -25759,9 +25023,7 @@
       <c r="T334" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U334" s="2" t="n">
-        <v>14</v>
-      </c>
+      <c r="U334" s="2" t="inlineStr"/>
       <c r="V334" t="inlineStr"/>
       <c r="W334" s="2" t="n">
         <v>137</v>
@@ -25834,9 +25096,7 @@
       <c r="T335" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U335" s="2" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U335" s="2" t="inlineStr"/>
       <c r="V335" t="inlineStr"/>
       <c r="W335" s="2" t="n">
         <v>137.4</v>
@@ -25909,9 +25169,7 @@
       <c r="T336" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U336" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U336" s="2" t="inlineStr"/>
       <c r="V336" t="inlineStr"/>
       <c r="W336" s="2" t="n">
         <v>139</v>
@@ -25984,9 +25242,7 @@
       <c r="T337" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U337" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U337" s="2" t="inlineStr"/>
       <c r="V337" t="inlineStr"/>
       <c r="W337" s="2" t="n">
         <v>138.6</v>
@@ -26059,9 +25315,7 @@
       <c r="T338" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U338" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U338" s="2" t="inlineStr"/>
       <c r="V338" t="inlineStr"/>
       <c r="W338" s="2" t="n">
         <v>139.5</v>
@@ -26134,9 +25388,7 @@
       <c r="T339" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U339" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U339" s="2" t="inlineStr"/>
       <c r="V339" t="inlineStr"/>
       <c r="W339" s="2" t="n">
         <v>144.2</v>
@@ -26209,9 +25461,7 @@
       <c r="T340" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U340" s="2" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U340" s="2" t="inlineStr"/>
       <c r="V340" t="inlineStr"/>
       <c r="W340" s="2" t="n">
         <v>142.5</v>
@@ -26284,9 +25534,7 @@
       <c r="T341" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U341" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U341" s="2" t="inlineStr"/>
       <c r="V341" t="inlineStr"/>
       <c r="W341" s="2" t="n">
         <v>143.2</v>
@@ -26359,9 +25607,7 @@
       <c r="T342" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U342" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U342" s="2" t="inlineStr"/>
       <c r="V342" t="inlineStr"/>
       <c r="W342" s="2" t="n">
         <v>136.9</v>
@@ -26434,9 +25680,7 @@
       <c r="T343" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U343" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U343" s="2" t="inlineStr"/>
       <c r="V343" t="inlineStr"/>
       <c r="W343" s="2" t="n">
         <v>142.1</v>
@@ -26513,9 +25757,7 @@
       <c r="T344" s="7" t="n">
         <v>21.5</v>
       </c>
-      <c r="U344" s="6" t="n">
-        <v>28.7</v>
-      </c>
+      <c r="U344" s="7" t="inlineStr"/>
       <c r="V344" s="4" t="inlineStr"/>
       <c r="W344" s="7" t="n">
         <v>152.2</v>
@@ -26588,9 +25830,7 @@
       <c r="T345" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U345" s="2" t="n">
-        <v>16</v>
-      </c>
+      <c r="U345" s="2" t="inlineStr"/>
       <c r="V345" t="inlineStr"/>
       <c r="W345" s="2" t="n">
         <v>145</v>
@@ -26663,9 +25903,7 @@
       <c r="T346" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U346" s="2" t="n">
-        <v>20.6</v>
-      </c>
+      <c r="U346" s="2" t="inlineStr"/>
       <c r="V346" t="inlineStr"/>
       <c r="W346" s="2" t="n">
         <v>142</v>
@@ -26738,9 +25976,7 @@
       <c r="T347" s="2" t="n">
         <v>22.2</v>
       </c>
-      <c r="U347" s="2" t="n">
-        <v>23.9</v>
-      </c>
+      <c r="U347" s="2" t="inlineStr"/>
       <c r="V347" t="inlineStr"/>
       <c r="W347" s="2" t="n">
         <v>143.1</v>
@@ -26813,9 +26049,7 @@
       <c r="T348" s="2" t="n">
         <v>19.4</v>
       </c>
-      <c r="U348" s="2" t="n">
-        <v>21.1</v>
-      </c>
+      <c r="U348" s="2" t="inlineStr"/>
       <c r="V348" t="inlineStr"/>
       <c r="W348" s="2" t="n">
         <v>143</v>
@@ -26888,9 +26122,7 @@
       <c r="T349" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U349" s="2" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U349" s="2" t="inlineStr"/>
       <c r="V349" t="inlineStr"/>
       <c r="W349" s="2" t="n">
         <v>142.6</v>
@@ -26963,9 +26195,7 @@
       <c r="T350" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U350" s="2" t="n">
-        <v>12.9</v>
-      </c>
+      <c r="U350" s="2" t="inlineStr"/>
       <c r="V350" t="inlineStr"/>
       <c r="W350" s="2" t="n">
         <v>144.3</v>
@@ -27038,9 +26268,7 @@
       <c r="T351" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U351" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U351" s="2" t="inlineStr"/>
       <c r="V351" t="inlineStr"/>
       <c r="W351" s="2" t="n">
         <v>142.7</v>
@@ -27117,9 +26345,7 @@
       <c r="T352" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U352" s="2" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U352" s="2" t="inlineStr"/>
       <c r="V352" t="inlineStr"/>
       <c r="W352" s="2" t="n">
         <v>142.6</v>
@@ -27192,9 +26418,7 @@
       <c r="T353" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U353" s="2" t="n">
-        <v>15.7</v>
-      </c>
+      <c r="U353" s="2" t="inlineStr"/>
       <c r="V353" t="inlineStr"/>
       <c r="W353" s="2" t="n">
         <v>146.7</v>
@@ -27271,9 +26495,7 @@
       <c r="T354" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U354" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U354" s="2" t="inlineStr"/>
       <c r="V354" t="inlineStr"/>
       <c r="W354" s="2" t="n">
         <v>141.9</v>
@@ -27346,9 +26568,7 @@
       <c r="T355" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U355" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U355" s="2" t="inlineStr"/>
       <c r="V355" t="inlineStr"/>
       <c r="W355" s="2" t="n">
         <v>143.1</v>
@@ -27421,9 +26641,7 @@
       <c r="T356" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U356" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U356" s="2" t="inlineStr"/>
       <c r="V356" t="inlineStr"/>
       <c r="W356" s="2" t="n">
         <v>145.3</v>
@@ -27496,9 +26714,7 @@
       <c r="T357" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U357" s="2" t="n">
-        <v>16</v>
-      </c>
+      <c r="U357" s="2" t="inlineStr"/>
       <c r="V357" t="inlineStr"/>
       <c r="W357" s="2" t="n">
         <v>139.9</v>
@@ -27571,9 +26787,7 @@
       <c r="T358" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U358" s="2" t="n">
-        <v>17.6</v>
-      </c>
+      <c r="U358" s="2" t="inlineStr"/>
       <c r="V358" t="inlineStr"/>
       <c r="W358" s="2" t="n">
         <v>139.4</v>
@@ -27646,9 +26860,7 @@
       <c r="T359" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U359" s="2" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U359" s="2" t="inlineStr"/>
       <c r="V359" t="inlineStr"/>
       <c r="W359" s="2" t="n">
         <v>144.5</v>
@@ -27721,9 +26933,7 @@
       <c r="T360" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U360" s="2" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U360" s="2" t="inlineStr"/>
       <c r="V360" t="inlineStr"/>
       <c r="W360" s="2" t="n">
         <v>149.6</v>
@@ -27796,9 +27006,7 @@
       <c r="T361" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U361" s="2" t="n">
-        <v>13</v>
-      </c>
+      <c r="U361" s="2" t="inlineStr"/>
       <c r="V361" t="inlineStr"/>
       <c r="W361" s="2" t="n">
         <v>154.8</v>
@@ -27871,9 +27079,7 @@
       <c r="T362" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U362" s="2" t="n">
-        <v>13.2</v>
-      </c>
+      <c r="U362" s="2" t="inlineStr"/>
       <c r="V362" t="inlineStr"/>
       <c r="W362" s="2" t="n">
         <v>150</v>
@@ -27946,9 +27152,7 @@
       <c r="T363" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U363" s="2" t="n">
-        <v>8.699999999999999</v>
-      </c>
+      <c r="U363" s="2" t="inlineStr"/>
       <c r="V363" t="inlineStr"/>
       <c r="W363" s="2" t="n">
         <v>145.4</v>
@@ -28021,9 +27225,7 @@
       <c r="T364" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U364" s="2" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U364" s="2" t="inlineStr"/>
       <c r="V364" t="inlineStr"/>
       <c r="W364" s="2" t="n">
         <v>145.7</v>
@@ -28096,9 +27298,7 @@
       <c r="T365" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U365" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U365" s="2" t="inlineStr"/>
       <c r="V365" t="inlineStr"/>
       <c r="W365" s="2" t="n">
         <v>149.8</v>
@@ -28171,9 +27371,7 @@
       <c r="T366" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U366" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U366" s="2" t="inlineStr"/>
       <c r="V366" t="inlineStr"/>
       <c r="W366" s="2" t="n">
         <v>144.7</v>
@@ -28246,9 +27444,7 @@
       <c r="T367" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U367" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U367" s="2" t="inlineStr"/>
       <c r="V367" t="inlineStr"/>
       <c r="W367" s="2" t="n">
         <v>144.3</v>
@@ -28321,9 +27517,7 @@
       <c r="T368" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U368" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U368" s="2" t="inlineStr"/>
       <c r="V368" t="inlineStr"/>
       <c r="W368" s="2" t="n">
         <v>145.7</v>
@@ -28396,9 +27590,7 @@
       <c r="T369" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U369" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U369" s="2" t="inlineStr"/>
       <c r="V369" t="inlineStr"/>
       <c r="W369" s="2" t="n">
         <v>145.1</v>
@@ -28471,9 +27663,7 @@
       <c r="T370" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U370" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U370" s="2" t="inlineStr"/>
       <c r="V370" t="inlineStr"/>
       <c r="W370" s="2" t="n">
         <v>148.5</v>
@@ -28546,9 +27736,7 @@
       <c r="T371" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U371" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U371" s="2" t="inlineStr"/>
       <c r="V371" t="inlineStr"/>
       <c r="W371" s="2" t="n">
         <v>145.7</v>
@@ -28625,9 +27813,7 @@
       <c r="T372" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="U372" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U372" s="2" t="inlineStr"/>
       <c r="V372" t="inlineStr"/>
       <c r="W372" s="2" t="n">
         <v>147.3</v>
@@ -31594,31 +30780,31 @@
         <v>7572.69</v>
       </c>
       <c r="F413" t="n">
-        <v>7583.51</v>
+        <v>7585.73</v>
       </c>
       <c r="G413" t="n">
-        <v>1416902000</v>
+        <v>2810532000</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>-0.48</v>
+        <v>-0.45</v>
       </c>
       <c r="I413" t="n">
         <v>2</v>
       </c>
       <c r="J413" t="n">
-        <v>7668.82</v>
+        <v>7668.93</v>
       </c>
       <c r="K413" t="n">
-        <v>7581.69</v>
+        <v>7581.73</v>
       </c>
       <c r="L413" t="n">
-        <v>7384.69</v>
+        <v>7384.71</v>
       </c>
       <c r="M413" t="n">
-        <v>7171.21</v>
+        <v>7171.23</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>41.74</v>
+        <v>41.9</v>
       </c>
       <c r="O413" t="n">
         <v>29</v>
@@ -31635,16 +30821,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>17.6</v>
+        <v>17.2</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>14.8</v>
+        <v>17.1</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>146.6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -30710,7 +30710,7 @@
         <v>7585.73</v>
       </c>
       <c r="G412" t="n">
-        <v>2810532000</v>
+        <v>5154930000</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>-0.45</v>
@@ -30734,7 +30734,7 @@
         <v>41.9</v>
       </c>
       <c r="O412" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -30753,13 +30753,84 @@
       <c r="T412" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U412" s="2" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U412" s="2" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="n">
         <v>146.6</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>7601.25</v>
+      </c>
+      <c r="D413" t="n">
+        <v>7626.79</v>
+      </c>
+      <c r="E413" t="n">
+        <v>7597.61</v>
+      </c>
+      <c r="F413" t="n">
+        <v>7611.6</v>
+      </c>
+      <c r="G413" t="n">
+        <v>929674082</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2</v>
+      </c>
+      <c r="J413" t="n">
+        <v>7664.92</v>
+      </c>
+      <c r="K413" t="n">
+        <v>7584.04</v>
+      </c>
+      <c r="L413" t="n">
+        <v>7393.21</v>
+      </c>
+      <c r="M413" t="n">
+        <v>7175.22</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>44.56</v>
+      </c>
+      <c r="O413" t="n">
+        <v>29</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -30777,37 +30777,37 @@
         <v>7626.79</v>
       </c>
       <c r="E413" t="n">
-        <v>7597.61</v>
+        <v>7507.77</v>
       </c>
       <c r="F413" t="n">
-        <v>7611.6</v>
+        <v>7547.03</v>
       </c>
       <c r="G413" t="n">
-        <v>929674082</v>
-      </c>
-      <c r="H413" s="3" t="n">
-        <v>0.34</v>
+        <v>2032838000</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-0.51</v>
       </c>
       <c r="I413" t="n">
         <v>2</v>
       </c>
       <c r="J413" t="n">
-        <v>7664.92</v>
+        <v>7661.7</v>
       </c>
       <c r="K413" t="n">
-        <v>7584.04</v>
+        <v>7582.97</v>
       </c>
       <c r="L413" t="n">
-        <v>7393.21</v>
+        <v>7392.67</v>
       </c>
       <c r="M413" t="n">
-        <v>7175.22</v>
+        <v>7174.9</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>44.56</v>
+        <v>39.32</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -30819,15 +30819,19 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R413" t="inlineStr"/>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>2nd: MA60, 50% cash, 5d</t>
+        </is>
+      </c>
       <c r="S413" t="n">
-        <v>4.96</v>
+        <v>5.01</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>16.8</v>
+        <v>18.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>16.2</v>
+        <v>18</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -11197,7 +11197,7 @@
         <v>6219.75</v>
       </c>
       <c r="L146" t="n">
-        <v>5913.86</v>
+        <v>5913.87</v>
       </c>
       <c r="M146" t="n">
         <v>5944.69</v>
@@ -29685,7 +29685,7 @@
         <v>2</v>
       </c>
       <c r="J398" t="n">
-        <v>7668.83</v>
+        <v>7668.84</v>
       </c>
       <c r="K398" t="n">
         <v>7536.22</v>
@@ -29838,7 +29838,7 @@
         <v>7701.48</v>
       </c>
       <c r="K400" t="n">
-        <v>7539.51</v>
+        <v>7539.5</v>
       </c>
       <c r="L400" t="n">
         <v>7284.89</v>
@@ -30780,31 +30780,31 @@
         <v>7507.77</v>
       </c>
       <c r="F413" t="n">
-        <v>7547.03</v>
+        <v>7551.81</v>
       </c>
       <c r="G413" t="n">
-        <v>2032838000</v>
+        <v>2901247000</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>-0.51</v>
+        <v>-0.45</v>
       </c>
       <c r="I413" t="n">
         <v>2</v>
       </c>
       <c r="J413" t="n">
-        <v>7661.7</v>
+        <v>7661.94</v>
       </c>
       <c r="K413" t="n">
-        <v>7582.97</v>
+        <v>7583.04</v>
       </c>
       <c r="L413" t="n">
-        <v>7392.67</v>
+        <v>7392.71</v>
       </c>
       <c r="M413" t="n">
-        <v>7174.9</v>
+        <v>7174.92</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>39.32</v>
+        <v>39.63</v>
       </c>
       <c r="O413" t="n">
         <v>26</v>
@@ -30828,13 +30828,15 @@
         <v>5.01</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>18.1</v>
+        <v>17.7</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>145.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -30783,7 +30783,7 @@
         <v>7551.81</v>
       </c>
       <c r="G413" t="n">
-        <v>2901247000</v>
+        <v>5307920000</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-0.45</v>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -30807,7 +30807,7 @@
         <v>39.63</v>
       </c>
       <c r="O413" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -30830,13 +30830,84 @@
       <c r="T413" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U413" s="2" t="n">
-        <v>17</v>
-      </c>
+      <c r="U413" s="2" t="inlineStr"/>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="n">
         <v>145.9</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>7631.44</v>
+      </c>
+      <c r="D414" t="n">
+        <v>7646.6</v>
+      </c>
+      <c r="E414" t="n">
+        <v>7611.81</v>
+      </c>
+      <c r="F414" t="n">
+        <v>7637.66</v>
+      </c>
+      <c r="G414" t="n">
+        <v>1451915000</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>7658.42</v>
+      </c>
+      <c r="K414" t="n">
+        <v>7587.58</v>
+      </c>
+      <c r="L414" t="n">
+        <v>7402.38</v>
+      </c>
+      <c r="M414" t="n">
+        <v>7178.86</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="O414" t="n">
+        <v>29</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -30851,16 +30851,16 @@
         <v>7631.44</v>
       </c>
       <c r="D414" t="n">
-        <v>7646.6</v>
+        <v>7646.86</v>
       </c>
       <c r="E414" t="n">
         <v>7611.81</v>
       </c>
       <c r="F414" t="n">
-        <v>7637.66</v>
+        <v>7637.76</v>
       </c>
       <c r="G414" t="n">
-        <v>1451915000</v>
+        <v>2887250000</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>1.14</v>
@@ -30881,7 +30881,7 @@
         <v>7178.86</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>42.57</v>
+        <v>42.58</v>
       </c>
       <c r="O414" t="n">
         <v>29</v>
@@ -30901,13 +30901,15 @@
         <v>4.95</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.7</v>
+        <v>13.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>145.7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -30860,7 +30860,7 @@
         <v>7637.76</v>
       </c>
       <c r="G414" t="n">
-        <v>2887250000</v>
+        <v>5058210000</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>1.14</v>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -30884,7 +30884,7 @@
         <v>42.58</v>
       </c>
       <c r="O414" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -30903,13 +30903,84 @@
       <c r="T414" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U414" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U414" s="2" t="inlineStr"/>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="n">
         <v>145.7</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>7657.17</v>
+      </c>
+      <c r="D415" t="n">
+        <v>7657.17</v>
+      </c>
+      <c r="E415" t="n">
+        <v>7619.74</v>
+      </c>
+      <c r="F415" t="n">
+        <v>7628.49</v>
+      </c>
+      <c r="G415" t="n">
+        <v>713236445</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="I415" t="n">
+        <v>2</v>
+      </c>
+      <c r="J415" t="n">
+        <v>7657.79</v>
+      </c>
+      <c r="K415" t="n">
+        <v>7592.09</v>
+      </c>
+      <c r="L415" t="n">
+        <v>7412.88</v>
+      </c>
+      <c r="M415" t="n">
+        <v>7182.94</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>43.27</v>
+      </c>
+      <c r="O415" t="n">
+        <v>29</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -645,7 +645,9 @@
       <c r="T2" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" s="1" t="n">
         <v>168.6</v>
@@ -718,7 +720,9 @@
       <c r="T3" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="n">
+        <v>13.5</v>
+      </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" s="1" t="n">
         <v>163.6</v>
@@ -791,7 +795,9 @@
       <c r="T4" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="1" t="n">
         <v>157.4</v>
@@ -864,7 +870,9 @@
       <c r="T5" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="1" t="n">
         <v>156.7</v>
@@ -937,7 +945,9 @@
       <c r="T6" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="1" t="n">
         <v>158.5</v>
@@ -1010,7 +1020,9 @@
       <c r="T7" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="1" t="n">
         <v>155.4</v>
@@ -1083,7 +1095,9 @@
       <c r="T8" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="1" t="n">
         <v>159.4</v>
@@ -1156,7 +1170,9 @@
       <c r="T9" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="1" t="n">
         <v>162.6</v>
@@ -1229,7 +1245,9 @@
       <c r="T10" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" s="1" t="n">
         <v>163.6</v>
@@ -1302,7 +1320,9 @@
       <c r="T11" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" s="1" t="n">
         <v>166.5</v>
@@ -1375,7 +1395,9 @@
       <c r="T12" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" s="1" t="n">
         <v>166.9</v>
@@ -1448,7 +1470,9 @@
       <c r="T13" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" s="1" t="n">
         <v>168.8</v>
@@ -1521,7 +1545,9 @@
       <c r="T14" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="n">
+        <v>12.8</v>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" s="1" t="n">
         <v>166.1</v>
@@ -1594,7 +1620,9 @@
       <c r="T15" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="n">
+        <v>11</v>
+      </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" s="1" t="n">
         <v>163.4</v>
@@ -1667,7 +1695,9 @@
       <c r="T16" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" s="1" t="n">
         <v>168</v>
@@ -1740,7 +1770,9 @@
       <c r="T17" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" s="1" t="n">
         <v>183.1</v>
@@ -1813,7 +1845,9 @@
       <c r="T18" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" s="1" t="n">
         <v>175.8</v>
@@ -1886,7 +1920,9 @@
       <c r="T19" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" s="1" t="n">
         <v>178.6</v>
@@ -1963,7 +1999,9 @@
       <c r="T20" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" s="1" t="n">
         <v>165</v>
@@ -2036,7 +2074,9 @@
       <c r="T21" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" s="1" t="n">
         <v>156.9</v>
@@ -2109,7 +2149,9 @@
       <c r="T22" s="2" t="n">
         <v>19.4</v>
       </c>
-      <c r="U22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" s="1" t="n">
         <v>157.6</v>
@@ -2182,7 +2224,9 @@
       <c r="T23" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="n">
+        <v>20.5</v>
+      </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" s="2" t="n">
         <v>153.4</v>
@@ -2259,7 +2303,9 @@
       <c r="T24" s="2" t="n">
         <v>21.1</v>
       </c>
-      <c r="U24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V24" t="inlineStr"/>
       <c r="W24" s="2" t="n">
         <v>149.3</v>
@@ -2332,7 +2378,9 @@
       <c r="T25" s="2" t="n">
         <v>19.6</v>
       </c>
-      <c r="U25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="n">
+        <v>18.7</v>
+      </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" s="1" t="n">
         <v>157.9</v>
@@ -2409,7 +2457,9 @@
       <c r="T26" s="2" t="n">
         <v>22.8</v>
       </c>
-      <c r="U26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="n">
+        <v>21.8</v>
+      </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" s="2" t="n">
         <v>154.3</v>
@@ -2482,7 +2532,9 @@
       <c r="T27" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="n">
+        <v>24.6</v>
+      </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" s="2" t="n">
         <v>151.4</v>
@@ -2555,7 +2607,9 @@
       <c r="T28" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="U28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" s="2" t="n">
         <v>138.9</v>
@@ -2628,7 +2682,9 @@
       <c r="T29" s="2" t="n">
         <v>24.9</v>
       </c>
-      <c r="U29" s="2" t="inlineStr"/>
+      <c r="U29" s="3" t="n">
+        <v>31.1</v>
+      </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" s="2" t="n">
         <v>137.6</v>
@@ -2701,7 +2757,9 @@
       <c r="T30" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="n">
+        <v>24.7</v>
+      </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" s="2" t="n">
         <v>139.9</v>
@@ -2778,8 +2836,14 @@
       <c r="T31" s="6" t="n">
         <v>27.9</v>
       </c>
-      <c r="U31" s="7" t="inlineStr"/>
-      <c r="V31" s="4" t="inlineStr"/>
+      <c r="U31" s="6" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="V31" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W31" s="7" t="n">
         <v>146</v>
       </c>
@@ -2855,8 +2919,14 @@
       <c r="T32" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="U32" s="2" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="U32" s="3" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W32" s="2" t="n">
         <v>132.8</v>
       </c>
@@ -2932,7 +3002,9 @@
       <c r="T33" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="n">
+        <v>23.2</v>
+      </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" s="2" t="n">
         <v>128.7</v>
@@ -3009,7 +3081,9 @@
       <c r="T34" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="n">
+        <v>23.4</v>
+      </c>
       <c r="V34" t="inlineStr"/>
       <c r="W34" s="2" t="n">
         <v>128.9</v>
@@ -3082,7 +3156,9 @@
       <c r="T35" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="n">
+        <v>21.4</v>
+      </c>
       <c r="V35" t="inlineStr"/>
       <c r="W35" s="2" t="n">
         <v>130.3</v>
@@ -3155,7 +3231,9 @@
       <c r="T36" s="2" t="n">
         <v>20.5</v>
       </c>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="n">
+        <v>16.4</v>
+      </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" s="2" t="n">
         <v>133.9</v>
@@ -3228,7 +3306,9 @@
       <c r="T37" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="U37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" s="2" t="n">
         <v>136.8</v>
@@ -3301,7 +3381,9 @@
       <c r="T38" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="n">
+        <v>18.5</v>
+      </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" s="2" t="n">
         <v>136.4</v>
@@ -3374,7 +3456,9 @@
       <c r="T39" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="n">
+        <v>18.6</v>
+      </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" s="2" t="n">
         <v>140.8</v>
@@ -3447,7 +3531,9 @@
       <c r="T40" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V40" t="inlineStr"/>
       <c r="W40" s="2" t="n">
         <v>141.7</v>
@@ -3520,7 +3606,9 @@
       <c r="T41" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="n">
+        <v>13</v>
+      </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" s="2" t="n">
         <v>144</v>
@@ -3593,7 +3681,9 @@
       <c r="T42" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V42" t="inlineStr"/>
       <c r="W42" s="2" t="n">
         <v>148.7</v>
@@ -3670,7 +3760,9 @@
       <c r="T43" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V43" t="inlineStr"/>
       <c r="W43" s="2" t="n">
         <v>144.8</v>
@@ -3743,7 +3835,9 @@
       <c r="T44" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" s="2" t="n">
         <v>140.9</v>
@@ -3816,7 +3910,9 @@
       <c r="T45" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="U45" s="2" t="inlineStr"/>
+      <c r="U45" s="3" t="n">
+        <v>25.4</v>
+      </c>
       <c r="V45" t="inlineStr"/>
       <c r="W45" s="2" t="n">
         <v>139</v>
@@ -3889,7 +3985,9 @@
       <c r="T46" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="U46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="n">
+        <v>21.8</v>
+      </c>
       <c r="V46" t="inlineStr"/>
       <c r="W46" s="2" t="n">
         <v>148.6</v>
@@ -3962,7 +4060,9 @@
       <c r="T47" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="n">
+        <v>20.1</v>
+      </c>
       <c r="V47" t="inlineStr"/>
       <c r="W47" s="2" t="n">
         <v>143</v>
@@ -4035,7 +4135,9 @@
       <c r="T48" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="U48" s="2" t="inlineStr"/>
+      <c r="U48" s="3" t="n">
+        <v>26.7</v>
+      </c>
       <c r="V48" t="inlineStr"/>
       <c r="W48" s="2" t="n">
         <v>144.3</v>
@@ -4112,8 +4214,14 @@
       <c r="T49" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="U49" s="7" t="inlineStr"/>
-      <c r="V49" s="4" t="inlineStr"/>
+      <c r="U49" s="6" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="V49" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W49" s="7" t="n">
         <v>139.2</v>
       </c>
@@ -4189,8 +4297,14 @@
       <c r="T50" s="6" t="n">
         <v>45.3</v>
       </c>
-      <c r="U50" s="7" t="inlineStr"/>
-      <c r="V50" s="4" t="inlineStr"/>
+      <c r="U50" s="6" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="V50" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W50" s="7" t="n">
         <v>136.5</v>
       </c>
@@ -4266,8 +4380,14 @@
       <c r="T51" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="U51" s="2" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
+      <c r="U51" s="3" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W51" s="2" t="n">
         <v>133.8</v>
       </c>
@@ -4343,8 +4463,14 @@
       <c r="T52" s="3" t="n">
         <v>52.3</v>
       </c>
-      <c r="U52" s="2" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+      <c r="U52" s="3" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W52" s="2" t="n">
         <v>135.7</v>
       </c>
@@ -4416,8 +4542,14 @@
       <c r="T53" s="3" t="n">
         <v>33.6</v>
       </c>
-      <c r="U53" s="2" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
+      <c r="U53" s="3" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W53" s="2" t="n">
         <v>142.2</v>
       </c>
@@ -4489,8 +4621,14 @@
       <c r="T54" s="6" t="n">
         <v>40.7</v>
       </c>
-      <c r="U54" s="7" t="inlineStr"/>
-      <c r="V54" s="4" t="inlineStr"/>
+      <c r="U54" s="6" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="V54" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W54" s="7" t="n">
         <v>127.5</v>
       </c>
@@ -4562,8 +4700,14 @@
       <c r="T55" s="3" t="n">
         <v>37.6</v>
       </c>
-      <c r="U55" s="2" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
+      <c r="U55" s="3" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W55" s="2" t="n">
         <v>128.6</v>
       </c>
@@ -4635,7 +4779,9 @@
       <c r="T56" s="3" t="n">
         <v>30.9</v>
       </c>
-      <c r="U56" s="2" t="inlineStr"/>
+      <c r="U56" s="3" t="n">
+        <v>28.5</v>
+      </c>
       <c r="V56" t="inlineStr"/>
       <c r="W56" s="2" t="n">
         <v>135.7</v>
@@ -4708,7 +4854,9 @@
       <c r="T57" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="U57" s="2" t="inlineStr"/>
+      <c r="U57" s="3" t="n">
+        <v>26</v>
+      </c>
       <c r="V57" t="inlineStr"/>
       <c r="W57" s="2" t="n">
         <v>135.8</v>
@@ -4781,8 +4929,14 @@
       <c r="T58" s="6" t="n">
         <v>32.6</v>
       </c>
-      <c r="U58" s="7" t="inlineStr"/>
-      <c r="V58" s="4" t="inlineStr"/>
+      <c r="U58" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="V58" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W58" s="7" t="n">
         <v>131.3</v>
       </c>
@@ -4854,8 +5008,14 @@
       <c r="T59" s="3" t="n">
         <v>29.6</v>
       </c>
-      <c r="U59" s="2" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
+      <c r="U59" s="3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W59" s="2" t="n">
         <v>130</v>
       </c>
@@ -4927,7 +5087,9 @@
       <c r="T60" s="6" t="n">
         <v>33.8</v>
       </c>
-      <c r="U60" s="7" t="inlineStr"/>
+      <c r="U60" s="6" t="n">
+        <v>30.6</v>
+      </c>
       <c r="V60" s="4" t="inlineStr"/>
       <c r="W60" s="6" t="n">
         <v>125.8</v>
@@ -5000,7 +5162,9 @@
       <c r="T61" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="U61" s="2" t="inlineStr"/>
+      <c r="U61" s="3" t="n">
+        <v>29.1</v>
+      </c>
       <c r="V61" t="inlineStr"/>
       <c r="W61" s="3" t="n">
         <v>125.9</v>
@@ -5073,8 +5237,14 @@
       <c r="T62" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="U62" s="2" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
+      <c r="U62" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="V62" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W62" s="3" t="n">
         <v>126.7</v>
       </c>
@@ -5146,7 +5316,9 @@
       <c r="T63" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="U63" s="2" t="inlineStr"/>
+      <c r="U63" s="3" t="n">
+        <v>25.7</v>
+      </c>
       <c r="V63" t="inlineStr"/>
       <c r="W63" s="2" t="n">
         <v>129</v>
@@ -5219,7 +5391,9 @@
       <c r="T64" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="U64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="n">
+        <v>23.6</v>
+      </c>
       <c r="V64" t="inlineStr"/>
       <c r="W64" s="2" t="n">
         <v>132.4</v>
@@ -5292,7 +5466,9 @@
       <c r="T65" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="U65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="n">
+        <v>21.4</v>
+      </c>
       <c r="V65" t="inlineStr"/>
       <c r="W65" s="2" t="n">
         <v>131.3</v>
@@ -5365,7 +5541,9 @@
       <c r="T66" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V66" t="inlineStr"/>
       <c r="W66" s="2" t="n">
         <v>134.3</v>
@@ -5438,7 +5616,9 @@
       <c r="T67" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="n">
+        <v>22.9</v>
+      </c>
       <c r="V67" t="inlineStr"/>
       <c r="W67" s="2" t="n">
         <v>132.7</v>
@@ -5511,7 +5691,9 @@
       <c r="T68" s="2" t="n">
         <v>24.6</v>
       </c>
-      <c r="U68" s="2" t="inlineStr"/>
+      <c r="U68" s="3" t="n">
+        <v>27.5</v>
+      </c>
       <c r="V68" t="inlineStr"/>
       <c r="W68" s="2" t="n">
         <v>134.1</v>
@@ -5584,7 +5766,9 @@
       <c r="T69" s="2" t="n">
         <v>22.7</v>
       </c>
-      <c r="U69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="n">
+        <v>20</v>
+      </c>
       <c r="V69" t="inlineStr"/>
       <c r="W69" s="2" t="n">
         <v>134.8</v>
@@ -5661,7 +5845,9 @@
       <c r="T70" s="2" t="n">
         <v>23.6</v>
       </c>
-      <c r="U70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V70" t="inlineStr"/>
       <c r="W70" s="2" t="n">
         <v>134.1</v>
@@ -5734,7 +5920,9 @@
       <c r="T71" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="U71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="n">
+        <v>22.2</v>
+      </c>
       <c r="V71" t="inlineStr"/>
       <c r="W71" s="2" t="n">
         <v>133.2</v>
@@ -5807,7 +5995,9 @@
       <c r="T72" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="n">
+        <v>19.8</v>
+      </c>
       <c r="V72" t="inlineStr"/>
       <c r="W72" s="2" t="n">
         <v>132.2</v>
@@ -5880,7 +6070,9 @@
       <c r="T73" s="2" t="n">
         <v>22.5</v>
       </c>
-      <c r="U73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V73" t="inlineStr"/>
       <c r="W73" s="2" t="n">
         <v>131.5</v>
@@ -5953,7 +6145,9 @@
       <c r="T74" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="U74" s="2" t="inlineStr"/>
+      <c r="U74" s="3" t="n">
+        <v>26.9</v>
+      </c>
       <c r="V74" t="inlineStr"/>
       <c r="W74" s="2" t="n">
         <v>128.4</v>
@@ -6026,7 +6220,9 @@
       <c r="T75" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="n">
+        <v>18.7</v>
+      </c>
       <c r="V75" t="inlineStr"/>
       <c r="W75" s="2" t="n">
         <v>137.7</v>
@@ -6099,7 +6295,9 @@
       <c r="T76" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="n">
+        <v>15.4</v>
+      </c>
       <c r="V76" t="inlineStr"/>
       <c r="W76" s="2" t="n">
         <v>140.5</v>
@@ -6172,7 +6370,9 @@
       <c r="T77" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V77" t="inlineStr"/>
       <c r="W77" s="2" t="n">
         <v>138.9</v>
@@ -6245,7 +6445,9 @@
       <c r="T78" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V78" t="inlineStr"/>
       <c r="W78" s="2" t="n">
         <v>140.9</v>
@@ -6318,7 +6520,9 @@
       <c r="T79" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" s="2" t="n">
         <v>136</v>
@@ -6391,7 +6595,9 @@
       <c r="T80" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="n">
+        <v>13.5</v>
+      </c>
       <c r="V80" t="inlineStr"/>
       <c r="W80" s="2" t="n">
         <v>135.9</v>
@@ -6464,7 +6670,9 @@
       <c r="T81" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V81" t="inlineStr"/>
       <c r="W81" s="2" t="n">
         <v>137.3</v>
@@ -6537,7 +6745,9 @@
       <c r="T82" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="U82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" s="2" t="n">
         <v>137.3</v>
@@ -6610,7 +6820,9 @@
       <c r="T83" s="2" t="n">
         <v>20.3</v>
       </c>
-      <c r="U83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V83" t="inlineStr"/>
       <c r="W83" s="2" t="n">
         <v>139</v>
@@ -6687,7 +6899,9 @@
       <c r="T84" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="U84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="n">
+        <v>21.7</v>
+      </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" s="2" t="n">
         <v>139.3</v>
@@ -6760,7 +6974,9 @@
       <c r="T85" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" s="2" t="n">
         <v>140.9</v>
@@ -6833,7 +7049,9 @@
       <c r="T86" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" s="2" t="n">
         <v>137.6</v>
@@ -6906,7 +7124,9 @@
       <c r="T87" s="2" t="n">
         <v>19.2</v>
       </c>
-      <c r="U87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" s="2" t="n">
         <v>137.3</v>
@@ -6979,7 +7199,9 @@
       <c r="T88" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="n">
+        <v>17</v>
+      </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" s="2" t="n">
         <v>138.2</v>
@@ -7052,7 +7274,9 @@
       <c r="T89" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="n">
+        <v>13.3</v>
+      </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" s="2" t="n">
         <v>141</v>
@@ -7125,7 +7349,9 @@
       <c r="T90" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" s="2" t="n">
         <v>141.6</v>
@@ -7198,7 +7424,9 @@
       <c r="T91" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V91" t="inlineStr"/>
       <c r="W91" s="2" t="n">
         <v>137.5</v>
@@ -7271,7 +7499,9 @@
       <c r="T92" s="2" t="n">
         <v>18.5</v>
       </c>
-      <c r="U92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="V92" t="inlineStr"/>
       <c r="W92" s="2" t="n">
         <v>140.1</v>
@@ -7344,7 +7574,9 @@
       <c r="T93" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="n">
+        <v>14.3</v>
+      </c>
       <c r="V93" t="inlineStr"/>
       <c r="W93" s="2" t="n">
         <v>138.9</v>
@@ -7417,7 +7649,9 @@
       <c r="T94" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V94" t="inlineStr"/>
       <c r="W94" s="2" t="n">
         <v>139.2</v>
@@ -7490,7 +7724,9 @@
       <c r="T95" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V95" t="inlineStr"/>
       <c r="W95" s="2" t="n">
         <v>141.2</v>
@@ -7563,7 +7799,9 @@
       <c r="T96" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="n">
+        <v>13.9</v>
+      </c>
       <c r="V96" t="inlineStr"/>
       <c r="W96" s="2" t="n">
         <v>141.4</v>
@@ -7636,7 +7874,9 @@
       <c r="T97" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V97" t="inlineStr"/>
       <c r="W97" s="2" t="n">
         <v>145.6</v>
@@ -7709,7 +7949,9 @@
       <c r="T98" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="n">
+        <v>21.7</v>
+      </c>
       <c r="V98" t="inlineStr"/>
       <c r="W98" s="2" t="n">
         <v>149.6</v>
@@ -7782,7 +8024,9 @@
       <c r="T99" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V99" t="inlineStr"/>
       <c r="W99" s="1" t="n">
         <v>156.6</v>
@@ -7855,7 +8099,9 @@
       <c r="T100" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="U100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="n">
+        <v>21</v>
+      </c>
       <c r="V100" t="inlineStr"/>
       <c r="W100" s="2" t="n">
         <v>154.4</v>
@@ -7928,7 +8174,9 @@
       <c r="T101" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="U101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V101" t="inlineStr"/>
       <c r="W101" s="2" t="n">
         <v>148.4</v>
@@ -8001,7 +8249,9 @@
       <c r="T102" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="n">
+        <v>18.4</v>
+      </c>
       <c r="V102" t="inlineStr"/>
       <c r="W102" s="2" t="n">
         <v>149.2</v>
@@ -8074,7 +8324,9 @@
       <c r="T103" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V103" t="inlineStr"/>
       <c r="W103" s="2" t="n">
         <v>154.8</v>
@@ -8147,7 +8399,9 @@
       <c r="T104" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V104" t="inlineStr"/>
       <c r="W104" s="1" t="n">
         <v>155</v>
@@ -8220,7 +8474,9 @@
       <c r="T105" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V105" t="inlineStr"/>
       <c r="W105" s="2" t="n">
         <v>152.2</v>
@@ -8293,7 +8549,9 @@
       <c r="T106" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V106" t="inlineStr"/>
       <c r="W106" s="2" t="n">
         <v>147.5</v>
@@ -8366,7 +8624,9 @@
       <c r="T107" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V107" t="inlineStr"/>
       <c r="W107" s="2" t="n">
         <v>143.4</v>
@@ -8439,7 +8699,9 @@
       <c r="T108" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V108" t="inlineStr"/>
       <c r="W108" s="2" t="n">
         <v>139.6</v>
@@ -8512,7 +8774,9 @@
       <c r="T109" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="V109" t="inlineStr"/>
       <c r="W109" s="2" t="n">
         <v>140.1</v>
@@ -8585,7 +8849,9 @@
       <c r="T110" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V110" t="inlineStr"/>
       <c r="W110" s="2" t="n">
         <v>139.3</v>
@@ -8658,7 +8924,9 @@
       <c r="T111" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U111" s="2" t="inlineStr"/>
+      <c r="U111" s="2" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V111" t="inlineStr"/>
       <c r="W111" s="2" t="n">
         <v>141.4</v>
@@ -8731,7 +8999,9 @@
       <c r="T112" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U112" s="2" t="inlineStr"/>
+      <c r="U112" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V112" t="inlineStr"/>
       <c r="W112" s="2" t="n">
         <v>138</v>
@@ -8804,7 +9074,9 @@
       <c r="T113" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U113" s="2" t="inlineStr"/>
+      <c r="U113" s="2" t="n">
+        <v>10.5</v>
+      </c>
       <c r="V113" t="inlineStr"/>
       <c r="W113" s="2" t="n">
         <v>140.8</v>
@@ -8877,7 +9149,9 @@
       <c r="T114" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U114" s="2" t="inlineStr"/>
+      <c r="U114" s="2" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V114" t="inlineStr"/>
       <c r="W114" s="2" t="n">
         <v>141.8</v>
@@ -8950,7 +9224,9 @@
       <c r="T115" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U115" s="2" t="inlineStr"/>
+      <c r="U115" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V115" t="inlineStr"/>
       <c r="W115" s="2" t="n">
         <v>143.3</v>
@@ -9023,7 +9299,9 @@
       <c r="T116" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U116" s="2" t="inlineStr"/>
+      <c r="U116" s="2" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V116" t="inlineStr"/>
       <c r="W116" s="2" t="n">
         <v>145</v>
@@ -9096,7 +9374,9 @@
       <c r="T117" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U117" s="2" t="inlineStr"/>
+      <c r="U117" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V117" t="inlineStr"/>
       <c r="W117" s="2" t="n">
         <v>147</v>
@@ -9169,7 +9449,9 @@
       <c r="T118" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U118" s="2" t="inlineStr"/>
+      <c r="U118" s="2" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V118" t="inlineStr"/>
       <c r="W118" s="2" t="n">
         <v>143.7</v>
@@ -9242,7 +9524,9 @@
       <c r="T119" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U119" s="2" t="inlineStr"/>
+      <c r="U119" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V119" t="inlineStr"/>
       <c r="W119" s="2" t="n">
         <v>146.7</v>
@@ -9315,7 +9599,9 @@
       <c r="T120" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U120" s="2" t="inlineStr"/>
+      <c r="U120" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V120" t="inlineStr"/>
       <c r="W120" s="2" t="n">
         <v>151.1</v>
@@ -9388,7 +9674,9 @@
       <c r="T121" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U121" s="2" t="inlineStr"/>
+      <c r="U121" s="2" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V121" t="inlineStr"/>
       <c r="W121" s="2" t="n">
         <v>150.4</v>
@@ -9461,7 +9749,9 @@
       <c r="T122" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U122" s="2" t="inlineStr"/>
+      <c r="U122" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V122" t="inlineStr"/>
       <c r="W122" s="2" t="n">
         <v>154.8</v>
@@ -9534,7 +9824,9 @@
       <c r="T123" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U123" s="2" t="inlineStr"/>
+      <c r="U123" s="2" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V123" t="inlineStr"/>
       <c r="W123" s="2" t="n">
         <v>153.4</v>
@@ -9607,7 +9899,9 @@
       <c r="T124" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U124" s="2" t="inlineStr"/>
+      <c r="U124" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V124" t="inlineStr"/>
       <c r="W124" s="1" t="n">
         <v>159.3</v>
@@ -9680,7 +9974,9 @@
       <c r="T125" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U125" s="2" t="inlineStr"/>
+      <c r="U125" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V125" t="inlineStr"/>
       <c r="W125" s="1" t="n">
         <v>159.4</v>
@@ -9753,7 +10049,9 @@
       <c r="T126" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U126" s="2" t="inlineStr"/>
+      <c r="U126" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V126" t="inlineStr"/>
       <c r="W126" s="2" t="n">
         <v>145.6</v>
@@ -9826,7 +10124,9 @@
       <c r="T127" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U127" s="2" t="inlineStr"/>
+      <c r="U127" s="2" t="n">
+        <v>7.9</v>
+      </c>
       <c r="V127" t="inlineStr"/>
       <c r="W127" s="2" t="n">
         <v>147.6</v>
@@ -9899,7 +10199,9 @@
       <c r="T128" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U128" s="2" t="inlineStr"/>
+      <c r="U128" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V128" t="inlineStr"/>
       <c r="W128" s="2" t="n">
         <v>149.1</v>
@@ -9972,7 +10274,9 @@
       <c r="T129" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U129" s="2" t="inlineStr"/>
+      <c r="U129" s="2" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V129" t="inlineStr"/>
       <c r="W129" s="2" t="n">
         <v>154.1</v>
@@ -10045,7 +10349,9 @@
       <c r="T130" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U130" s="2" t="inlineStr"/>
+      <c r="U130" s="2" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V130" t="inlineStr"/>
       <c r="W130" s="2" t="n">
         <v>152.3</v>
@@ -10122,7 +10428,9 @@
       <c r="T131" s="2" t="n">
         <v>20.4</v>
       </c>
-      <c r="U131" s="2" t="inlineStr"/>
+      <c r="U131" s="2" t="n">
+        <v>20</v>
+      </c>
       <c r="V131" t="inlineStr"/>
       <c r="W131" s="1" t="n">
         <v>155.5</v>
@@ -10195,7 +10503,9 @@
       <c r="T132" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U132" s="2" t="inlineStr"/>
+      <c r="U132" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V132" t="inlineStr"/>
       <c r="W132" s="1" t="n">
         <v>159.3</v>
@@ -10272,7 +10582,9 @@
       <c r="T133" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U133" s="2" t="inlineStr"/>
+      <c r="U133" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V133" t="inlineStr"/>
       <c r="W133" s="2" t="n">
         <v>149.9</v>
@@ -10345,7 +10657,9 @@
       <c r="T134" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U134" s="2" t="inlineStr"/>
+      <c r="U134" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V134" t="inlineStr"/>
       <c r="W134" s="2" t="n">
         <v>149.7</v>
@@ -10418,7 +10732,9 @@
       <c r="T135" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U135" s="2" t="inlineStr"/>
+      <c r="U135" s="2" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V135" t="inlineStr"/>
       <c r="W135" s="2" t="n">
         <v>147</v>
@@ -10491,7 +10807,9 @@
       <c r="T136" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U136" s="2" t="inlineStr"/>
+      <c r="U136" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V136" t="inlineStr"/>
       <c r="W136" s="2" t="n">
         <v>147.5</v>
@@ -10564,7 +10882,9 @@
       <c r="T137" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U137" s="2" t="inlineStr"/>
+      <c r="U137" s="2" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V137" t="inlineStr"/>
       <c r="W137" s="2" t="n">
         <v>148.6</v>
@@ -10637,7 +10957,9 @@
       <c r="T138" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="U138" s="2" t="inlineStr"/>
+      <c r="U138" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V138" t="inlineStr"/>
       <c r="W138" s="2" t="n">
         <v>151.4</v>
@@ -10710,7 +11032,9 @@
       <c r="T139" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U139" s="2" t="inlineStr"/>
+      <c r="U139" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V139" t="inlineStr"/>
       <c r="W139" s="2" t="n">
         <v>153.1</v>
@@ -10783,7 +11107,9 @@
       <c r="T140" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U140" s="2" t="inlineStr"/>
+      <c r="U140" s="2" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V140" t="inlineStr"/>
       <c r="W140" s="2" t="n">
         <v>150.6</v>
@@ -10856,7 +11182,9 @@
       <c r="T141" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U141" s="2" t="inlineStr"/>
+      <c r="U141" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V141" t="inlineStr"/>
       <c r="W141" s="2" t="n">
         <v>153.8</v>
@@ -10929,7 +11257,9 @@
       <c r="T142" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U142" s="2" t="inlineStr"/>
+      <c r="U142" s="2" t="n">
+        <v>7.8</v>
+      </c>
       <c r="V142" t="inlineStr"/>
       <c r="W142" s="2" t="n">
         <v>153.9</v>
@@ -11002,7 +11332,9 @@
       <c r="T143" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U143" s="2" t="inlineStr"/>
+      <c r="U143" s="2" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V143" t="inlineStr"/>
       <c r="W143" s="2" t="n">
         <v>153.2</v>
@@ -11075,7 +11407,9 @@
       <c r="T144" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U144" s="2" t="inlineStr"/>
+      <c r="U144" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V144" t="inlineStr"/>
       <c r="W144" s="2" t="n">
         <v>144.6</v>
@@ -11152,7 +11486,9 @@
       <c r="T145" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U145" s="2" t="inlineStr"/>
+      <c r="U145" s="2" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V145" t="inlineStr"/>
       <c r="W145" s="2" t="n">
         <v>144.3</v>
@@ -11225,7 +11561,9 @@
       <c r="T146" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U146" s="2" t="inlineStr"/>
+      <c r="U146" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V146" t="inlineStr"/>
       <c r="W146" s="2" t="n">
         <v>146.4</v>
@@ -11298,7 +11636,9 @@
       <c r="T147" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U147" s="2" t="inlineStr"/>
+      <c r="U147" s="2" t="n">
+        <v>8.1</v>
+      </c>
       <c r="V147" t="inlineStr"/>
       <c r="W147" s="2" t="n">
         <v>150</v>
@@ -11371,7 +11711,9 @@
       <c r="T148" s="2" t="n">
         <v>14.6</v>
       </c>
-      <c r="U148" s="2" t="inlineStr"/>
+      <c r="U148" s="2" t="n">
+        <v>7.8</v>
+      </c>
       <c r="V148" t="inlineStr"/>
       <c r="W148" s="1" t="n">
         <v>156.5</v>
@@ -11444,7 +11786,9 @@
       <c r="T149" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U149" s="2" t="inlineStr"/>
+      <c r="U149" s="2" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V149" t="inlineStr"/>
       <c r="W149" s="2" t="n">
         <v>150.9</v>
@@ -11517,7 +11861,9 @@
       <c r="T150" s="2" t="n">
         <v>14.4</v>
       </c>
-      <c r="U150" s="2" t="inlineStr"/>
+      <c r="U150" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V150" t="inlineStr"/>
       <c r="W150" s="2" t="n">
         <v>152.5</v>
@@ -11590,7 +11936,9 @@
       <c r="T151" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U151" s="2" t="inlineStr"/>
+      <c r="U151" s="2" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V151" t="inlineStr"/>
       <c r="W151" s="2" t="n">
         <v>152.1</v>
@@ -11667,7 +12015,9 @@
       <c r="T152" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U152" s="2" t="inlineStr"/>
+      <c r="U152" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V152" t="inlineStr"/>
       <c r="W152" s="2" t="n">
         <v>151.5</v>
@@ -11740,7 +12090,9 @@
       <c r="T153" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U153" s="2" t="inlineStr"/>
+      <c r="U153" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V153" t="inlineStr"/>
       <c r="W153" s="2" t="n">
         <v>150.2</v>
@@ -11813,7 +12165,9 @@
       <c r="T154" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U154" s="2" t="inlineStr"/>
+      <c r="U154" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V154" t="inlineStr"/>
       <c r="W154" s="2" t="n">
         <v>154</v>
@@ -11886,7 +12240,9 @@
       <c r="T155" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U155" s="2" t="inlineStr"/>
+      <c r="U155" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V155" t="inlineStr"/>
       <c r="W155" s="2" t="n">
         <v>148.2</v>
@@ -11959,7 +12315,9 @@
       <c r="T156" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U156" s="2" t="inlineStr"/>
+      <c r="U156" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V156" t="inlineStr"/>
       <c r="W156" s="2" t="n">
         <v>148.8</v>
@@ -12032,7 +12390,9 @@
       <c r="T157" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U157" s="2" t="inlineStr"/>
+      <c r="U157" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V157" t="inlineStr"/>
       <c r="W157" s="2" t="n">
         <v>150.9</v>
@@ -12105,7 +12465,9 @@
       <c r="T158" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U158" s="2" t="inlineStr"/>
+      <c r="U158" s="2" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V158" t="inlineStr"/>
       <c r="W158" s="2" t="n">
         <v>151.9</v>
@@ -12178,7 +12540,9 @@
       <c r="T159" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="U159" s="2" t="inlineStr"/>
+      <c r="U159" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V159" t="inlineStr"/>
       <c r="W159" s="2" t="n">
         <v>147.6</v>
@@ -12251,7 +12615,9 @@
       <c r="T160" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U160" s="2" t="inlineStr"/>
+      <c r="U160" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V160" t="inlineStr"/>
       <c r="W160" s="2" t="n">
         <v>149.5</v>
@@ -12324,7 +12690,9 @@
       <c r="T161" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U161" s="2" t="inlineStr"/>
+      <c r="U161" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="V161" t="inlineStr"/>
       <c r="W161" s="2" t="n">
         <v>152.1</v>
@@ -12397,7 +12765,9 @@
       <c r="T162" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U162" s="2" t="inlineStr"/>
+      <c r="U162" s="2" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V162" t="inlineStr"/>
       <c r="W162" s="2" t="n">
         <v>148.2</v>
@@ -12470,7 +12840,9 @@
       <c r="T163" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U163" s="2" t="inlineStr"/>
+      <c r="U163" s="2" t="n">
+        <v>14.8</v>
+      </c>
       <c r="V163" t="inlineStr"/>
       <c r="W163" s="2" t="n">
         <v>146.4</v>
@@ -12543,7 +12915,9 @@
       <c r="T164" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U164" s="2" t="inlineStr"/>
+      <c r="U164" s="2" t="n">
+        <v>14.4</v>
+      </c>
       <c r="V164" t="inlineStr"/>
       <c r="W164" s="2" t="n">
         <v>148.2</v>
@@ -12616,7 +12990,9 @@
       <c r="T165" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U165" s="2" t="inlineStr"/>
+      <c r="U165" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V165" t="inlineStr"/>
       <c r="W165" s="2" t="n">
         <v>147</v>
@@ -12689,7 +13065,9 @@
       <c r="T166" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U166" s="2" t="inlineStr"/>
+      <c r="U166" s="2" t="n">
+        <v>9.1</v>
+      </c>
       <c r="V166" t="inlineStr"/>
       <c r="W166" s="2" t="n">
         <v>145.5</v>
@@ -12762,7 +13140,9 @@
       <c r="T167" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U167" s="2" t="inlineStr"/>
+      <c r="U167" s="2" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="V167" t="inlineStr"/>
       <c r="W167" s="2" t="n">
         <v>146.5</v>
@@ -12835,7 +13215,9 @@
       <c r="T168" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U168" s="2" t="inlineStr"/>
+      <c r="U168" s="2" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V168" t="inlineStr"/>
       <c r="W168" s="2" t="n">
         <v>145.9</v>
@@ -12908,7 +13290,9 @@
       <c r="T169" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U169" s="2" t="inlineStr"/>
+      <c r="U169" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V169" t="inlineStr"/>
       <c r="W169" s="2" t="n">
         <v>145.9</v>
@@ -12981,7 +13365,9 @@
       <c r="T170" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U170" s="2" t="inlineStr"/>
+      <c r="U170" s="2" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V170" t="inlineStr"/>
       <c r="W170" s="2" t="n">
         <v>141.5</v>
@@ -13054,7 +13440,9 @@
       <c r="T171" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U171" s="2" t="inlineStr"/>
+      <c r="U171" s="2" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V171" t="inlineStr"/>
       <c r="W171" s="2" t="n">
         <v>143</v>
@@ -13127,7 +13515,9 @@
       <c r="T172" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U172" s="2" t="inlineStr"/>
+      <c r="U172" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="V172" t="inlineStr"/>
       <c r="W172" s="2" t="n">
         <v>143.4</v>
@@ -13200,7 +13590,9 @@
       <c r="T173" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U173" s="2" t="inlineStr"/>
+      <c r="U173" s="2" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V173" t="inlineStr"/>
       <c r="W173" s="2" t="n">
         <v>143.7</v>
@@ -13273,7 +13665,9 @@
       <c r="T174" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U174" s="2" t="inlineStr"/>
+      <c r="U174" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V174" t="inlineStr"/>
       <c r="W174" s="2" t="n">
         <v>145.9</v>
@@ -13346,7 +13740,9 @@
       <c r="T175" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U175" s="2" t="inlineStr"/>
+      <c r="U175" s="2" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V175" t="inlineStr"/>
       <c r="W175" s="2" t="n">
         <v>144.6</v>
@@ -13419,7 +13815,9 @@
       <c r="T176" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U176" s="2" t="inlineStr"/>
+      <c r="U176" s="2" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V176" t="inlineStr"/>
       <c r="W176" s="2" t="n">
         <v>142.5</v>
@@ -13492,7 +13890,9 @@
       <c r="T177" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U177" s="2" t="inlineStr"/>
+      <c r="U177" s="2" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V177" t="inlineStr"/>
       <c r="W177" s="2" t="n">
         <v>145.2</v>
@@ -13565,7 +13965,9 @@
       <c r="T178" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U178" s="2" t="inlineStr"/>
+      <c r="U178" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V178" t="inlineStr"/>
       <c r="W178" s="2" t="n">
         <v>145.8</v>
@@ -13638,7 +14040,9 @@
       <c r="T179" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U179" s="2" t="inlineStr"/>
+      <c r="U179" s="2" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V179" t="inlineStr"/>
       <c r="W179" s="2" t="n">
         <v>145.3</v>
@@ -13715,7 +14119,9 @@
       <c r="T180" s="7" t="n">
         <v>21.7</v>
       </c>
-      <c r="U180" s="7" t="inlineStr"/>
+      <c r="U180" s="6" t="n">
+        <v>25.7</v>
+      </c>
       <c r="V180" s="4" t="inlineStr"/>
       <c r="W180" s="7" t="n">
         <v>138.9</v>
@@ -13788,7 +14194,9 @@
       <c r="T181" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U181" s="2" t="inlineStr"/>
+      <c r="U181" s="2" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V181" t="inlineStr"/>
       <c r="W181" s="2" t="n">
         <v>142.8</v>
@@ -13861,7 +14269,9 @@
       <c r="T182" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U182" s="2" t="inlineStr"/>
+      <c r="U182" s="2" t="n">
+        <v>17.7</v>
+      </c>
       <c r="V182" t="inlineStr"/>
       <c r="W182" s="2" t="n">
         <v>146.5</v>
@@ -13934,7 +14344,9 @@
       <c r="T183" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U183" s="2" t="inlineStr"/>
+      <c r="U183" s="2" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V183" t="inlineStr"/>
       <c r="W183" s="2" t="n">
         <v>145</v>
@@ -14007,7 +14419,9 @@
       <c r="T184" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="U184" s="2" t="inlineStr"/>
+      <c r="U184" s="2" t="n">
+        <v>23.8</v>
+      </c>
       <c r="V184" t="inlineStr"/>
       <c r="W184" s="2" t="n">
         <v>147.1</v>
@@ -14080,7 +14494,9 @@
       <c r="T185" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U185" s="2" t="inlineStr"/>
+      <c r="U185" s="2" t="n">
+        <v>17.9</v>
+      </c>
       <c r="V185" t="inlineStr"/>
       <c r="W185" s="2" t="n">
         <v>147.6</v>
@@ -14153,7 +14569,9 @@
       <c r="T186" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U186" s="2" t="inlineStr"/>
+      <c r="U186" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V186" t="inlineStr"/>
       <c r="W186" s="2" t="n">
         <v>151.3</v>
@@ -14226,7 +14644,9 @@
       <c r="T187" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U187" s="2" t="inlineStr"/>
+      <c r="U187" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V187" t="inlineStr"/>
       <c r="W187" s="2" t="n">
         <v>149.9</v>
@@ -14299,7 +14719,9 @@
       <c r="T188" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U188" s="2" t="inlineStr"/>
+      <c r="U188" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V188" t="inlineStr"/>
       <c r="W188" s="2" t="n">
         <v>152.9</v>
@@ -14372,7 +14794,9 @@
       <c r="T189" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U189" s="2" t="inlineStr"/>
+      <c r="U189" s="2" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V189" t="inlineStr"/>
       <c r="W189" s="2" t="n">
         <v>154.3</v>
@@ -14445,7 +14869,9 @@
       <c r="T190" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U190" s="2" t="inlineStr"/>
+      <c r="U190" s="2" t="n">
+        <v>14.5</v>
+      </c>
       <c r="V190" t="inlineStr"/>
       <c r="W190" s="2" t="n">
         <v>153.5</v>
@@ -14518,7 +14944,9 @@
       <c r="T191" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U191" s="2" t="inlineStr"/>
+      <c r="U191" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V191" t="inlineStr"/>
       <c r="W191" s="2" t="n">
         <v>148.5</v>
@@ -14591,7 +15019,9 @@
       <c r="T192" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U192" s="2" t="inlineStr"/>
+      <c r="U192" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V192" t="inlineStr"/>
       <c r="W192" s="2" t="n">
         <v>140.4</v>
@@ -14664,7 +15094,9 @@
       <c r="T193" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U193" s="2" t="inlineStr"/>
+      <c r="U193" s="2" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V193" t="inlineStr"/>
       <c r="W193" s="2" t="n">
         <v>139.4</v>
@@ -14737,7 +15169,9 @@
       <c r="T194" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U194" s="2" t="inlineStr"/>
+      <c r="U194" s="2" t="n">
+        <v>14.2</v>
+      </c>
       <c r="V194" t="inlineStr"/>
       <c r="W194" s="2" t="n">
         <v>141.1</v>
@@ -14810,7 +15244,9 @@
       <c r="T195" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U195" s="2" t="inlineStr"/>
+      <c r="U195" s="2" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V195" t="inlineStr"/>
       <c r="W195" s="2" t="n">
         <v>142.8</v>
@@ -14883,7 +15319,9 @@
       <c r="T196" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U196" s="2" t="inlineStr"/>
+      <c r="U196" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V196" t="inlineStr"/>
       <c r="W196" s="2" t="n">
         <v>142</v>
@@ -14956,7 +15394,9 @@
       <c r="T197" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U197" s="2" t="inlineStr"/>
+      <c r="U197" s="2" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V197" t="inlineStr"/>
       <c r="W197" s="2" t="n">
         <v>144</v>
@@ -15029,7 +15469,9 @@
       <c r="T198" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U198" s="2" t="inlineStr"/>
+      <c r="U198" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V198" t="inlineStr"/>
       <c r="W198" s="2" t="n">
         <v>143.6</v>
@@ -15106,7 +15548,9 @@
       <c r="T199" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U199" s="2" t="inlineStr"/>
+      <c r="U199" s="2" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V199" t="inlineStr"/>
       <c r="W199" s="2" t="n">
         <v>143.5</v>
@@ -15179,7 +15623,9 @@
       <c r="T200" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U200" s="2" t="inlineStr"/>
+      <c r="U200" s="2" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V200" t="inlineStr"/>
       <c r="W200" s="2" t="n">
         <v>141.3</v>
@@ -15252,7 +15698,9 @@
       <c r="T201" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U201" s="2" t="inlineStr"/>
+      <c r="U201" s="2" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V201" t="inlineStr"/>
       <c r="W201" s="2" t="n">
         <v>142.9</v>
@@ -15325,7 +15773,9 @@
       <c r="T202" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U202" s="2" t="inlineStr"/>
+      <c r="U202" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V202" t="inlineStr"/>
       <c r="W202" s="2" t="n">
         <v>143.4</v>
@@ -15398,7 +15848,9 @@
       <c r="T203" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U203" s="2" t="inlineStr"/>
+      <c r="U203" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V203" t="inlineStr"/>
       <c r="W203" s="2" t="n">
         <v>138.6</v>
@@ -15475,7 +15927,9 @@
       <c r="T204" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="U204" s="2" t="inlineStr"/>
+      <c r="U204" s="2" t="n">
+        <v>17</v>
+      </c>
       <c r="V204" t="inlineStr"/>
       <c r="W204" s="2" t="n">
         <v>142.5</v>
@@ -15548,7 +16002,9 @@
       <c r="T205" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U205" s="2" t="inlineStr"/>
+      <c r="U205" s="2" t="n">
+        <v>18.5</v>
+      </c>
       <c r="V205" t="inlineStr"/>
       <c r="W205" s="2" t="n">
         <v>137.9</v>
@@ -15621,7 +16077,9 @@
       <c r="T206" s="2" t="n">
         <v>22.4</v>
       </c>
-      <c r="U206" s="2" t="inlineStr"/>
+      <c r="U206" s="2" t="n">
+        <v>19.4</v>
+      </c>
       <c r="V206" t="inlineStr"/>
       <c r="W206" s="2" t="n">
         <v>140.9</v>
@@ -15698,7 +16156,9 @@
       <c r="T207" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U207" s="2" t="inlineStr"/>
+      <c r="U207" s="2" t="n">
+        <v>20.9</v>
+      </c>
       <c r="V207" t="inlineStr"/>
       <c r="W207" s="2" t="n">
         <v>143</v>
@@ -15771,7 +16231,9 @@
       <c r="T208" s="2" t="n">
         <v>23.7</v>
       </c>
-      <c r="U208" s="2" t="inlineStr"/>
+      <c r="U208" s="3" t="n">
+        <v>26.9</v>
+      </c>
       <c r="V208" t="inlineStr"/>
       <c r="W208" s="2" t="n">
         <v>143.1</v>
@@ -15844,8 +16306,14 @@
       <c r="T209" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="U209" s="2" t="inlineStr"/>
-      <c r="V209" t="inlineStr"/>
+      <c r="U209" s="3" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="V209" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W209" s="2" t="n">
         <v>145</v>
       </c>
@@ -15917,7 +16385,9 @@
       <c r="T210" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="U210" s="2" t="inlineStr"/>
+      <c r="U210" s="2" t="n">
+        <v>23.3</v>
+      </c>
       <c r="V210" t="inlineStr"/>
       <c r="W210" s="2" t="n">
         <v>148.3</v>
@@ -15990,7 +16460,9 @@
       <c r="T211" s="2" t="n">
         <v>20.5</v>
       </c>
-      <c r="U211" s="2" t="inlineStr"/>
+      <c r="U211" s="2" t="n">
+        <v>14.3</v>
+      </c>
       <c r="V211" t="inlineStr"/>
       <c r="W211" s="2" t="n">
         <v>148.6</v>
@@ -16063,7 +16535,9 @@
       <c r="T212" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U212" s="2" t="inlineStr"/>
+      <c r="U212" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V212" t="inlineStr"/>
       <c r="W212" s="2" t="n">
         <v>151.7</v>
@@ -16136,7 +16610,9 @@
       <c r="T213" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U213" s="2" t="inlineStr"/>
+      <c r="U213" s="2" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V213" t="inlineStr"/>
       <c r="W213" s="2" t="n">
         <v>145</v>
@@ -16209,7 +16685,9 @@
       <c r="T214" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U214" s="2" t="inlineStr"/>
+      <c r="U214" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V214" t="inlineStr"/>
       <c r="W214" s="2" t="n">
         <v>143</v>
@@ -16282,7 +16760,9 @@
       <c r="T215" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U215" s="2" t="inlineStr"/>
+      <c r="U215" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V215" t="inlineStr"/>
       <c r="W215" s="2" t="n">
         <v>144.9</v>
@@ -16355,7 +16835,9 @@
       <c r="T216" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U216" s="2" t="inlineStr"/>
+      <c r="U216" s="2" t="n">
+        <v>10.5</v>
+      </c>
       <c r="V216" t="inlineStr"/>
       <c r="W216" s="2" t="n">
         <v>144.9</v>
@@ -16428,7 +16910,9 @@
       <c r="T217" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U217" s="2" t="inlineStr"/>
+      <c r="U217" s="2" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="V217" t="inlineStr"/>
       <c r="W217" s="2" t="n">
         <v>149.2</v>
@@ -16501,7 +16985,9 @@
       <c r="T218" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U218" s="2" t="inlineStr"/>
+      <c r="U218" s="2" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V218" t="inlineStr"/>
       <c r="W218" s="2" t="n">
         <v>148.9</v>
@@ -16574,7 +17060,9 @@
       <c r="T219" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U219" s="2" t="inlineStr"/>
+      <c r="U219" s="2" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V219" t="inlineStr"/>
       <c r="W219" s="2" t="n">
         <v>148.8</v>
@@ -16647,7 +17135,9 @@
       <c r="T220" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U220" s="2" t="inlineStr"/>
+      <c r="U220" s="2" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V220" t="inlineStr"/>
       <c r="W220" s="2" t="n">
         <v>150.6</v>
@@ -16720,7 +17210,9 @@
       <c r="T221" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U221" s="2" t="inlineStr"/>
+      <c r="U221" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V221" t="inlineStr"/>
       <c r="W221" s="2" t="n">
         <v>150.3</v>
@@ -16793,7 +17285,9 @@
       <c r="T222" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U222" s="2" t="inlineStr"/>
+      <c r="U222" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V222" t="inlineStr"/>
       <c r="W222" s="2" t="n">
         <v>147.6</v>
@@ -16866,7 +17360,9 @@
       <c r="T223" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U223" s="2" t="inlineStr"/>
+      <c r="U223" s="2" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V223" t="inlineStr"/>
       <c r="W223" s="2" t="n">
         <v>148.3</v>
@@ -16939,7 +17435,9 @@
       <c r="T224" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U224" s="2" t="inlineStr"/>
+      <c r="U224" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V224" t="inlineStr"/>
       <c r="W224" s="2" t="n">
         <v>153.6</v>
@@ -17012,7 +17510,9 @@
       <c r="T225" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U225" s="2" t="inlineStr"/>
+      <c r="U225" s="2" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V225" t="inlineStr"/>
       <c r="W225" s="1" t="n">
         <v>161.9</v>
@@ -17085,7 +17585,9 @@
       <c r="T226" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U226" s="2" t="inlineStr"/>
+      <c r="U226" s="2" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V226" t="inlineStr"/>
       <c r="W226" s="1" t="n">
         <v>157</v>
@@ -17162,7 +17664,9 @@
       <c r="T227" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U227" s="2" t="inlineStr"/>
+      <c r="U227" s="2" t="n">
+        <v>16.9</v>
+      </c>
       <c r="V227" t="inlineStr"/>
       <c r="W227" s="2" t="n">
         <v>153.5</v>
@@ -17235,7 +17739,9 @@
       <c r="T228" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U228" s="2" t="inlineStr"/>
+      <c r="U228" s="2" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V228" t="inlineStr"/>
       <c r="W228" s="1" t="n">
         <v>155.4</v>
@@ -17308,7 +17814,9 @@
       <c r="T229" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U229" s="2" t="inlineStr"/>
+      <c r="U229" s="2" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V229" t="inlineStr"/>
       <c r="W229" s="1" t="n">
         <v>155.9</v>
@@ -17381,7 +17889,9 @@
       <c r="T230" s="2" t="n">
         <v>14.1</v>
       </c>
-      <c r="U230" s="2" t="inlineStr"/>
+      <c r="U230" s="2" t="n">
+        <v>7.7</v>
+      </c>
       <c r="V230" t="inlineStr"/>
       <c r="W230" s="1" t="n">
         <v>159.9</v>
@@ -17454,7 +17964,9 @@
       <c r="T231" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="U231" s="2" t="inlineStr"/>
+      <c r="U231" s="2" t="n">
+        <v>7.6</v>
+      </c>
       <c r="V231" t="inlineStr"/>
       <c r="W231" s="1" t="n">
         <v>160.5</v>
@@ -17527,7 +18039,9 @@
       <c r="T232" s="2" t="n">
         <v>13.5</v>
       </c>
-      <c r="U232" s="2" t="inlineStr"/>
+      <c r="U232" s="2" t="n">
+        <v>7.4</v>
+      </c>
       <c r="V232" t="inlineStr"/>
       <c r="W232" s="1" t="n">
         <v>160.5</v>
@@ -17600,7 +18114,9 @@
       <c r="T233" s="2" t="n">
         <v>13.6</v>
       </c>
-      <c r="U233" s="2" t="inlineStr"/>
+      <c r="U233" s="2" t="n">
+        <v>7.7</v>
+      </c>
       <c r="V233" t="inlineStr"/>
       <c r="W233" s="2" t="n">
         <v>151.4</v>
@@ -17673,7 +18189,9 @@
       <c r="T234" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U234" s="2" t="inlineStr"/>
+      <c r="U234" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="V234" t="inlineStr"/>
       <c r="W234" s="2" t="n">
         <v>150.5</v>
@@ -17746,7 +18264,9 @@
       <c r="T235" s="2" t="n">
         <v>14.3</v>
       </c>
-      <c r="U235" s="2" t="inlineStr"/>
+      <c r="U235" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V235" t="inlineStr"/>
       <c r="W235" s="2" t="n">
         <v>148.3</v>
@@ -17823,7 +18343,9 @@
       <c r="T236" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U236" s="2" t="inlineStr"/>
+      <c r="U236" s="2" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V236" t="inlineStr"/>
       <c r="W236" s="2" t="n">
         <v>148.7</v>
@@ -17896,7 +18418,9 @@
       <c r="T237" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U237" s="2" t="inlineStr"/>
+      <c r="U237" s="2" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V237" t="inlineStr"/>
       <c r="W237" s="2" t="n">
         <v>141.9</v>
@@ -17969,7 +18493,9 @@
       <c r="T238" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U238" s="2" t="inlineStr"/>
+      <c r="U238" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V238" t="inlineStr"/>
       <c r="W238" s="2" t="n">
         <v>142.4</v>
@@ -18042,7 +18568,9 @@
       <c r="T239" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U239" s="2" t="inlineStr"/>
+      <c r="U239" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="V239" t="inlineStr"/>
       <c r="W239" s="2" t="n">
         <v>146.2</v>
@@ -18115,7 +18643,9 @@
       <c r="T240" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U240" s="2" t="inlineStr"/>
+      <c r="U240" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="V240" t="inlineStr"/>
       <c r="W240" s="2" t="n">
         <v>143.6</v>
@@ -18188,7 +18718,9 @@
       <c r="T241" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U241" s="2" t="inlineStr"/>
+      <c r="U241" s="2" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V241" t="inlineStr"/>
       <c r="W241" s="2" t="n">
         <v>147.1</v>
@@ -18261,7 +18793,9 @@
       <c r="T242" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U242" s="2" t="inlineStr"/>
+      <c r="U242" s="2" t="n">
+        <v>8.5</v>
+      </c>
       <c r="V242" t="inlineStr"/>
       <c r="W242" s="2" t="n">
         <v>146</v>
@@ -18334,7 +18868,9 @@
       <c r="T243" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U243" s="2" t="inlineStr"/>
+      <c r="U243" s="2" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V243" t="inlineStr"/>
       <c r="W243" s="2" t="n">
         <v>149.8</v>
@@ -18407,7 +18943,9 @@
       <c r="T244" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U244" s="2" t="inlineStr"/>
+      <c r="U244" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V244" t="inlineStr"/>
       <c r="W244" s="2" t="n">
         <v>151.6</v>
@@ -18480,7 +19018,9 @@
       <c r="T245" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U245" s="2" t="inlineStr"/>
+      <c r="U245" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V245" t="inlineStr"/>
       <c r="W245" s="2" t="n">
         <v>152.5</v>
@@ -18553,7 +19093,9 @@
       <c r="T246" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U246" s="2" t="inlineStr"/>
+      <c r="U246" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V246" t="inlineStr"/>
       <c r="W246" s="2" t="n">
         <v>151.6</v>
@@ -18626,7 +19168,9 @@
       <c r="T247" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U247" s="2" t="inlineStr"/>
+      <c r="U247" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V247" t="inlineStr"/>
       <c r="W247" s="2" t="n">
         <v>153.6</v>
@@ -18703,7 +19247,9 @@
       <c r="T248" s="7" t="n">
         <v>20.1</v>
       </c>
-      <c r="U248" s="7" t="inlineStr"/>
+      <c r="U248" s="7" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V248" s="4" t="inlineStr"/>
       <c r="W248" s="5" t="n">
         <v>155</v>
@@ -18776,7 +19322,9 @@
       <c r="T249" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U249" s="2" t="inlineStr"/>
+      <c r="U249" s="2" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V249" t="inlineStr"/>
       <c r="W249" s="2" t="n">
         <v>144.4</v>
@@ -18849,7 +19397,9 @@
       <c r="T250" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U250" s="2" t="inlineStr"/>
+      <c r="U250" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V250" t="inlineStr"/>
       <c r="W250" s="2" t="n">
         <v>141.3</v>
@@ -18922,7 +19472,9 @@
       <c r="T251" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U251" s="2" t="inlineStr"/>
+      <c r="U251" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V251" t="inlineStr"/>
       <c r="W251" s="2" t="n">
         <v>144</v>
@@ -18995,7 +19547,9 @@
       <c r="T252" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U252" s="2" t="inlineStr"/>
+      <c r="U252" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="V252" t="inlineStr"/>
       <c r="W252" s="2" t="n">
         <v>148.1</v>
@@ -19068,7 +19622,9 @@
       <c r="T253" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U253" s="2" t="inlineStr"/>
+      <c r="U253" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V253" t="inlineStr"/>
       <c r="W253" s="2" t="n">
         <v>147.2</v>
@@ -19141,7 +19697,9 @@
       <c r="T254" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U254" s="2" t="inlineStr"/>
+      <c r="U254" s="2" t="n">
+        <v>13.2</v>
+      </c>
       <c r="V254" t="inlineStr"/>
       <c r="W254" s="2" t="n">
         <v>145</v>
@@ -19214,7 +19772,9 @@
       <c r="T255" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U255" s="2" t="inlineStr"/>
+      <c r="U255" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V255" t="inlineStr"/>
       <c r="W255" s="2" t="n">
         <v>143.7</v>
@@ -19287,7 +19847,9 @@
       <c r="T256" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U256" s="2" t="inlineStr"/>
+      <c r="U256" s="2" t="n">
+        <v>16.4</v>
+      </c>
       <c r="V256" t="inlineStr"/>
       <c r="W256" s="2" t="n">
         <v>143.6</v>
@@ -19360,7 +19922,9 @@
       <c r="T257" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U257" s="2" t="inlineStr"/>
+      <c r="U257" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V257" t="inlineStr"/>
       <c r="W257" s="2" t="n">
         <v>146.6</v>
@@ -19437,7 +20001,9 @@
       <c r="T258" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U258" s="2" t="inlineStr"/>
+      <c r="U258" s="2" t="n">
+        <v>14.5</v>
+      </c>
       <c r="V258" t="inlineStr"/>
       <c r="W258" s="2" t="n">
         <v>143.9</v>
@@ -19510,7 +20076,9 @@
       <c r="T259" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U259" s="2" t="inlineStr"/>
+      <c r="U259" s="2" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V259" t="inlineStr"/>
       <c r="W259" s="2" t="n">
         <v>143.2</v>
@@ -19587,7 +20155,9 @@
       <c r="T260" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U260" s="2" t="inlineStr"/>
+      <c r="U260" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V260" t="inlineStr"/>
       <c r="W260" s="2" t="n">
         <v>137.2</v>
@@ -19660,7 +20230,9 @@
       <c r="T261" s="2" t="n">
         <v>20.4</v>
       </c>
-      <c r="U261" s="2" t="inlineStr"/>
+      <c r="U261" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="V261" t="inlineStr"/>
       <c r="W261" s="2" t="n">
         <v>140.3</v>
@@ -19733,7 +20305,9 @@
       <c r="T262" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U262" s="2" t="inlineStr"/>
+      <c r="U262" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V262" t="inlineStr"/>
       <c r="W262" s="2" t="n">
         <v>145.2</v>
@@ -19806,7 +20380,9 @@
       <c r="T263" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U263" s="2" t="inlineStr"/>
+      <c r="U263" s="2" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V263" t="inlineStr"/>
       <c r="W263" s="2" t="n">
         <v>145.7</v>
@@ -19879,7 +20455,9 @@
       <c r="T264" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U264" s="2" t="inlineStr"/>
+      <c r="U264" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V264" t="inlineStr"/>
       <c r="W264" s="2" t="n">
         <v>143.8</v>
@@ -19956,7 +20534,9 @@
       <c r="T265" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U265" s="2" t="inlineStr"/>
+      <c r="U265" s="2" t="n">
+        <v>21.5</v>
+      </c>
       <c r="V265" t="inlineStr"/>
       <c r="W265" s="2" t="n">
         <v>142.5</v>
@@ -20029,7 +20609,9 @@
       <c r="T266" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U266" s="2" t="inlineStr"/>
+      <c r="U266" s="2" t="n">
+        <v>22.4</v>
+      </c>
       <c r="V266" t="inlineStr"/>
       <c r="W266" s="2" t="n">
         <v>139.4</v>
@@ -20102,7 +20684,9 @@
       <c r="T267" s="2" t="n">
         <v>20.3</v>
       </c>
-      <c r="U267" s="2" t="inlineStr"/>
+      <c r="U267" s="2" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V267" t="inlineStr"/>
       <c r="W267" s="2" t="n">
         <v>140.3</v>
@@ -20175,7 +20759,9 @@
       <c r="T268" s="2" t="n">
         <v>19.6</v>
       </c>
-      <c r="U268" s="2" t="inlineStr"/>
+      <c r="U268" s="2" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V268" t="inlineStr"/>
       <c r="W268" s="2" t="n">
         <v>139.2</v>
@@ -20252,7 +20838,9 @@
       <c r="T269" s="2" t="n">
         <v>20.2</v>
       </c>
-      <c r="U269" s="2" t="inlineStr"/>
+      <c r="U269" s="2" t="n">
+        <v>16.6</v>
+      </c>
       <c r="V269" t="inlineStr"/>
       <c r="W269" s="2" t="n">
         <v>141.2</v>
@@ -20325,7 +20913,9 @@
       <c r="T270" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U270" s="2" t="inlineStr"/>
+      <c r="U270" s="2" t="n">
+        <v>17.8</v>
+      </c>
       <c r="V270" t="inlineStr"/>
       <c r="W270" s="2" t="n">
         <v>145.5</v>
@@ -20402,7 +20992,9 @@
       <c r="T271" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="U271" s="2" t="inlineStr"/>
+      <c r="U271" s="2" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V271" t="inlineStr"/>
       <c r="W271" s="2" t="n">
         <v>141.4</v>
@@ -20475,7 +21067,9 @@
       <c r="T272" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U272" s="2" t="inlineStr"/>
+      <c r="U272" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V272" t="inlineStr"/>
       <c r="W272" s="2" t="n">
         <v>141.9</v>
@@ -20548,7 +21142,9 @@
       <c r="T273" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U273" s="2" t="inlineStr"/>
+      <c r="U273" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V273" t="inlineStr"/>
       <c r="W273" s="2" t="n">
         <v>146.1</v>
@@ -20621,7 +21217,9 @@
       <c r="T274" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U274" s="2" t="inlineStr"/>
+      <c r="U274" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V274" t="inlineStr"/>
       <c r="W274" s="2" t="n">
         <v>146.6</v>
@@ -20698,7 +21296,9 @@
       <c r="T275" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U275" s="2" t="inlineStr"/>
+      <c r="U275" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="V275" t="inlineStr"/>
       <c r="W275" s="2" t="n">
         <v>146.7</v>
@@ -20771,7 +21371,9 @@
       <c r="T276" s="2" t="n">
         <v>21.4</v>
       </c>
-      <c r="U276" s="2" t="inlineStr"/>
+      <c r="U276" s="2" t="n">
+        <v>16.3</v>
+      </c>
       <c r="V276" t="inlineStr"/>
       <c r="W276" s="2" t="n">
         <v>151.8</v>
@@ -20844,7 +21446,9 @@
       <c r="T277" s="2" t="n">
         <v>23.6</v>
       </c>
-      <c r="U277" s="2" t="inlineStr"/>
+      <c r="U277" s="2" t="n">
+        <v>20.3</v>
+      </c>
       <c r="V277" t="inlineStr"/>
       <c r="W277" s="2" t="n">
         <v>152.8</v>
@@ -20917,7 +21521,9 @@
       <c r="T278" s="2" t="n">
         <v>21.1</v>
       </c>
-      <c r="U278" s="2" t="inlineStr"/>
+      <c r="U278" s="2" t="n">
+        <v>17.8</v>
+      </c>
       <c r="V278" t="inlineStr"/>
       <c r="W278" s="2" t="n">
         <v>152.9</v>
@@ -20990,7 +21596,9 @@
       <c r="T279" s="2" t="n">
         <v>23.8</v>
       </c>
-      <c r="U279" s="2" t="inlineStr"/>
+      <c r="U279" s="2" t="n">
+        <v>21.9</v>
+      </c>
       <c r="V279" t="inlineStr"/>
       <c r="W279" s="2" t="n">
         <v>153.9</v>
@@ -21067,8 +21675,14 @@
       <c r="T280" s="3" t="n">
         <v>29.5</v>
       </c>
-      <c r="U280" s="2" t="inlineStr"/>
-      <c r="V280" t="inlineStr"/>
+      <c r="U280" s="3" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="V280" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W280" s="2" t="n">
         <v>151.8</v>
       </c>
@@ -21140,7 +21754,9 @@
       <c r="T281" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="U281" s="2" t="inlineStr"/>
+      <c r="U281" s="2" t="n">
+        <v>22.7</v>
+      </c>
       <c r="V281" t="inlineStr"/>
       <c r="W281" s="1" t="n">
         <v>158</v>
@@ -21213,7 +21829,9 @@
       <c r="T282" s="2" t="n">
         <v>24.9</v>
       </c>
-      <c r="U282" s="2" t="inlineStr"/>
+      <c r="U282" s="2" t="n">
+        <v>21.3</v>
+      </c>
       <c r="V282" t="inlineStr"/>
       <c r="W282" s="2" t="n">
         <v>154.5</v>
@@ -21286,7 +21904,9 @@
       <c r="T283" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U283" s="2" t="inlineStr"/>
+      <c r="U283" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="V283" t="inlineStr"/>
       <c r="W283" s="2" t="n">
         <v>152.4</v>
@@ -21353,7 +21973,9 @@
       <c r="T284" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="U284" s="2" t="inlineStr"/>
+      <c r="U284" s="2" t="n">
+        <v>24.2</v>
+      </c>
       <c r="V284" t="inlineStr"/>
       <c r="W284" s="2" t="n">
         <v>139.9</v>
@@ -21426,8 +22048,14 @@
       <c r="T285" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="U285" s="2" t="inlineStr"/>
-      <c r="V285" t="inlineStr"/>
+      <c r="U285" s="3" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="V285" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W285" s="2" t="n">
         <v>137.8</v>
       </c>
@@ -21499,7 +22127,9 @@
       <c r="T286" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U286" s="2" t="inlineStr"/>
+      <c r="U286" s="2" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V286" t="inlineStr"/>
       <c r="W286" s="2" t="n">
         <v>141.5</v>
@@ -21572,7 +22202,9 @@
       <c r="T287" s="2" t="n">
         <v>22.4</v>
       </c>
-      <c r="U287" s="2" t="inlineStr"/>
+      <c r="U287" s="2" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V287" t="inlineStr"/>
       <c r="W287" s="2" t="n">
         <v>145</v>
@@ -21645,7 +22277,9 @@
       <c r="T288" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="U288" s="2" t="inlineStr"/>
+      <c r="U288" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V288" t="inlineStr"/>
       <c r="W288" s="2" t="n">
         <v>136.5</v>
@@ -21722,7 +22356,9 @@
       <c r="T289" s="2" t="n">
         <v>24.1</v>
       </c>
-      <c r="U289" s="2" t="inlineStr"/>
+      <c r="U289" s="2" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V289" t="inlineStr"/>
       <c r="W289" s="2" t="n">
         <v>138.3</v>
@@ -21799,8 +22435,14 @@
       <c r="T290" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="U290" s="2" t="inlineStr"/>
-      <c r="V290" t="inlineStr"/>
+      <c r="U290" s="3" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="V290" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W290" s="2" t="n">
         <v>139.1</v>
       </c>
@@ -21872,7 +22514,9 @@
       <c r="T291" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="U291" s="2" t="inlineStr"/>
+      <c r="U291" s="2" t="n">
+        <v>23.2</v>
+      </c>
       <c r="V291" t="inlineStr"/>
       <c r="W291" s="2" t="n">
         <v>142</v>
@@ -21949,7 +22593,9 @@
       <c r="T292" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="U292" s="2" t="inlineStr"/>
+      <c r="U292" s="2" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V292" t="inlineStr"/>
       <c r="W292" s="2" t="n">
         <v>142.6</v>
@@ -22022,7 +22668,9 @@
       <c r="T293" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="U293" s="2" t="inlineStr"/>
+      <c r="U293" s="2" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V293" t="inlineStr"/>
       <c r="W293" s="2" t="n">
         <v>140.9</v>
@@ -22095,7 +22743,9 @@
       <c r="T294" s="3" t="n">
         <v>27.4</v>
       </c>
-      <c r="U294" s="2" t="inlineStr"/>
+      <c r="U294" s="2" t="n">
+        <v>23.9</v>
+      </c>
       <c r="V294" t="inlineStr"/>
       <c r="W294" s="2" t="n">
         <v>144</v>
@@ -22172,8 +22822,14 @@
       <c r="T295" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="U295" s="2" t="inlineStr"/>
-      <c r="V295" t="inlineStr"/>
+      <c r="U295" s="3" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="V295" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W295" s="2" t="n">
         <v>139</v>
       </c>
@@ -22249,7 +22905,9 @@
       <c r="T296" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="U296" s="2" t="inlineStr"/>
+      <c r="U296" s="2" t="n">
+        <v>23</v>
+      </c>
       <c r="V296" t="inlineStr"/>
       <c r="W296" s="2" t="n">
         <v>142.2</v>
@@ -22322,7 +22980,9 @@
       <c r="T297" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="U297" s="2" t="inlineStr"/>
+      <c r="U297" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="V297" t="inlineStr"/>
       <c r="W297" s="2" t="n">
         <v>145.4</v>
@@ -22395,7 +23055,9 @@
       <c r="T298" s="2" t="n">
         <v>24.5</v>
       </c>
-      <c r="U298" s="2" t="inlineStr"/>
+      <c r="U298" s="2" t="n">
+        <v>23</v>
+      </c>
       <c r="V298" t="inlineStr"/>
       <c r="W298" s="2" t="n">
         <v>143.8</v>
@@ -22468,7 +23130,9 @@
       <c r="T299" s="2" t="n">
         <v>23.9</v>
       </c>
-      <c r="U299" s="2" t="inlineStr"/>
+      <c r="U299" s="3" t="n">
+        <v>27.6</v>
+      </c>
       <c r="V299" t="inlineStr"/>
       <c r="W299" s="2" t="n">
         <v>146.9</v>
@@ -22541,7 +23205,9 @@
       <c r="T300" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U300" s="2" t="inlineStr"/>
+      <c r="U300" s="2" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V300" t="inlineStr"/>
       <c r="W300" s="2" t="n">
         <v>147.6</v>
@@ -22614,8 +23280,14 @@
       <c r="T301" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="U301" s="2" t="inlineStr"/>
-      <c r="V301" t="inlineStr"/>
+      <c r="U301" s="3" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="V301" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W301" s="2" t="n">
         <v>148.4</v>
       </c>
@@ -22687,7 +23359,9 @@
       <c r="T302" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="U302" s="2" t="inlineStr"/>
+      <c r="U302" s="2" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V302" t="inlineStr"/>
       <c r="W302" s="2" t="n">
         <v>150.4</v>
@@ -22760,7 +23434,9 @@
       <c r="T303" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U303" s="2" t="inlineStr"/>
+      <c r="U303" s="2" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V303" t="inlineStr"/>
       <c r="W303" s="2" t="n">
         <v>143.3</v>
@@ -22833,7 +23509,9 @@
       <c r="T304" s="2" t="n">
         <v>19.2</v>
       </c>
-      <c r="U304" s="2" t="inlineStr"/>
+      <c r="U304" s="2" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V304" t="inlineStr"/>
       <c r="W304" s="2" t="n">
         <v>144.2</v>
@@ -22906,7 +23584,9 @@
       <c r="T305" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U305" s="2" t="inlineStr"/>
+      <c r="U305" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V305" t="inlineStr"/>
       <c r="W305" s="1" t="n">
         <v>156.9</v>
@@ -22979,7 +23659,9 @@
       <c r="T306" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U306" s="2" t="inlineStr"/>
+      <c r="U306" s="2" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V306" t="inlineStr"/>
       <c r="W306" s="2" t="n">
         <v>149.9</v>
@@ -23052,7 +23734,9 @@
       <c r="T307" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U307" s="2" t="inlineStr"/>
+      <c r="U307" s="2" t="n">
+        <v>12.6</v>
+      </c>
       <c r="V307" t="inlineStr"/>
       <c r="W307" s="2" t="n">
         <v>139.2</v>
@@ -23125,7 +23809,9 @@
       <c r="T308" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U308" s="2" t="inlineStr"/>
+      <c r="U308" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="V308" t="inlineStr"/>
       <c r="W308" s="2" t="n">
         <v>140.7</v>
@@ -23198,7 +23884,9 @@
       <c r="T309" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U309" s="2" t="inlineStr"/>
+      <c r="U309" s="2" t="n">
+        <v>14.2</v>
+      </c>
       <c r="V309" t="inlineStr"/>
       <c r="W309" s="2" t="n">
         <v>141.8</v>
@@ -23271,7 +23959,9 @@
       <c r="T310" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U310" s="2" t="inlineStr"/>
+      <c r="U310" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V310" t="inlineStr"/>
       <c r="W310" s="2" t="n">
         <v>141.9</v>
@@ -23344,7 +24034,9 @@
       <c r="T311" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U311" s="2" t="inlineStr"/>
+      <c r="U311" s="2" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V311" t="inlineStr"/>
       <c r="W311" s="2" t="n">
         <v>140.9</v>
@@ -23417,7 +24109,9 @@
       <c r="T312" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U312" s="2" t="inlineStr"/>
+      <c r="U312" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V312" t="inlineStr"/>
       <c r="W312" s="2" t="n">
         <v>140.8</v>
@@ -23490,7 +24184,9 @@
       <c r="T313" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U313" s="2" t="inlineStr"/>
+      <c r="U313" s="2" t="n">
+        <v>14.8</v>
+      </c>
       <c r="V313" t="inlineStr"/>
       <c r="W313" s="2" t="n">
         <v>139.6</v>
@@ -23563,7 +24259,9 @@
       <c r="T314" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U314" s="2" t="inlineStr"/>
+      <c r="U314" s="2" t="n">
+        <v>16.6</v>
+      </c>
       <c r="V314" t="inlineStr"/>
       <c r="W314" s="2" t="n">
         <v>139.1</v>
@@ -23636,7 +24334,9 @@
       <c r="T315" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U315" s="2" t="inlineStr"/>
+      <c r="U315" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V315" t="inlineStr"/>
       <c r="W315" s="2" t="n">
         <v>139.6</v>
@@ -23709,7 +24409,9 @@
       <c r="T316" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U316" s="2" t="inlineStr"/>
+      <c r="U316" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V316" t="inlineStr"/>
       <c r="W316" s="2" t="n">
         <v>138.2</v>
@@ -23782,7 +24484,9 @@
       <c r="T317" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="U317" s="2" t="inlineStr"/>
+      <c r="U317" s="2" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V317" t="inlineStr"/>
       <c r="W317" s="2" t="n">
         <v>141.9</v>
@@ -23855,7 +24559,9 @@
       <c r="T318" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U318" s="2" t="inlineStr"/>
+      <c r="U318" s="2" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V318" t="inlineStr"/>
       <c r="W318" s="2" t="n">
         <v>143.3</v>
@@ -23928,7 +24634,9 @@
       <c r="T319" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U319" s="2" t="inlineStr"/>
+      <c r="U319" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V319" t="inlineStr"/>
       <c r="W319" s="2" t="n">
         <v>141.4</v>
@@ -24001,7 +24709,9 @@
       <c r="T320" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="U320" s="2" t="inlineStr"/>
+      <c r="U320" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V320" t="inlineStr"/>
       <c r="W320" s="2" t="n">
         <v>141.7</v>
@@ -24074,7 +24784,9 @@
       <c r="T321" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U321" s="2" t="inlineStr"/>
+      <c r="U321" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V321" t="inlineStr"/>
       <c r="W321" s="2" t="n">
         <v>138.7</v>
@@ -24147,7 +24859,9 @@
       <c r="T322" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U322" s="2" t="inlineStr"/>
+      <c r="U322" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V322" t="inlineStr"/>
       <c r="W322" s="2" t="n">
         <v>135.4</v>
@@ -24220,7 +24934,9 @@
       <c r="T323" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U323" s="2" t="inlineStr"/>
+      <c r="U323" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V323" t="inlineStr"/>
       <c r="W323" s="2" t="n">
         <v>136.1</v>
@@ -24293,7 +25009,9 @@
       <c r="T324" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U324" s="2" t="inlineStr"/>
+      <c r="U324" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V324" t="inlineStr"/>
       <c r="W324" s="2" t="n">
         <v>138.2</v>
@@ -24366,7 +25084,9 @@
       <c r="T325" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U325" s="2" t="inlineStr"/>
+      <c r="U325" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V325" t="inlineStr"/>
       <c r="W325" s="2" t="n">
         <v>140.2</v>
@@ -24439,7 +25159,9 @@
       <c r="T326" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U326" s="2" t="inlineStr"/>
+      <c r="U326" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V326" t="inlineStr"/>
       <c r="W326" s="2" t="n">
         <v>139.4</v>
@@ -24512,7 +25234,9 @@
       <c r="T327" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U327" s="2" t="inlineStr"/>
+      <c r="U327" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V327" t="inlineStr"/>
       <c r="W327" s="2" t="n">
         <v>141.5</v>
@@ -24585,7 +25309,9 @@
       <c r="T328" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U328" s="2" t="inlineStr"/>
+      <c r="U328" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V328" t="inlineStr"/>
       <c r="W328" s="2" t="n">
         <v>139.3</v>
@@ -24658,7 +25384,9 @@
       <c r="T329" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U329" s="2" t="inlineStr"/>
+      <c r="U329" s="2" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V329" t="inlineStr"/>
       <c r="W329" s="2" t="n">
         <v>145.8</v>
@@ -24731,7 +25459,9 @@
       <c r="T330" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U330" s="2" t="inlineStr"/>
+      <c r="U330" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V330" t="inlineStr"/>
       <c r="W330" s="2" t="n">
         <v>138.4</v>
@@ -24804,7 +25534,9 @@
       <c r="T331" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U331" s="2" t="inlineStr"/>
+      <c r="U331" s="2" t="n">
+        <v>13.3</v>
+      </c>
       <c r="V331" t="inlineStr"/>
       <c r="W331" s="2" t="n">
         <v>135.5</v>
@@ -24877,7 +25609,9 @@
       <c r="T332" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U332" s="2" t="inlineStr"/>
+      <c r="U332" s="2" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V332" t="inlineStr"/>
       <c r="W332" s="2" t="n">
         <v>132.3</v>
@@ -24950,7 +25684,9 @@
       <c r="T333" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U333" s="2" t="inlineStr"/>
+      <c r="U333" s="2" t="n">
+        <v>14</v>
+      </c>
       <c r="V333" t="inlineStr"/>
       <c r="W333" s="2" t="n">
         <v>137</v>
@@ -25023,7 +25759,9 @@
       <c r="T334" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U334" s="2" t="inlineStr"/>
+      <c r="U334" s="2" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V334" t="inlineStr"/>
       <c r="W334" s="2" t="n">
         <v>137.4</v>
@@ -25096,7 +25834,9 @@
       <c r="T335" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U335" s="2" t="inlineStr"/>
+      <c r="U335" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V335" t="inlineStr"/>
       <c r="W335" s="2" t="n">
         <v>139</v>
@@ -25169,7 +25909,9 @@
       <c r="T336" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U336" s="2" t="inlineStr"/>
+      <c r="U336" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V336" t="inlineStr"/>
       <c r="W336" s="2" t="n">
         <v>138.6</v>
@@ -25242,7 +25984,9 @@
       <c r="T337" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U337" s="2" t="inlineStr"/>
+      <c r="U337" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V337" t="inlineStr"/>
       <c r="W337" s="2" t="n">
         <v>139.5</v>
@@ -25315,7 +26059,9 @@
       <c r="T338" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U338" s="2" t="inlineStr"/>
+      <c r="U338" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V338" t="inlineStr"/>
       <c r="W338" s="2" t="n">
         <v>144.2</v>
@@ -25388,7 +26134,9 @@
       <c r="T339" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U339" s="2" t="inlineStr"/>
+      <c r="U339" s="2" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V339" t="inlineStr"/>
       <c r="W339" s="2" t="n">
         <v>142.5</v>
@@ -25461,7 +26209,9 @@
       <c r="T340" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U340" s="2" t="inlineStr"/>
+      <c r="U340" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V340" t="inlineStr"/>
       <c r="W340" s="2" t="n">
         <v>143.2</v>
@@ -25534,7 +26284,9 @@
       <c r="T341" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U341" s="2" t="inlineStr"/>
+      <c r="U341" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V341" t="inlineStr"/>
       <c r="W341" s="2" t="n">
         <v>136.9</v>
@@ -25607,7 +26359,9 @@
       <c r="T342" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U342" s="2" t="inlineStr"/>
+      <c r="U342" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V342" t="inlineStr"/>
       <c r="W342" s="2" t="n">
         <v>142.1</v>
@@ -25684,7 +26438,9 @@
       <c r="T343" s="7" t="n">
         <v>21.5</v>
       </c>
-      <c r="U343" s="7" t="inlineStr"/>
+      <c r="U343" s="6" t="n">
+        <v>28.7</v>
+      </c>
       <c r="V343" s="4" t="inlineStr"/>
       <c r="W343" s="7" t="n">
         <v>152.2</v>
@@ -25757,7 +26513,9 @@
       <c r="T344" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U344" s="2" t="inlineStr"/>
+      <c r="U344" s="2" t="n">
+        <v>16</v>
+      </c>
       <c r="V344" t="inlineStr"/>
       <c r="W344" s="2" t="n">
         <v>145</v>
@@ -25830,7 +26588,9 @@
       <c r="T345" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U345" s="2" t="inlineStr"/>
+      <c r="U345" s="2" t="n">
+        <v>20.6</v>
+      </c>
       <c r="V345" t="inlineStr"/>
       <c r="W345" s="2" t="n">
         <v>142</v>
@@ -25903,7 +26663,9 @@
       <c r="T346" s="2" t="n">
         <v>22.2</v>
       </c>
-      <c r="U346" s="2" t="inlineStr"/>
+      <c r="U346" s="2" t="n">
+        <v>23.9</v>
+      </c>
       <c r="V346" t="inlineStr"/>
       <c r="W346" s="2" t="n">
         <v>143.1</v>
@@ -25976,7 +26738,9 @@
       <c r="T347" s="2" t="n">
         <v>19.4</v>
       </c>
-      <c r="U347" s="2" t="inlineStr"/>
+      <c r="U347" s="2" t="n">
+        <v>21.1</v>
+      </c>
       <c r="V347" t="inlineStr"/>
       <c r="W347" s="2" t="n">
         <v>143</v>
@@ -26049,7 +26813,9 @@
       <c r="T348" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U348" s="2" t="inlineStr"/>
+      <c r="U348" s="2" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V348" t="inlineStr"/>
       <c r="W348" s="2" t="n">
         <v>142.6</v>
@@ -26122,7 +26888,9 @@
       <c r="T349" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U349" s="2" t="inlineStr"/>
+      <c r="U349" s="2" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V349" t="inlineStr"/>
       <c r="W349" s="2" t="n">
         <v>144.3</v>
@@ -26195,7 +26963,9 @@
       <c r="T350" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U350" s="2" t="inlineStr"/>
+      <c r="U350" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V350" t="inlineStr"/>
       <c r="W350" s="2" t="n">
         <v>142.7</v>
@@ -26272,7 +27042,9 @@
       <c r="T351" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U351" s="2" t="inlineStr"/>
+      <c r="U351" s="2" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V351" t="inlineStr"/>
       <c r="W351" s="2" t="n">
         <v>142.6</v>
@@ -26345,7 +27117,9 @@
       <c r="T352" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U352" s="2" t="inlineStr"/>
+      <c r="U352" s="2" t="n">
+        <v>15.7</v>
+      </c>
       <c r="V352" t="inlineStr"/>
       <c r="W352" s="2" t="n">
         <v>146.7</v>
@@ -26422,7 +27196,9 @@
       <c r="T353" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U353" s="2" t="inlineStr"/>
+      <c r="U353" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V353" t="inlineStr"/>
       <c r="W353" s="2" t="n">
         <v>141.9</v>
@@ -26495,7 +27271,9 @@
       <c r="T354" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U354" s="2" t="inlineStr"/>
+      <c r="U354" s="2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V354" t="inlineStr"/>
       <c r="W354" s="2" t="n">
         <v>143.1</v>
@@ -26568,7 +27346,9 @@
       <c r="T355" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U355" s="2" t="inlineStr"/>
+      <c r="U355" s="2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V355" t="inlineStr"/>
       <c r="W355" s="2" t="n">
         <v>145.3</v>
@@ -26641,7 +27421,9 @@
       <c r="T356" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U356" s="2" t="inlineStr"/>
+      <c r="U356" s="2" t="n">
+        <v>16</v>
+      </c>
       <c r="V356" t="inlineStr"/>
       <c r="W356" s="2" t="n">
         <v>139.9</v>
@@ -26714,7 +27496,9 @@
       <c r="T357" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U357" s="2" t="inlineStr"/>
+      <c r="U357" s="2" t="n">
+        <v>17.6</v>
+      </c>
       <c r="V357" t="inlineStr"/>
       <c r="W357" s="2" t="n">
         <v>139.4</v>
@@ -26787,7 +27571,9 @@
       <c r="T358" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U358" s="2" t="inlineStr"/>
+      <c r="U358" s="2" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V358" t="inlineStr"/>
       <c r="W358" s="2" t="n">
         <v>144.5</v>
@@ -26860,7 +27646,9 @@
       <c r="T359" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U359" s="2" t="inlineStr"/>
+      <c r="U359" s="2" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V359" t="inlineStr"/>
       <c r="W359" s="2" t="n">
         <v>149.6</v>
@@ -26933,7 +27721,9 @@
       <c r="T360" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U360" s="2" t="inlineStr"/>
+      <c r="U360" s="2" t="n">
+        <v>13</v>
+      </c>
       <c r="V360" t="inlineStr"/>
       <c r="W360" s="2" t="n">
         <v>154.8</v>
@@ -27006,7 +27796,9 @@
       <c r="T361" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U361" s="2" t="inlineStr"/>
+      <c r="U361" s="2" t="n">
+        <v>13.2</v>
+      </c>
       <c r="V361" t="inlineStr"/>
       <c r="W361" s="2" t="n">
         <v>150</v>
@@ -27079,7 +27871,9 @@
       <c r="T362" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U362" s="2" t="inlineStr"/>
+      <c r="U362" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="V362" t="inlineStr"/>
       <c r="W362" s="2" t="n">
         <v>145.4</v>
@@ -27152,7 +27946,9 @@
       <c r="T363" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U363" s="2" t="inlineStr"/>
+      <c r="U363" s="2" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V363" t="inlineStr"/>
       <c r="W363" s="2" t="n">
         <v>145.7</v>
@@ -27225,7 +28021,9 @@
       <c r="T364" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U364" s="2" t="inlineStr"/>
+      <c r="U364" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V364" t="inlineStr"/>
       <c r="W364" s="2" t="n">
         <v>149.8</v>
@@ -27298,7 +28096,9 @@
       <c r="T365" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U365" s="2" t="inlineStr"/>
+      <c r="U365" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V365" t="inlineStr"/>
       <c r="W365" s="2" t="n">
         <v>144.7</v>
@@ -27371,7 +28171,9 @@
       <c r="T366" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U366" s="2" t="inlineStr"/>
+      <c r="U366" s="2" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V366" t="inlineStr"/>
       <c r="W366" s="2" t="n">
         <v>144.3</v>
@@ -27444,7 +28246,9 @@
       <c r="T367" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U367" s="2" t="inlineStr"/>
+      <c r="U367" s="2" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V367" t="inlineStr"/>
       <c r="W367" s="2" t="n">
         <v>145.7</v>
@@ -27517,7 +28321,9 @@
       <c r="T368" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U368" s="2" t="inlineStr"/>
+      <c r="U368" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V368" t="inlineStr"/>
       <c r="W368" s="2" t="n">
         <v>145.1</v>
@@ -27590,7 +28396,9 @@
       <c r="T369" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U369" s="2" t="inlineStr"/>
+      <c r="U369" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V369" t="inlineStr"/>
       <c r="W369" s="2" t="n">
         <v>148.5</v>
@@ -27663,7 +28471,9 @@
       <c r="T370" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U370" s="2" t="inlineStr"/>
+      <c r="U370" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V370" t="inlineStr"/>
       <c r="W370" s="2" t="n">
         <v>145.7</v>
@@ -27740,7 +28550,9 @@
       <c r="T371" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="U371" s="2" t="inlineStr"/>
+      <c r="U371" s="2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V371" t="inlineStr"/>
       <c r="W371" s="2" t="n">
         <v>147.3</v>
@@ -27813,7 +28625,9 @@
       <c r="T372" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U372" s="2" t="inlineStr"/>
+      <c r="U372" s="2" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V372" t="inlineStr"/>
       <c r="W372" s="2" t="n">
         <v>146.1</v>
@@ -27886,7 +28700,9 @@
       <c r="T373" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U373" s="2" t="inlineStr"/>
+      <c r="U373" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V373" t="inlineStr"/>
       <c r="W373" s="2" t="n">
         <v>151.7</v>
@@ -27959,7 +28775,9 @@
       <c r="T374" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U374" s="2" t="inlineStr"/>
+      <c r="U374" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V374" t="inlineStr"/>
       <c r="W374" s="2" t="n">
         <v>150.2</v>
@@ -28036,7 +28854,9 @@
       <c r="T375" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U375" s="2" t="inlineStr"/>
+      <c r="U375" s="2" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V375" t="inlineStr"/>
       <c r="W375" s="2" t="n">
         <v>145.9</v>
@@ -28109,7 +28929,9 @@
       <c r="T376" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U376" s="2" t="inlineStr"/>
+      <c r="U376" s="2" t="n">
+        <v>15.4</v>
+      </c>
       <c r="V376" t="inlineStr"/>
       <c r="W376" s="2" t="n">
         <v>147.3</v>
@@ -28182,7 +29004,9 @@
       <c r="T377" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U377" s="2" t="inlineStr"/>
+      <c r="U377" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V377" t="inlineStr"/>
       <c r="W377" s="2" t="n">
         <v>146.6</v>
@@ -28255,7 +29079,9 @@
       <c r="T378" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U378" s="2" t="inlineStr"/>
+      <c r="U378" s="2" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V378" t="inlineStr"/>
       <c r="W378" s="2" t="n">
         <v>143</v>
@@ -28328,7 +29154,9 @@
       <c r="T379" s="2" t="n">
         <v>20.7</v>
       </c>
-      <c r="U379" s="2" t="inlineStr"/>
+      <c r="U379" s="2" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V379" t="inlineStr"/>
       <c r="W379" s="2" t="n">
         <v>139.6</v>
@@ -28401,7 +29229,9 @@
       <c r="T380" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U380" s="2" t="inlineStr"/>
+      <c r="U380" s="2" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V380" t="inlineStr"/>
       <c r="W380" s="2" t="n">
         <v>139.9</v>
@@ -28474,7 +29304,9 @@
       <c r="T381" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U381" s="2" t="inlineStr"/>
+      <c r="U381" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V381" t="inlineStr"/>
       <c r="W381" s="2" t="n">
         <v>141.2</v>
@@ -28547,7 +29379,9 @@
       <c r="T382" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U382" s="2" t="inlineStr"/>
+      <c r="U382" s="2" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V382" t="inlineStr"/>
       <c r="W382" s="2" t="n">
         <v>140</v>
@@ -28620,7 +29454,9 @@
       <c r="T383" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U383" s="2" t="inlineStr"/>
+      <c r="U383" s="2" t="n">
+        <v>13.9</v>
+      </c>
       <c r="V383" t="inlineStr"/>
       <c r="W383" s="3" t="n">
         <v>126.4</v>
@@ -28693,7 +29529,9 @@
       <c r="T384" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U384" s="2" t="inlineStr"/>
+      <c r="U384" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V384" t="inlineStr"/>
       <c r="W384" s="2" t="n">
         <v>133.3</v>
@@ -28766,7 +29604,9 @@
       <c r="T385" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U385" s="2" t="inlineStr"/>
+      <c r="U385" s="2" t="n">
+        <v>12.6</v>
+      </c>
       <c r="V385" t="inlineStr"/>
       <c r="W385" s="2" t="n">
         <v>134.7</v>
@@ -28839,7 +29679,9 @@
       <c r="T386" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U386" s="2" t="inlineStr"/>
+      <c r="U386" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V386" t="inlineStr"/>
       <c r="W386" s="2" t="n">
         <v>132.6</v>
@@ -28912,7 +29754,9 @@
       <c r="T387" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U387" s="2" t="inlineStr"/>
+      <c r="U387" s="2" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V387" t="inlineStr"/>
       <c r="W387" s="2" t="n">
         <v>137.1</v>
@@ -28985,7 +29829,9 @@
       <c r="T388" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U388" s="2" t="inlineStr"/>
+      <c r="U388" s="2" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V388" t="inlineStr"/>
       <c r="W388" s="2" t="n">
         <v>135.6</v>
@@ -29058,7 +29904,9 @@
       <c r="T389" s="2" t="n">
         <v>14.6</v>
       </c>
-      <c r="U389" s="2" t="inlineStr"/>
+      <c r="U389" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V389" t="inlineStr"/>
       <c r="W389" s="2" t="n">
         <v>136.5</v>
@@ -29131,7 +29979,9 @@
       <c r="T390" s="2" t="n">
         <v>14.6</v>
       </c>
-      <c r="U390" s="2" t="inlineStr"/>
+      <c r="U390" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V390" t="inlineStr"/>
       <c r="W390" s="2" t="n">
         <v>134.4</v>
@@ -29204,7 +30054,9 @@
       <c r="T391" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U391" s="2" t="inlineStr"/>
+      <c r="U391" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="V391" t="inlineStr"/>
       <c r="W391" s="2" t="n">
         <v>138.4</v>
@@ -29277,7 +30129,9 @@
       <c r="T392" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U392" s="2" t="inlineStr"/>
+      <c r="U392" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V392" t="inlineStr"/>
       <c r="W392" s="2" t="n">
         <v>142.9</v>
@@ -29350,7 +30204,9 @@
       <c r="T393" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U393" s="2" t="inlineStr"/>
+      <c r="U393" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V393" t="inlineStr"/>
       <c r="W393" s="2" t="n">
         <v>143.6</v>
@@ -29423,7 +30279,9 @@
       <c r="T394" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U394" s="2" t="inlineStr"/>
+      <c r="U394" s="2" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="V394" t="inlineStr"/>
       <c r="W394" s="2" t="n">
         <v>142.9</v>
@@ -29496,7 +30354,9 @@
       <c r="T395" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U395" s="2" t="inlineStr"/>
+      <c r="U395" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V395" t="inlineStr"/>
       <c r="W395" s="2" t="n">
         <v>143.2</v>
@@ -29569,7 +30429,9 @@
       <c r="T396" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U396" s="2" t="inlineStr"/>
+      <c r="U396" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V396" t="inlineStr"/>
       <c r="W396" s="2" t="n">
         <v>143.9</v>
@@ -29646,7 +30508,9 @@
       <c r="T397" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U397" s="2" t="inlineStr"/>
+      <c r="U397" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="V397" t="inlineStr"/>
       <c r="W397" s="2" t="n">
         <v>145.6</v>
@@ -29719,7 +30583,9 @@
       <c r="T398" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U398" s="2" t="inlineStr"/>
+      <c r="U398" s="2" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V398" t="inlineStr"/>
       <c r="W398" s="2" t="n">
         <v>143.3</v>
@@ -29796,7 +30662,9 @@
       <c r="T399" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U399" s="2" t="inlineStr"/>
+      <c r="U399" s="2" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V399" t="inlineStr"/>
       <c r="W399" s="2" t="n">
         <v>143</v>
@@ -29869,7 +30737,9 @@
       <c r="T400" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U400" s="2" t="inlineStr"/>
+      <c r="U400" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V400" t="inlineStr"/>
       <c r="W400" s="2" t="n">
         <v>144.1</v>
@@ -29946,7 +30816,9 @@
       <c r="T401" s="2" t="n">
         <v>14.4</v>
       </c>
-      <c r="U401" s="2" t="inlineStr"/>
+      <c r="U401" s="2" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V401" t="inlineStr"/>
       <c r="W401" s="2" t="n">
         <v>149.8</v>
@@ -30019,7 +30891,9 @@
       <c r="T402" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U402" s="2" t="inlineStr"/>
+      <c r="U402" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V402" t="inlineStr"/>
       <c r="W402" s="2" t="n">
         <v>148.5</v>
@@ -30092,7 +30966,9 @@
       <c r="T403" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U403" s="2" t="inlineStr"/>
+      <c r="U403" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V403" t="inlineStr"/>
       <c r="W403" s="2" t="n">
         <v>149.2</v>
@@ -30165,7 +31041,9 @@
       <c r="T404" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U404" s="2" t="inlineStr"/>
+      <c r="U404" s="2" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V404" t="inlineStr"/>
       <c r="W404" s="2" t="n">
         <v>144.1</v>
@@ -30238,7 +31116,9 @@
       <c r="T405" s="2" t="n">
         <v>14.3</v>
       </c>
-      <c r="U405" s="2" t="inlineStr"/>
+      <c r="U405" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V405" t="inlineStr"/>
       <c r="W405" s="2" t="n">
         <v>150.6</v>
@@ -30311,7 +31191,9 @@
       <c r="T406" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U406" s="2" t="inlineStr"/>
+      <c r="U406" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="V406" t="inlineStr"/>
       <c r="W406" s="2" t="n">
         <v>151.6</v>
@@ -30388,7 +31270,9 @@
       <c r="T407" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U407" s="2" t="inlineStr"/>
+      <c r="U407" s="2" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V407" t="inlineStr"/>
       <c r="W407" s="2" t="n">
         <v>148.9</v>
@@ -30461,7 +31345,9 @@
       <c r="T408" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U408" s="2" t="inlineStr"/>
+      <c r="U408" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V408" t="inlineStr"/>
       <c r="W408" s="2" t="n">
         <v>149.2</v>
@@ -30534,7 +31420,9 @@
       <c r="T409" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U409" s="2" t="inlineStr"/>
+      <c r="U409" s="2" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V409" t="inlineStr"/>
       <c r="W409" s="2" t="n">
         <v>147</v>
@@ -30607,7 +31495,9 @@
       <c r="T410" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U410" s="2" t="inlineStr"/>
+      <c r="U410" s="2" t="n">
+        <v>13</v>
+      </c>
       <c r="V410" t="inlineStr"/>
       <c r="W410" s="2" t="n">
         <v>154.5</v>
@@ -30680,7 +31570,9 @@
       <c r="T411" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U411" s="2" t="inlineStr"/>
+      <c r="U411" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="V411" t="inlineStr"/>
       <c r="W411" s="2" t="n">
         <v>152.1</v>
@@ -30753,7 +31645,9 @@
       <c r="T412" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U412" s="2" t="inlineStr"/>
+      <c r="U412" s="2" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="n">
         <v>146.6</v>
@@ -30830,7 +31724,9 @@
       <c r="T413" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U413" s="2" t="inlineStr"/>
+      <c r="U413" s="2" t="n">
+        <v>17</v>
+      </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="n">
         <v>145.9</v>
@@ -30903,7 +31799,9 @@
       <c r="T414" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U414" s="2" t="inlineStr"/>
+      <c r="U414" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="n">
         <v>145.7</v>
@@ -30927,13 +31825,13 @@
         <v>7657.17</v>
       </c>
       <c r="E415" t="n">
-        <v>7619.74</v>
+        <v>7610.52</v>
       </c>
       <c r="F415" t="n">
-        <v>7628.49</v>
+        <v>7628.83</v>
       </c>
       <c r="G415" t="n">
-        <v>713236445</v>
+        <v>1670205000</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>-0.12</v>
@@ -30942,7 +31840,7 @@
         <v>2</v>
       </c>
       <c r="J415" t="n">
-        <v>7657.79</v>
+        <v>7657.81</v>
       </c>
       <c r="K415" t="n">
         <v>7592.09</v>
@@ -30951,10 +31849,10 @@
         <v>7412.88</v>
       </c>
       <c r="M415" t="n">
-        <v>7182.94</v>
+        <v>7182.95</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>43.27</v>
+        <v>43.29</v>
       </c>
       <c r="O415" t="n">
         <v>29</v>
@@ -30974,10 +31872,10 @@
         <v>5</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>7.5</v>
+        <v>10.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31828,31 +31828,31 @@
         <v>7610.52</v>
       </c>
       <c r="F415" t="n">
-        <v>7628.83</v>
+        <v>7650.5</v>
       </c>
       <c r="G415" t="n">
-        <v>1670205000</v>
-      </c>
-      <c r="H415" s="1" t="n">
-        <v>-0.12</v>
+        <v>5982564000</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>0.17</v>
       </c>
       <c r="I415" t="n">
         <v>2</v>
       </c>
       <c r="J415" t="n">
-        <v>7657.81</v>
+        <v>7658.89</v>
       </c>
       <c r="K415" t="n">
-        <v>7592.09</v>
+        <v>7592.45</v>
       </c>
       <c r="L415" t="n">
-        <v>7412.88</v>
+        <v>7413.06</v>
       </c>
       <c r="M415" t="n">
-        <v>7182.95</v>
+        <v>7183.05</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>43.29</v>
+        <v>45.07</v>
       </c>
       <c r="O415" t="n">
         <v>29</v>
@@ -31872,13 +31872,15 @@
         <v>5</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>15.3</v>
+        <v>14.8</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>10.1</v>
+        <v>11.4</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
+        <v>148.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31831,7 +31831,7 @@
         <v>7650.5</v>
       </c>
       <c r="G415" t="n">
-        <v>5982564000</v>
+        <v>6050102000</v>
       </c>
       <c r="H415" s="3" t="n">
         <v>0.17</v>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -8515,7 +8515,7 @@
         <v>2</v>
       </c>
       <c r="J106" t="n">
-        <v>6043.05</v>
+        <v>6043.06</v>
       </c>
       <c r="K106" t="n">
         <v>5748.09</v>
@@ -30324,7 +30324,7 @@
         <v>2</v>
       </c>
       <c r="J395" t="n">
-        <v>7668.84</v>
+        <v>7668.83</v>
       </c>
       <c r="K395" t="n">
         <v>7536.22</v>
@@ -30481,7 +30481,7 @@
         <v>7701.48</v>
       </c>
       <c r="K397" t="n">
-        <v>7539.5</v>
+        <v>7539.51</v>
       </c>
       <c r="L397" t="n">
         <v>7284.89</v>
@@ -31630,7 +31630,7 @@
         <v>45.07</v>
       </c>
       <c r="O412" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31656,6 +31656,79 @@
       <c r="W412" s="2" t="n">
         <v>148.1</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>7692.83</v>
+      </c>
+      <c r="D413" t="n">
+        <v>7756.56</v>
+      </c>
+      <c r="E413" t="n">
+        <v>7691.19</v>
+      </c>
+      <c r="F413" t="n">
+        <v>7753.2</v>
+      </c>
+      <c r="G413" t="n">
+        <v>1387626000</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2</v>
+      </c>
+      <c r="J413" t="n">
+        <v>7662.83</v>
+      </c>
+      <c r="K413" t="n">
+        <v>7599.05</v>
+      </c>
+      <c r="L413" t="n">
+        <v>7424.8</v>
+      </c>
+      <c r="M413" t="n">
+        <v>7187.67</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="O413" t="n">
+        <v>34</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -8515,7 +8515,7 @@
         <v>2</v>
       </c>
       <c r="J106" t="n">
-        <v>6043.06</v>
+        <v>6043.05</v>
       </c>
       <c r="K106" t="n">
         <v>5748.09</v>
@@ -30324,7 +30324,7 @@
         <v>2</v>
       </c>
       <c r="J395" t="n">
-        <v>7668.83</v>
+        <v>7668.84</v>
       </c>
       <c r="K395" t="n">
         <v>7536.22</v>
@@ -30481,7 +30481,7 @@
         <v>7701.48</v>
       </c>
       <c r="K397" t="n">
-        <v>7539.51</v>
+        <v>7539.5</v>
       </c>
       <c r="L397" t="n">
         <v>7284.89</v>
@@ -31672,37 +31672,37 @@
         <v>7692.83</v>
       </c>
       <c r="D413" t="n">
-        <v>7756.56</v>
+        <v>7779.22</v>
       </c>
       <c r="E413" t="n">
         <v>7691.19</v>
       </c>
       <c r="F413" t="n">
-        <v>7753.2</v>
+        <v>7764.7</v>
       </c>
       <c r="G413" t="n">
-        <v>1387626000</v>
+        <v>3278075000</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="I413" t="n">
         <v>2</v>
       </c>
       <c r="J413" t="n">
-        <v>7662.83</v>
+        <v>7663.41</v>
       </c>
       <c r="K413" t="n">
-        <v>7599.05</v>
+        <v>7599.24</v>
       </c>
       <c r="L413" t="n">
-        <v>7424.8</v>
+        <v>7424.9</v>
       </c>
       <c r="M413" t="n">
-        <v>7187.67</v>
+        <v>7187.73</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>54.8</v>
+        <v>55.53</v>
       </c>
       <c r="O413" t="n">
         <v>34</v>
@@ -31719,13 +31719,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31728,7 +31728,9 @@
         <v>10</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>142.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31606,7 +31606,7 @@
         <v>7764.7</v>
       </c>
       <c r="G412" t="n">
-        <v>3278075000</v>
+        <v>4828050000</v>
       </c>
       <c r="H412" s="3" t="n">
         <v>1.49</v>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31657,6 +31657,79 @@
         <v>142.2</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>7770.81</v>
+      </c>
+      <c r="D413" t="n">
+        <v>7782.19</v>
+      </c>
+      <c r="E413" t="n">
+        <v>7766.33</v>
+      </c>
+      <c r="F413" t="n">
+        <v>7769.45</v>
+      </c>
+      <c r="G413" t="n">
+        <v>560860582</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2</v>
+      </c>
+      <c r="J413" t="n">
+        <v>7669.24</v>
+      </c>
+      <c r="K413" t="n">
+        <v>7606.17</v>
+      </c>
+      <c r="L413" t="n">
+        <v>7435.24</v>
+      </c>
+      <c r="M413" t="n">
+        <v>7192.33</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>60.45</v>
+      </c>
+      <c r="O413" t="n">
+        <v>37</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31675,13 +31675,13 @@
         <v>7782.19</v>
       </c>
       <c r="E413" t="n">
-        <v>7766.33</v>
+        <v>7756.26</v>
       </c>
       <c r="F413" t="n">
-        <v>7769.45</v>
+        <v>7769.07</v>
       </c>
       <c r="G413" t="n">
-        <v>560860582</v>
+        <v>1722442000</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>0.06</v>
@@ -31690,10 +31690,10 @@
         <v>2</v>
       </c>
       <c r="J413" t="n">
-        <v>7669.24</v>
+        <v>7669.22</v>
       </c>
       <c r="K413" t="n">
-        <v>7606.17</v>
+        <v>7606.16</v>
       </c>
       <c r="L413" t="n">
         <v>7435.24</v>
@@ -31702,10 +31702,10 @@
         <v>7192.33</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>60.45</v>
+        <v>60.42</v>
       </c>
       <c r="O413" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31722,10 +31722,10 @@
         <v>4.95</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -8440,7 +8440,7 @@
         <v>2</v>
       </c>
       <c r="J105" t="n">
-        <v>6043.05</v>
+        <v>6043.06</v>
       </c>
       <c r="K105" t="n">
         <v>5748.09</v>
@@ -11233,7 +11233,7 @@
         <v>6219.75</v>
       </c>
       <c r="L142" t="n">
-        <v>5913.87</v>
+        <v>5913.86</v>
       </c>
       <c r="M142" t="n">
         <v>5944.69</v>
@@ -31678,34 +31678,34 @@
         <v>7756.26</v>
       </c>
       <c r="F413" t="n">
-        <v>7769.07</v>
+        <v>7764.64</v>
       </c>
       <c r="G413" t="n">
-        <v>1722442000</v>
-      </c>
-      <c r="H413" s="3" t="n">
-        <v>0.06</v>
+        <v>3164537000</v>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I413" t="n">
         <v>2</v>
       </c>
       <c r="J413" t="n">
-        <v>7669.22</v>
+        <v>7669</v>
       </c>
       <c r="K413" t="n">
-        <v>7606.16</v>
+        <v>7606.08</v>
       </c>
       <c r="L413" t="n">
-        <v>7435.24</v>
+        <v>7435.2</v>
       </c>
       <c r="M413" t="n">
-        <v>7192.33</v>
+        <v>7192.31</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>60.42</v>
+        <v>60.16</v>
       </c>
       <c r="O413" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31719,16 +31719,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.95</v>
+        <v>4.97</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>144.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31593,18 +31593,10 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="C412" t="n">
-        <v>7770.81</v>
-      </c>
-      <c r="D412" t="n">
-        <v>7782.19</v>
-      </c>
-      <c r="E412" t="n">
-        <v>7756.26</v>
-      </c>
-      <c r="F412" t="n">
-        <v>7764.64</v>
-      </c>
+      <c r="C412" t="inlineStr"/>
+      <c r="D412" t="inlineStr"/>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr"/>
       <c r="G412" t="n">
         <v>3164537000</v>
       </c>
@@ -31614,18 +31606,10 @@
       <c r="I412" t="n">
         <v>2</v>
       </c>
-      <c r="J412" t="n">
-        <v>7669</v>
-      </c>
-      <c r="K412" t="n">
-        <v>7606.08</v>
-      </c>
-      <c r="L412" t="n">
-        <v>7435.2</v>
-      </c>
-      <c r="M412" t="n">
-        <v>7192.31</v>
-      </c>
+      <c r="J412" t="inlineStr"/>
+      <c r="K412" t="inlineStr"/>
+      <c r="L412" t="inlineStr"/>
+      <c r="M412" t="inlineStr"/>
       <c r="N412" s="2" t="n">
         <v>60.16</v>
       </c>
@@ -31643,19 +31627,11 @@
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="T412" s="2" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="U412" s="2" t="n">
-        <v>8.800000000000001</v>
-      </c>
+      <c r="S412" t="inlineStr"/>
+      <c r="T412" s="2" t="inlineStr"/>
+      <c r="U412" s="2" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
-      <c r="W412" s="2" t="n">
-        <v>144.8</v>
-      </c>
+      <c r="W412" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31590,31 +31590,47 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>7761.94</v>
+      </c>
+      <c r="D412" t="n">
+        <v>7761.94</v>
+      </c>
+      <c r="E412" t="n">
+        <v>7711.49</v>
+      </c>
+      <c r="F412" t="n">
+        <v>7711.82</v>
+      </c>
       <c r="G412" t="n">
-        <v>3164537000</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>1150265000</v>
+      </c>
+      <c r="H412" s="1" t="n">
+        <v>-0.68</v>
       </c>
       <c r="I412" t="n">
         <v>2</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>7666.36</v>
+      </c>
+      <c r="K412" t="n">
+        <v>7605.2</v>
+      </c>
+      <c r="L412" t="n">
+        <v>7434.76</v>
+      </c>
+      <c r="M412" t="n">
+        <v>7192.04</v>
+      </c>
       <c r="N412" s="2" t="n">
-        <v>60.16</v>
+        <v>55.67</v>
       </c>
       <c r="O412" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31623,13 +31639,19 @@
       </c>
       <c r="Q412" t="inlineStr">
         <is>
-          <t>BUY STOP</t>
+          <t>2x BUY</t>
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="inlineStr"/>
-      <c r="T412" s="2" t="inlineStr"/>
-      <c r="U412" s="2" t="inlineStr"/>
+      <c r="S412" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="T412" s="2" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="U412" s="2" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="inlineStr"/>
     </row>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -8365,7 +8365,7 @@
         <v>2</v>
       </c>
       <c r="J104" t="n">
-        <v>6043.06</v>
+        <v>6043.05</v>
       </c>
       <c r="K104" t="n">
         <v>5748.09</v>
@@ -11158,7 +11158,7 @@
         <v>6219.75</v>
       </c>
       <c r="L141" t="n">
-        <v>5913.86</v>
+        <v>5913.87</v>
       </c>
       <c r="M141" t="n">
         <v>5944.69</v>
@@ -31600,37 +31600,37 @@
         <v>7761.94</v>
       </c>
       <c r="E412" t="n">
-        <v>7711.49</v>
+        <v>7694.89</v>
       </c>
       <c r="F412" t="n">
-        <v>7711.82</v>
+        <v>7706.39</v>
       </c>
       <c r="G412" t="n">
-        <v>1150265000</v>
+        <v>2767069000</v>
       </c>
       <c r="H412" s="1" t="n">
-        <v>-0.68</v>
+        <v>-0.75</v>
       </c>
       <c r="I412" t="n">
         <v>2</v>
       </c>
       <c r="J412" t="n">
-        <v>7666.36</v>
+        <v>7666.08</v>
       </c>
       <c r="K412" t="n">
-        <v>7605.2</v>
+        <v>7605.11</v>
       </c>
       <c r="L412" t="n">
-        <v>7434.76</v>
+        <v>7434.72</v>
       </c>
       <c r="M412" t="n">
-        <v>7192.04</v>
+        <v>7192.01</v>
       </c>
       <c r="N412" s="2" t="n">
-        <v>55.67</v>
+        <v>55.25</v>
       </c>
       <c r="O412" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31644,13 +31644,13 @@
       </c>
       <c r="R412" t="inlineStr"/>
       <c r="S412" t="n">
-        <v>5.09</v>
+        <v>5.11</v>
       </c>
       <c r="T412" s="2" t="n">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="U412" s="2" t="n">
-        <v>8.4</v>
+        <v>10.6</v>
       </c>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="inlineStr"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31603,31 +31603,31 @@
         <v>7694.89</v>
       </c>
       <c r="F412" t="n">
-        <v>7706.39</v>
+        <v>7706.03</v>
       </c>
       <c r="G412" t="n">
-        <v>2767069000</v>
+        <v>2977393000</v>
       </c>
       <c r="H412" s="1" t="n">
-        <v>-0.75</v>
+        <v>-0.76</v>
       </c>
       <c r="I412" t="n">
         <v>2</v>
       </c>
       <c r="J412" t="n">
-        <v>7666.08</v>
+        <v>7666.07</v>
       </c>
       <c r="K412" t="n">
         <v>7605.11</v>
       </c>
       <c r="L412" t="n">
-        <v>7434.72</v>
+        <v>7434.71</v>
       </c>
       <c r="M412" t="n">
         <v>7192.01</v>
       </c>
       <c r="N412" s="2" t="n">
-        <v>55.25</v>
+        <v>55.22</v>
       </c>
       <c r="O412" t="n">
         <v>35</v>
@@ -31650,10 +31650,12 @@
         <v>15.2</v>
       </c>
       <c r="U412" s="2" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="V412" t="inlineStr"/>
-      <c r="W412" s="2" t="inlineStr"/>
+      <c r="W412" s="2" t="n">
+        <v>146.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31606,7 +31606,7 @@
         <v>7706.03</v>
       </c>
       <c r="G412" t="n">
-        <v>2977393000</v>
+        <v>5110910000</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>-0.76</v>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31630,7 +31630,7 @@
         <v>55.22</v>
       </c>
       <c r="O412" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31656,6 +31656,79 @@
       <c r="W412" s="2" t="n">
         <v>146.1</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>7666.99</v>
+      </c>
+      <c r="D413" t="n">
+        <v>7719.01</v>
+      </c>
+      <c r="E413" t="n">
+        <v>7662.57</v>
+      </c>
+      <c r="F413" t="n">
+        <v>7702.16</v>
+      </c>
+      <c r="G413" t="n">
+        <v>1625714000</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2</v>
+      </c>
+      <c r="J413" t="n">
+        <v>7667.31</v>
+      </c>
+      <c r="K413" t="n">
+        <v>7609.47</v>
+      </c>
+      <c r="L413" t="n">
+        <v>7444.1</v>
+      </c>
+      <c r="M413" t="n">
+        <v>7196.24</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="O413" t="n">
+        <v>35</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31678,34 +31678,34 @@
         <v>7662.57</v>
       </c>
       <c r="F413" t="n">
-        <v>7702.16</v>
+        <v>7704.13</v>
       </c>
       <c r="G413" t="n">
-        <v>1625714000</v>
+        <v>2911730000</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="I413" t="n">
         <v>2</v>
       </c>
       <c r="J413" t="n">
-        <v>7667.31</v>
+        <v>7667.41</v>
       </c>
       <c r="K413" t="n">
-        <v>7609.47</v>
+        <v>7609.5</v>
       </c>
       <c r="L413" t="n">
-        <v>7444.1</v>
+        <v>7444.12</v>
       </c>
       <c r="M413" t="n">
-        <v>7196.24</v>
+        <v>7196.25</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>52.6</v>
+        <v>52.76</v>
       </c>
       <c r="O413" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31719,16 +31719,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.18</v>
+        <v>5.16</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>11.6</v>
+        <v>12.1</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>146</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31681,7 +31681,7 @@
         <v>7704.13</v>
       </c>
       <c r="G413" t="n">
-        <v>2911730000</v>
+        <v>5316390000</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-0.02</v>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31590,47 +31590,47 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>7761.94</v>
+        <v>7770.81</v>
       </c>
       <c r="D412" t="n">
-        <v>7761.94</v>
+        <v>7782.19</v>
       </c>
       <c r="E412" t="n">
-        <v>7694.89</v>
+        <v>7756.26</v>
       </c>
       <c r="F412" t="n">
-        <v>7706.03</v>
+        <v>7764.64</v>
       </c>
       <c r="G412" t="n">
-        <v>5110910000</v>
-      </c>
-      <c r="H412" s="1" t="n">
-        <v>-0.76</v>
+        <v>5286270000</v>
+      </c>
+      <c r="H412" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I412" t="n">
         <v>2</v>
       </c>
       <c r="J412" t="n">
-        <v>7666.07</v>
+        <v>7669</v>
       </c>
       <c r="K412" t="n">
-        <v>7605.11</v>
+        <v>7606.08</v>
       </c>
       <c r="L412" t="n">
-        <v>7434.71</v>
+        <v>7435.2</v>
       </c>
       <c r="M412" t="n">
-        <v>7192.01</v>
+        <v>7192.31</v>
       </c>
       <c r="N412" s="2" t="n">
-        <v>55.22</v>
+        <v>60.16</v>
       </c>
       <c r="O412" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31639,22 +31639,22 @@
       </c>
       <c r="Q412" t="inlineStr">
         <is>
-          <t>2x BUY</t>
+          <t>BUY STOP</t>
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
       <c r="S412" t="n">
-        <v>5.11</v>
+        <v>4.97</v>
       </c>
       <c r="T412" s="2" t="n">
-        <v>15.2</v>
+        <v>14.2</v>
       </c>
       <c r="U412" s="2" t="n">
-        <v>10.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="n">
-        <v>146.1</v>
+        <v>144.8</v>
       </c>
     </row>
     <row r="413">
@@ -31665,47 +31665,47 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C413" t="n">
-        <v>7666.99</v>
+        <v>7761.94</v>
       </c>
       <c r="D413" t="n">
-        <v>7719.01</v>
+        <v>7761.94</v>
       </c>
       <c r="E413" t="n">
-        <v>7662.57</v>
+        <v>7694.89</v>
       </c>
       <c r="F413" t="n">
-        <v>7704.13</v>
+        <v>7706.03</v>
       </c>
       <c r="G413" t="n">
-        <v>5316390000</v>
+        <v>5110910000</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.75</v>
       </c>
       <c r="I413" t="n">
         <v>2</v>
       </c>
       <c r="J413" t="n">
-        <v>7667.41</v>
+        <v>7670.43</v>
       </c>
       <c r="K413" t="n">
-        <v>7609.5</v>
+        <v>7610.51</v>
       </c>
       <c r="L413" t="n">
-        <v>7444.12</v>
+        <v>7444.62</v>
       </c>
       <c r="M413" t="n">
-        <v>7196.25</v>
+        <v>7196.55</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>52.76</v>
+        <v>52.9</v>
       </c>
       <c r="O413" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31719,16 +31719,91 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.16</v>
+        <v>5.11</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.7</v>
+        <v>15.2</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>12.1</v>
+        <v>10.7</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="n">
+        <v>146.1</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>7666.99</v>
+      </c>
+      <c r="D414" t="n">
+        <v>7719.01</v>
+      </c>
+      <c r="E414" t="n">
+        <v>7662.57</v>
+      </c>
+      <c r="F414" t="n">
+        <v>7704.13</v>
+      </c>
+      <c r="G414" t="n">
+        <v>5316390000</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>7671.86</v>
+      </c>
+      <c r="K414" t="n">
+        <v>7613.92</v>
+      </c>
+      <c r="L414" t="n">
+        <v>7453.97</v>
+      </c>
+      <c r="M414" t="n">
+        <v>7200.72</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>46.37</v>
+      </c>
+      <c r="O414" t="n">
+        <v>36</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
         <v>146</v>
       </c>
     </row>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31807,6 +31807,79 @@
         <v>146</v>
       </c>
     </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>7709.86</v>
+      </c>
+      <c r="D415" t="n">
+        <v>7749.3</v>
+      </c>
+      <c r="E415" t="n">
+        <v>7693.08</v>
+      </c>
+      <c r="F415" t="n">
+        <v>7743.56</v>
+      </c>
+      <c r="G415" t="n">
+        <v>1469867000</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I415" t="n">
+        <v>2</v>
+      </c>
+      <c r="J415" t="n">
+        <v>7672.48</v>
+      </c>
+      <c r="K415" t="n">
+        <v>7618.26</v>
+      </c>
+      <c r="L415" t="n">
+        <v>7463.4</v>
+      </c>
+      <c r="M415" t="n">
+        <v>7205.2</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>52.05</v>
+      </c>
+      <c r="O415" t="n">
+        <v>38</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31822,16 +31822,16 @@
         <v>7709.86</v>
       </c>
       <c r="D415" t="n">
-        <v>7749.3</v>
+        <v>7752.07</v>
       </c>
       <c r="E415" t="n">
         <v>7693.08</v>
       </c>
       <c r="F415" t="n">
-        <v>7743.56</v>
+        <v>7743.41</v>
       </c>
       <c r="G415" t="n">
-        <v>1469867000</v>
+        <v>2644756000</v>
       </c>
       <c r="H415" s="3" t="n">
         <v>0.51</v>
@@ -31852,10 +31852,10 @@
         <v>7205.2</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>52.05</v>
+        <v>52.03</v>
       </c>
       <c r="O415" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31869,16 +31869,18 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>11.2</v>
+        <v>12.5</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
+        <v>144.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31756,7 +31756,7 @@
         <v>7743.41</v>
       </c>
       <c r="G414" t="n">
-        <v>2644756000</v>
+        <v>4499180000</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>0.51</v>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -8140,7 +8140,7 @@
         <v>2</v>
       </c>
       <c r="J101" t="n">
-        <v>6043.05</v>
+        <v>6043.06</v>
       </c>
       <c r="K101" t="n">
         <v>5748.09</v>
@@ -10933,7 +10933,7 @@
         <v>6219.75</v>
       </c>
       <c r="L138" t="n">
-        <v>5913.87</v>
+        <v>5913.86</v>
       </c>
       <c r="M138" t="n">
         <v>5944.69</v>
@@ -30106,7 +30106,7 @@
         <v>7701.48</v>
       </c>
       <c r="K392" t="n">
-        <v>7539.5</v>
+        <v>7539.51</v>
       </c>
       <c r="L392" t="n">
         <v>7284.89</v>
@@ -31656,6 +31656,79 @@
       <c r="W412" s="2" t="n">
         <v>144.9</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>7721.7</v>
+      </c>
+      <c r="D413" t="n">
+        <v>7721.7</v>
+      </c>
+      <c r="E413" t="n">
+        <v>7666.6</v>
+      </c>
+      <c r="F413" t="n">
+        <v>7675.61</v>
+      </c>
+      <c r="G413" t="n">
+        <v>736703739</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2</v>
+      </c>
+      <c r="J413" t="n">
+        <v>7670.67</v>
+      </c>
+      <c r="K413" t="n">
+        <v>7621.47</v>
+      </c>
+      <c r="L413" t="n">
+        <v>7472.22</v>
+      </c>
+      <c r="M413" t="n">
+        <v>7209.38</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>50.17</v>
+      </c>
+      <c r="O413" t="n">
+        <v>34</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -10933,7 +10933,7 @@
         <v>6219.75</v>
       </c>
       <c r="L138" t="n">
-        <v>5913.86</v>
+        <v>5913.87</v>
       </c>
       <c r="M138" t="n">
         <v>5944.69</v>
@@ -29949,7 +29949,7 @@
         <v>2</v>
       </c>
       <c r="J390" t="n">
-        <v>7668.84</v>
+        <v>7668.83</v>
       </c>
       <c r="K390" t="n">
         <v>7536.22</v>
@@ -30106,7 +30106,7 @@
         <v>7701.48</v>
       </c>
       <c r="K392" t="n">
-        <v>7539.51</v>
+        <v>7539.5</v>
       </c>
       <c r="L392" t="n">
         <v>7284.89</v>
@@ -31672,37 +31672,37 @@
         <v>7721.7</v>
       </c>
       <c r="D413" t="n">
-        <v>7721.7</v>
+        <v>7724.15</v>
       </c>
       <c r="E413" t="n">
         <v>7666.6</v>
       </c>
       <c r="F413" t="n">
-        <v>7675.61</v>
+        <v>7683.69</v>
       </c>
       <c r="G413" t="n">
-        <v>736703739</v>
+        <v>2909239000</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.77</v>
       </c>
       <c r="I413" t="n">
         <v>2</v>
       </c>
       <c r="J413" t="n">
-        <v>7670.67</v>
+        <v>7671.07</v>
       </c>
       <c r="K413" t="n">
-        <v>7621.47</v>
+        <v>7621.6</v>
       </c>
       <c r="L413" t="n">
-        <v>7472.22</v>
+        <v>7472.29</v>
       </c>
       <c r="M413" t="n">
-        <v>7209.38</v>
+        <v>7209.42</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>50.17</v>
+        <v>50.81</v>
       </c>
       <c r="O413" t="n">
         <v>34</v>
@@ -31719,16 +31719,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>16.5</v>
+        <v>16.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>9.5</v>
+        <v>11.3</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>146.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31606,7 +31606,7 @@
         <v>7683.69</v>
       </c>
       <c r="G412" t="n">
-        <v>2909239000</v>
+        <v>5129710000</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>-0.77</v>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31657,6 +31657,83 @@
         <v>146.2</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>7699.6</v>
+      </c>
+      <c r="D413" t="n">
+        <v>7699.6</v>
+      </c>
+      <c r="E413" t="n">
+        <v>7655.55</v>
+      </c>
+      <c r="F413" t="n">
+        <v>7659.15</v>
+      </c>
+      <c r="G413" t="n">
+        <v>817698344</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2</v>
+      </c>
+      <c r="J413" t="n">
+        <v>7669.72</v>
+      </c>
+      <c r="K413" t="n">
+        <v>7623.63</v>
+      </c>
+      <c r="L413" t="n">
+        <v>7479.59</v>
+      </c>
+      <c r="M413" t="n">
+        <v>7213.28</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="O413" t="n">
+        <v>33</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
+      <c r="S413" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -8065,7 +8065,7 @@
         <v>2</v>
       </c>
       <c r="J100" t="n">
-        <v>6043.06</v>
+        <v>6043.05</v>
       </c>
       <c r="K100" t="n">
         <v>5748.09</v>
@@ -31675,37 +31675,37 @@
         <v>7699.6</v>
       </c>
       <c r="E413" t="n">
-        <v>7655.55</v>
+        <v>7653.55</v>
       </c>
       <c r="F413" t="n">
-        <v>7659.15</v>
+        <v>7670.84</v>
       </c>
       <c r="G413" t="n">
-        <v>817698344</v>
+        <v>2759055000</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>-0.32</v>
+        <v>-0.17</v>
       </c>
       <c r="I413" t="n">
         <v>2</v>
       </c>
       <c r="J413" t="n">
-        <v>7669.72</v>
+        <v>7670.31</v>
       </c>
       <c r="K413" t="n">
-        <v>7623.63</v>
+        <v>7623.83</v>
       </c>
       <c r="L413" t="n">
-        <v>7479.59</v>
+        <v>7479.69</v>
       </c>
       <c r="M413" t="n">
-        <v>7213.28</v>
+        <v>7213.34</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>51.86</v>
+        <v>52.87</v>
       </c>
       <c r="O413" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31717,19 +31717,15 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R413" t="inlineStr">
-        <is>
-          <t>1st: MA20, 10% cash</t>
-        </is>
-      </c>
+      <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31606,7 +31606,7 @@
         <v>7670.84</v>
       </c>
       <c r="G412" t="n">
-        <v>2775639000</v>
+        <v>5023590000</v>
       </c>
       <c r="H412" s="3" t="n">
         <v>-0.17</v>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31630,7 +31630,7 @@
         <v>52.87</v>
       </c>
       <c r="O412" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31657,6 +31657,79 @@
         <v>144.6</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>7688.99</v>
+      </c>
+      <c r="D413" t="n">
+        <v>7722.88</v>
+      </c>
+      <c r="E413" t="n">
+        <v>7688.99</v>
+      </c>
+      <c r="F413" t="n">
+        <v>7691.47</v>
+      </c>
+      <c r="G413" t="n">
+        <v>1572133000</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2</v>
+      </c>
+      <c r="J413" t="n">
+        <v>7673.31</v>
+      </c>
+      <c r="K413" t="n">
+        <v>7626.95</v>
+      </c>
+      <c r="L413" t="n">
+        <v>7486.91</v>
+      </c>
+      <c r="M413" t="n">
+        <v>7217.29</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="O413" t="n">
+        <v>33</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -608,7 +608,7 @@
         <v>0.67</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J2" t="n">
         <v>6020.98</v>
@@ -683,7 +683,7 @@
         <v>0.03</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J3" t="n">
         <v>6032.59</v>
@@ -758,7 +758,7 @@
         <v>-0.27</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J4" t="n">
         <v>6043.04</v>
@@ -833,7 +833,7 @@
         <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J5" t="n">
         <v>6051.3</v>
@@ -908,7 +908,7 @@
         <v>-0.01</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J6" t="n">
         <v>6060.17</v>
@@ -983,7 +983,7 @@
         <v>0.24</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="n">
         <v>6066.81</v>
@@ -1058,7 +1058,7 @@
         <v>0.24</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
         <v>6071.56</v>
@@ -1133,7 +1133,7 @@
         <v>-0.43</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
         <v>6073.11</v>
@@ -1208,7 +1208,7 @@
         <v>-1.71</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
         <v>6067.84</v>
@@ -1287,7 +1287,7 @@
         <v>-0.5</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J11" t="n">
         <v>6061.94</v>
@@ -1362,7 +1362,7 @@
         <v>-0.47</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J12" t="n">
         <v>6059.08</v>
@@ -1437,7 +1437,7 @@
         <v>0.01</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J13" t="n">
         <v>6053.5</v>
@@ -1512,7 +1512,7 @@
         <v>-1.59</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
         <v>6044.62</v>
@@ -1591,7 +1591,7 @@
         <v>1.59</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
         <v>6038.78</v>
@@ -1666,7 +1666,7 @@
         <v>-1.76</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J16" t="n">
         <v>6029.24</v>
@@ -1745,7 +1745,7 @@
         <v>-1.22</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J17" t="n">
         <v>6018.42</v>
@@ -1820,7 +1820,7 @@
         <v>1.12</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
         <v>6008.66</v>
@@ -1895,7 +1895,7 @@
         <v>-1.78</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
         <v>5992.51</v>
@@ -1970,7 +1970,7 @@
         <v>0.55</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
         <v>5976.84</v>
@@ -2045,7 +2045,7 @@
         <v>-2.7</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>5956.27</v>
@@ -2128,7 +2128,7 @@
         <v>-0.76</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>5931.55</v>
@@ -2211,7 +2211,7 @@
         <v>0.49</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>5908.09</v>
@@ -2290,7 +2290,7 @@
         <v>-1.39</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
         <v>5881.57</v>
@@ -2369,7 +2369,7 @@
         <v>2.13</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>5857.76</v>
@@ -2444,7 +2444,7 @@
         <v>0.64</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>5835.79</v>
@@ -2519,7 +2519,7 @@
         <v>-1.07</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>5810.04</v>
@@ -2594,7 +2594,7 @@
         <v>1.08</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>5786.6</v>
@@ -2669,7 +2669,7 @@
         <v>-0.22</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>5763.87</v>
@@ -2744,7 +2744,7 @@
         <v>0.08</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>5746.59</v>
@@ -2819,7 +2819,7 @@
         <v>1.76</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>5735.8</v>
@@ -2894,7 +2894,7 @@
         <v>0.16</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>5726.87</v>
@@ -2969,7 +2969,7 @@
         <v>-1.12</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
         <v>5714.68</v>
@@ -3048,7 +3048,7 @@
         <v>-0.33</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J34" t="n">
         <v>5706.27</v>
@@ -3094,77 +3094,77 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>2025-03-28</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="4" t="n">
         <v>5679.2</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="4" t="n">
         <v>5685.89</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="4" t="n">
         <v>5572.42</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35" s="4" t="n">
         <v>5580.94</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35" s="4" t="n">
         <v>4513330000</v>
       </c>
-      <c r="H35" s="3" t="n">
+      <c r="H35" s="5" t="n">
         <v>-1.97</v>
       </c>
-      <c r="I35" t="n">
-        <v>2</v>
-      </c>
-      <c r="J35" t="n">
+      <c r="I35" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J35" s="4" t="n">
         <v>5687.59</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K35" s="4" t="n">
         <v>5899.31</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L35" s="4" t="n">
         <v>5908.41</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M35" s="4" t="n">
         <v>5759.04</v>
       </c>
-      <c r="N35" s="2" t="n">
+      <c r="N35" s="7" t="n">
         <v>47.74</v>
       </c>
-      <c r="O35" t="n">
+      <c r="O35" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="P35" s="4" t="inlineStr">
         <is>
           <t>fear</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q35" s="4" t="inlineStr">
         <is>
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="n">
+      <c r="R35" s="4" t="inlineStr"/>
+      <c r="S35" s="4" t="n">
         <v>4.26</v>
       </c>
-      <c r="T35" s="2" t="n">
+      <c r="T35" s="7" t="n">
         <v>21.6</v>
       </c>
-      <c r="U35" s="1" t="n">
+      <c r="U35" s="6" t="n">
         <v>25.4</v>
       </c>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" s="2" t="n">
+      <c r="V35" s="4" t="inlineStr"/>
+      <c r="W35" s="7" t="n">
         <v>139</v>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
         <v>0.55</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J36" t="n">
         <v>5675.7</v>
@@ -3273,7 +3273,7 @@
         <v>0.38</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>5668.44</v>
@@ -3348,7 +3348,7 @@
         <v>0.67</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J38" t="n">
         <v>5659.86</v>
@@ -3423,7 +3423,7 @@
         <v>-4.84</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>5642.76</v>
@@ -3506,7 +3506,7 @@
         <v>-5.97</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>5607.95</v>
@@ -3589,7 +3589,7 @@
         <v>-0.23</v>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J41" t="n">
         <v>5580.34</v>
@@ -3672,7 +3672,7 @@
         <v>-1.57</v>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J42" t="n">
         <v>5550.87</v>
@@ -3755,7 +3755,7 @@
         <v>9.52</v>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J43" t="n">
         <v>5543.75</v>
@@ -3834,7 +3834,7 @@
         <v>-3.46</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>5531.08</v>
@@ -3913,7 +3913,7 @@
         <v>1.81</v>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J45" t="n">
         <v>5517.3</v>
@@ -3992,7 +3992,7 @@
         <v>0.79</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>5503.84</v>
@@ -4067,7 +4067,7 @@
         <v>-0.17</v>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>5492.94</v>
@@ -4142,7 +4142,7 @@
         <v>-2.24</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>5472.96</v>
@@ -4221,7 +4221,7 @@
         <v>0.13</v>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>5453.95</v>
@@ -4300,7 +4300,7 @@
         <v>-2.36</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>5428.48</v>
@@ -4375,7 +4375,7 @@
         <v>2.51</v>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J51" t="n">
         <v>5404.49</v>
@@ -4450,7 +4450,7 @@
         <v>1.67</v>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J52" t="n">
         <v>5384.45</v>
@@ -4529,7 +4529,7 @@
         <v>2.03</v>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J53" t="n">
         <v>5373.08</v>
@@ -4604,7 +4604,7 @@
         <v>0.74</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J54" t="n">
         <v>5364.68</v>
@@ -4679,7 +4679,7 @@
         <v>0.06</v>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J55" t="n">
         <v>5362.07</v>
@@ -4754,7 +4754,7 @@
         <v>0.58</v>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J56" t="n">
         <v>5359.52</v>
@@ -4829,7 +4829,7 @@
         <v>0.15</v>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J57" t="n">
         <v>5356.32</v>
@@ -4904,7 +4904,7 @@
         <v>0.63</v>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J58" t="n">
         <v>5352.98</v>
@@ -4979,7 +4979,7 @@
         <v>1.47</v>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J59" t="n">
         <v>5367.48</v>
@@ -5054,7 +5054,7 @@
         <v>-0.64</v>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J60" t="n">
         <v>5396.3</v>
@@ -5133,7 +5133,7 @@
         <v>-0.77</v>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>5423.53</v>
@@ -5208,7 +5208,7 @@
         <v>0.43</v>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J62" t="n">
         <v>5455.96</v>
@@ -5283,7 +5283,7 @@
         <v>0.58</v>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>5466.31</v>
@@ -5358,7 +5358,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J64" t="n">
         <v>5485.9</v>
@@ -5433,7 +5433,7 @@
         <v>3.26</v>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>5509.94</v>
@@ -5508,7 +5508,7 @@
         <v>0.72</v>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>5533.97</v>
@@ -5583,7 +5583,7 @@
         <v>0.1</v>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>5558.77</v>
@@ -5658,7 +5658,7 @@
         <v>0.41</v>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>5590.83</v>
@@ -5733,7 +5733,7 @@
         <v>0.7</v>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>5624.62</v>
@@ -5808,7 +5808,7 @@
         <v>0.09</v>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>5664.88</v>
@@ -5883,7 +5883,7 @@
         <v>-0.39</v>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>5697.52</v>
@@ -5958,7 +5958,7 @@
         <v>-1.61</v>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J72" t="n">
         <v>5720.96</v>
@@ -6033,7 +6033,7 @@
         <v>-0.04</v>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>5738.82</v>
@@ -6108,7 +6108,7 @@
         <v>-0.67</v>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J74" t="n">
         <v>5752.7</v>
@@ -6187,7 +6187,7 @@
         <v>2.05</v>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J75" t="n">
         <v>5772.34</v>
@@ -6262,7 +6262,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J76" t="n">
         <v>5788.73</v>
@@ -6337,7 +6337,7 @@
         <v>0.4</v>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J77" t="n">
         <v>5805.88</v>
@@ -6412,7 +6412,7 @@
         <v>-0.01</v>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J78" t="n">
         <v>5821.26</v>
@@ -6487,7 +6487,7 @@
         <v>0.41</v>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J79" t="n">
         <v>5833.72</v>
@@ -6562,7 +6562,7 @@
         <v>0.58</v>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J80" t="n">
         <v>5849.72</v>
@@ -6637,7 +6637,7 @@
         <v>0.01</v>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J81" t="n">
         <v>5867.92</v>
@@ -6712,7 +6712,7 @@
         <v>-0.53</v>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J82" t="n">
         <v>5883.32</v>
@@ -6787,7 +6787,7 @@
         <v>1.03</v>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J83" t="n">
         <v>5900.14</v>
@@ -6862,7 +6862,7 @@
         <v>0.09</v>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J84" t="n">
         <v>5917.44</v>
@@ -6937,7 +6937,7 @@
         <v>0.55</v>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J85" t="n">
         <v>5927.17</v>
@@ -7012,7 +7012,7 @@
         <v>-0.27</v>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J86" t="n">
         <v>5933.95</v>
@@ -7087,7 +7087,7 @@
         <v>0.38</v>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J87" t="n">
         <v>5941.59</v>
@@ -7162,7 +7162,7 @@
         <v>-1.13</v>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J88" t="n">
         <v>5944.59</v>
@@ -7237,7 +7237,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J89" t="n">
         <v>5948.32</v>
@@ -7312,7 +7312,7 @@
         <v>-0.84</v>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J90" t="n">
         <v>5949.28</v>
@@ -7387,7 +7387,7 @@
         <v>-0.03</v>
       </c>
       <c r="I91" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J91" t="n">
         <v>5951.3</v>
@@ -7462,7 +7462,7 @@
         <v>-0.22</v>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J92" t="n">
         <v>5957.46</v>
@@ -7537,7 +7537,7 @@
         <v>0.96</v>
       </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J93" t="n">
         <v>5966.62</v>
@@ -7612,7 +7612,7 @@
         <v>1.11</v>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J94" t="n">
         <v>5981.09</v>
@@ -7687,7 +7687,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J95" t="n">
         <v>5989.62</v>
@@ -7762,7 +7762,7 @@
         <v>0.8</v>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J96" t="n">
         <v>6002.24</v>
@@ -7837,7 +7837,7 @@
         <v>0.52</v>
       </c>
       <c r="I97" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J97" t="n">
         <v>6015.29</v>
@@ -7912,7 +7912,7 @@
         <v>0.52</v>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J98" t="n">
         <v>6029.95</v>
@@ -7987,10 +7987,10 @@
         <v>-0.11</v>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J99" t="n">
-        <v>6043.05</v>
+        <v>6043.06</v>
       </c>
       <c r="K99" t="n">
         <v>5748.09</v>
@@ -8062,7 +8062,7 @@
         <v>0.47</v>
       </c>
       <c r="I100" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J100" t="n">
         <v>6055.91</v>
@@ -8137,7 +8137,7 @@
         <v>0.83</v>
       </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J101" t="n">
         <v>6071.33</v>
@@ -8212,7 +8212,7 @@
         <v>-0.79</v>
       </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J102" t="n">
         <v>6085.87</v>
@@ -8287,7 +8287,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="I103" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J103" t="n">
         <v>6097.13</v>
@@ -8362,7 +8362,7 @@
         <v>0.61</v>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J104" t="n">
         <v>6110</v>
@@ -8437,7 +8437,7 @@
         <v>0.27</v>
       </c>
       <c r="I105" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J105" t="n">
         <v>6122.08</v>
@@ -8512,7 +8512,7 @@
         <v>-0.33</v>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J106" t="n">
         <v>6133.95</v>
@@ -8587,7 +8587,7 @@
         <v>0.14</v>
       </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J107" t="n">
         <v>6145.12</v>
@@ -8662,7 +8662,7 @@
         <v>-0.4</v>
       </c>
       <c r="I108" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J108" t="n">
         <v>6158.46</v>
@@ -8737,7 +8737,7 @@
         <v>0.32</v>
       </c>
       <c r="I109" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J109" t="n">
         <v>6169.99</v>
@@ -8812,7 +8812,7 @@
         <v>0.54</v>
       </c>
       <c r="I110" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J110" t="n">
         <v>6185.72</v>
@@ -8887,7 +8887,7 @@
         <v>-0.01</v>
       </c>
       <c r="I111" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J111" t="n">
         <v>6201.52</v>
@@ -8962,7 +8962,7 @@
         <v>0.14</v>
       </c>
       <c r="I112" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J112" t="n">
         <v>6218.4</v>
@@ -9037,7 +9037,7 @@
         <v>0.06</v>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J113" t="n">
         <v>6232.63</v>
@@ -9112,7 +9112,7 @@
         <v>0.78</v>
       </c>
       <c r="I114" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J114" t="n">
         <v>6245.96</v>
@@ -9187,7 +9187,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I115" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J115" t="n">
         <v>6259.52</v>
@@ -9262,7 +9262,7 @@
         <v>0.4</v>
       </c>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J116" t="n">
         <v>6271.9</v>
@@ -9337,7 +9337,7 @@
         <v>0.02</v>
       </c>
       <c r="I117" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J117" t="n">
         <v>6282.74</v>
@@ -9412,7 +9412,7 @@
         <v>-0.3</v>
       </c>
       <c r="I118" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J118" t="n">
         <v>6291.03</v>
@@ -9487,7 +9487,7 @@
         <v>-0.12</v>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J119" t="n">
         <v>6299.28</v>
@@ -9562,7 +9562,7 @@
         <v>-0.37</v>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J120" t="n">
         <v>6304.88</v>
@@ -9637,7 +9637,7 @@
         <v>-1.6</v>
       </c>
       <c r="I121" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J121" t="n">
         <v>6302.81</v>
@@ -9716,7 +9716,7 @@
         <v>1.47</v>
       </c>
       <c r="I122" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J122" t="n">
         <v>6307.81</v>
@@ -9791,7 +9791,7 @@
         <v>-0.49</v>
       </c>
       <c r="I123" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J123" t="n">
         <v>6311.49</v>
@@ -9870,7 +9870,7 @@
         <v>0.73</v>
       </c>
       <c r="I124" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J124" t="n">
         <v>6315.58</v>
@@ -9945,7 +9945,7 @@
         <v>-0.08</v>
       </c>
       <c r="I125" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J125" t="n">
         <v>6318.56</v>
@@ -10020,7 +10020,7 @@
         <v>0.78</v>
       </c>
       <c r="I126" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J126" t="n">
         <v>6325.04</v>
@@ -10095,7 +10095,7 @@
         <v>-0.25</v>
       </c>
       <c r="I127" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J127" t="n">
         <v>6330.29</v>
@@ -10170,7 +10170,7 @@
         <v>1.13</v>
       </c>
       <c r="I128" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J128" t="n">
         <v>6340.39</v>
@@ -10245,7 +10245,7 @@
         <v>0.32</v>
       </c>
       <c r="I129" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J129" t="n">
         <v>6350.53</v>
@@ -10320,7 +10320,7 @@
         <v>0.03</v>
       </c>
       <c r="I130" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J130" t="n">
         <v>6359.09</v>
@@ -10395,7 +10395,7 @@
         <v>-0.29</v>
       </c>
       <c r="I131" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J131" t="n">
         <v>6366.74</v>
@@ -10470,7 +10470,7 @@
         <v>-0.01</v>
       </c>
       <c r="I132" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J132" t="n">
         <v>6373.92</v>
@@ -10545,7 +10545,7 @@
         <v>-0.59</v>
       </c>
       <c r="I133" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J133" t="n">
         <v>6379.01</v>
@@ -10620,7 +10620,7 @@
         <v>-0.24</v>
       </c>
       <c r="I134" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J134" t="n">
         <v>6380.85</v>
@@ -10695,7 +10695,7 @@
         <v>-0.4</v>
       </c>
       <c r="I135" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J135" t="n">
         <v>6381.19</v>
@@ -10774,7 +10774,7 @@
         <v>1.52</v>
       </c>
       <c r="I136" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J136" t="n">
         <v>6385.1</v>
@@ -10783,7 +10783,7 @@
         <v>6219.75</v>
       </c>
       <c r="L136" t="n">
-        <v>5913.87</v>
+        <v>5913.86</v>
       </c>
       <c r="M136" t="n">
         <v>5944.69</v>
@@ -10849,7 +10849,7 @@
         <v>-0.43</v>
       </c>
       <c r="I137" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J137" t="n">
         <v>6387.58</v>
@@ -10924,7 +10924,7 @@
         <v>0.41</v>
       </c>
       <c r="I138" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J138" t="n">
         <v>6392.34</v>
@@ -10999,7 +10999,7 @@
         <v>0.24</v>
       </c>
       <c r="I139" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J139" t="n">
         <v>6398.26</v>
@@ -11074,7 +11074,7 @@
         <v>0.32</v>
       </c>
       <c r="I140" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J140" t="n">
         <v>6406.38</v>
@@ -11149,7 +11149,7 @@
         <v>-0.64</v>
       </c>
       <c r="I141" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J141" t="n">
         <v>6417.5</v>
@@ -11224,7 +11224,7 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="I142" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J142" t="n">
         <v>6421.78</v>
@@ -11303,7 +11303,7 @@
         <v>0.51</v>
       </c>
       <c r="I143" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J143" t="n">
         <v>6429.23</v>
@@ -11378,7 +11378,7 @@
         <v>0.83</v>
       </c>
       <c r="I144" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J144" t="n">
         <v>6437.08</v>
@@ -11453,7 +11453,7 @@
         <v>-0.32</v>
       </c>
       <c r="I145" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J145" t="n">
         <v>6444.16</v>
@@ -11528,7 +11528,7 @@
         <v>0.21</v>
       </c>
       <c r="I146" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J146" t="n">
         <v>6449.44</v>
@@ -11603,7 +11603,7 @@
         <v>0.27</v>
       </c>
       <c r="I147" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J147" t="n">
         <v>6456.4</v>
@@ -11678,7 +11678,7 @@
         <v>0.3</v>
       </c>
       <c r="I148" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J148" t="n">
         <v>6460.71</v>
@@ -11753,7 +11753,7 @@
         <v>0.85</v>
       </c>
       <c r="I149" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J149" t="n">
         <v>6466.76</v>
@@ -11828,7 +11828,7 @@
         <v>-0.05</v>
       </c>
       <c r="I150" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J150" t="n">
         <v>6472.54</v>
@@ -11903,7 +11903,7 @@
         <v>0.47</v>
       </c>
       <c r="I151" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J151" t="n">
         <v>6480.82</v>
@@ -11978,7 +11978,7 @@
         <v>-0.13</v>
       </c>
       <c r="I152" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J152" t="n">
         <v>6488.7</v>
@@ -12053,7 +12053,7 @@
         <v>-0.1</v>
       </c>
       <c r="I153" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J153" t="n">
         <v>6498.15</v>
@@ -12128,7 +12128,7 @@
         <v>0.48</v>
       </c>
       <c r="I154" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J154" t="n">
         <v>6509.96</v>
@@ -12203,7 +12203,7 @@
         <v>0.49</v>
       </c>
       <c r="I155" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J155" t="n">
         <v>6524.67</v>
@@ -12278,7 +12278,7 @@
         <v>0.44</v>
       </c>
       <c r="I156" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J156" t="n">
         <v>6536.01</v>
@@ -12353,7 +12353,7 @@
         <v>-0.55</v>
       </c>
       <c r="I157" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J157" t="n">
         <v>6546.89</v>
@@ -12428,7 +12428,7 @@
         <v>-0.28</v>
       </c>
       <c r="I158" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J158" t="n">
         <v>6555.49</v>
@@ -12503,7 +12503,7 @@
         <v>-0.5</v>
       </c>
       <c r="I159" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J159" t="n">
         <v>6561.66</v>
@@ -12578,7 +12578,7 @@
         <v>0.59</v>
       </c>
       <c r="I160" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J160" t="n">
         <v>6568.75</v>
@@ -12653,7 +12653,7 @@
         <v>0.26</v>
       </c>
       <c r="I161" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J161" t="n">
         <v>6578.8</v>
@@ -12728,7 +12728,7 @@
         <v>0.41</v>
       </c>
       <c r="I162" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J162" t="n">
         <v>6592.44</v>
@@ -12803,7 +12803,7 @@
         <v>0.34</v>
       </c>
       <c r="I163" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J163" t="n">
         <v>6605.59</v>
@@ -12878,7 +12878,7 @@
         <v>0.06</v>
       </c>
       <c r="I164" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J164" t="n">
         <v>6616.25</v>
@@ -12953,7 +12953,7 @@
         <v>0.01</v>
       </c>
       <c r="I165" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J165" t="n">
         <v>6627.97</v>
@@ -13028,7 +13028,7 @@
         <v>0.36</v>
       </c>
       <c r="I166" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J166" t="n">
         <v>6640.22</v>
@@ -13103,7 +13103,7 @@
         <v>-0.38</v>
       </c>
       <c r="I167" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J167" t="n">
         <v>6650.32</v>
@@ -13178,7 +13178,7 @@
         <v>0.58</v>
       </c>
       <c r="I168" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J168" t="n">
         <v>6661.41</v>
@@ -13253,7 +13253,7 @@
         <v>-0.28</v>
       </c>
       <c r="I169" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J169" t="n">
         <v>6668.79</v>
@@ -13328,7 +13328,7 @@
         <v>-2.71</v>
       </c>
       <c r="I170" s="4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>6667.2</v>
@@ -13407,7 +13407,7 @@
         <v>1.56</v>
       </c>
       <c r="I171" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J171" t="n">
         <v>6669.17</v>
@@ -13482,7 +13482,7 @@
         <v>-0.16</v>
       </c>
       <c r="I172" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J172" t="n">
         <v>6671.05</v>
@@ -13557,7 +13557,7 @@
         <v>0.4</v>
       </c>
       <c r="I173" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J173" t="n">
         <v>6674.58</v>
@@ -13632,7 +13632,7 @@
         <v>-0.63</v>
       </c>
       <c r="I174" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J174" t="n">
         <v>6674.44</v>
@@ -13707,7 +13707,7 @@
         <v>0.53</v>
       </c>
       <c r="I175" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J175" t="n">
         <v>6674.42</v>
@@ -13782,7 +13782,7 @@
         <v>1.07</v>
       </c>
       <c r="I176" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J176" t="n">
         <v>6676.49</v>
@@ -13857,7 +13857,7 @@
         <v>0</v>
       </c>
       <c r="I177" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J177" t="n">
         <v>6680.41</v>
@@ -13932,7 +13932,7 @@
         <v>-0.53</v>
       </c>
       <c r="I178" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J178" t="n">
         <v>6683.48</v>
@@ -14007,7 +14007,7 @@
         <v>0.58</v>
       </c>
       <c r="I179" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J179" t="n">
         <v>6690.17</v>
@@ -14082,7 +14082,7 @@
         <v>0.79</v>
       </c>
       <c r="I180" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J180" t="n">
         <v>6697.57</v>
@@ -14157,7 +14157,7 @@
         <v>1.23</v>
       </c>
       <c r="I181" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J181" t="n">
         <v>6708.27</v>
@@ -14232,7 +14232,7 @@
         <v>0.23</v>
       </c>
       <c r="I182" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J182" t="n">
         <v>6718.39</v>
@@ -14307,7 +14307,7 @@
         <v>0</v>
       </c>
       <c r="I183" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J183" t="n">
         <v>6727.36</v>
@@ -14382,7 +14382,7 @@
         <v>-0.99</v>
       </c>
       <c r="I184" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J184" t="n">
         <v>6732.71</v>
@@ -14457,7 +14457,7 @@
         <v>0.26</v>
       </c>
       <c r="I185" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J185" t="n">
         <v>6738.93</v>
@@ -14532,7 +14532,7 @@
         <v>0.17</v>
       </c>
       <c r="I186" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J186" t="n">
         <v>6744.51</v>
@@ -14607,7 +14607,7 @@
         <v>-1.17</v>
       </c>
       <c r="I187" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J187" t="n">
         <v>6747.36</v>
@@ -14682,7 +14682,7 @@
         <v>0.37</v>
       </c>
       <c r="I188" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J188" t="n">
         <v>6749.49</v>
@@ -14757,7 +14757,7 @@
         <v>-1.12</v>
       </c>
       <c r="I189" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J189" t="n">
         <v>6748.75</v>
@@ -14836,7 +14836,7 @@
         <v>0.13</v>
       </c>
       <c r="I190" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J190" t="n">
         <v>6757.56</v>
@@ -14911,7 +14911,7 @@
         <v>1.54</v>
       </c>
       <c r="I191" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J191" t="n">
         <v>6766.45</v>
@@ -14986,7 +14986,7 @@
         <v>0.21</v>
       </c>
       <c r="I192" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J192" t="n">
         <v>6776.56</v>
@@ -15061,7 +15061,7 @@
         <v>0.06</v>
       </c>
       <c r="I193" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J193" t="n">
         <v>6785.56</v>
@@ -15136,7 +15136,7 @@
         <v>-1.66</v>
       </c>
       <c r="I194" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J194" t="n">
         <v>6790.98</v>
@@ -15215,7 +15215,7 @@
         <v>-0.05</v>
       </c>
       <c r="I195" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J195" t="n">
         <v>6794.48</v>
@@ -15290,7 +15290,7 @@
         <v>-0.92</v>
       </c>
       <c r="I196" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J196" t="n">
         <v>6791.35</v>
@@ -15365,7 +15365,7 @@
         <v>-0.83</v>
       </c>
       <c r="I197" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J197" t="n">
         <v>6785.45</v>
@@ -15444,7 +15444,7 @@
         <v>0.38</v>
       </c>
       <c r="I198" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J198" t="n">
         <v>6782.58</v>
@@ -15519,7 +15519,7 @@
         <v>-1.56</v>
       </c>
       <c r="I199" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J199" t="n">
         <v>6772.6</v>
@@ -15598,7 +15598,7 @@
         <v>0.98</v>
       </c>
       <c r="I200" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J200" t="n">
         <v>6763.17</v>
@@ -15673,7 +15673,7 @@
         <v>1.55</v>
       </c>
       <c r="I201" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J201" t="n">
         <v>6754.66</v>
@@ -15748,7 +15748,7 @@
         <v>0.91</v>
       </c>
       <c r="I202" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J202" t="n">
         <v>6748.41</v>
@@ -15823,7 +15823,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I203" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J203" t="n">
         <v>6744.51</v>
@@ -15898,7 +15898,7 @@
         <v>0.54</v>
       </c>
       <c r="I204" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J204" t="n">
         <v>6745.85</v>
@@ -15973,7 +15973,7 @@
         <v>-0.53</v>
       </c>
       <c r="I205" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J205" t="n">
         <v>6744.47</v>
@@ -16048,7 +16048,7 @@
         <v>0.25</v>
       </c>
       <c r="I206" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J206" t="n">
         <v>6743.34</v>
@@ -16123,7 +16123,7 @@
         <v>0.3</v>
       </c>
       <c r="I207" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J207" t="n">
         <v>6747.25</v>
@@ -16198,7 +16198,7 @@
         <v>0.11</v>
       </c>
       <c r="I208" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J208" t="n">
         <v>6750.29</v>
@@ -16273,7 +16273,7 @@
         <v>0.19</v>
       </c>
       <c r="I209" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J209" t="n">
         <v>6757.8</v>
@@ -16348,7 +16348,7 @@
         <v>-0.35</v>
       </c>
       <c r="I210" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J210" t="n">
         <v>6763.68</v>
@@ -16423,7 +16423,7 @@
         <v>-0.09</v>
       </c>
       <c r="I211" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J211" t="n">
         <v>6764.09</v>
@@ -16498,7 +16498,7 @@
         <v>0.67</v>
       </c>
       <c r="I212" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J212" t="n">
         <v>6766.09</v>
@@ -16573,7 +16573,7 @@
         <v>0.21</v>
       </c>
       <c r="I213" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J213" t="n">
         <v>6768.59</v>
@@ -16648,7 +16648,7 @@
         <v>-1.07</v>
       </c>
       <c r="I214" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J214" t="n">
         <v>6773.09</v>
@@ -16723,7 +16723,7 @@
         <v>-0.16</v>
       </c>
       <c r="I215" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J215" t="n">
         <v>6777.21</v>
@@ -16798,7 +16798,7 @@
         <v>-0.24</v>
       </c>
       <c r="I216" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J216" t="n">
         <v>6783.6</v>
@@ -16873,7 +16873,7 @@
         <v>-1.16</v>
       </c>
       <c r="I217" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J217" t="n">
         <v>6788.81</v>
@@ -16952,7 +16952,7 @@
         <v>0.79</v>
       </c>
       <c r="I218" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J218" t="n">
         <v>6795.44</v>
@@ -17027,7 +17027,7 @@
         <v>0.88</v>
       </c>
       <c r="I219" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J219" t="n">
         <v>6810.22</v>
@@ -17102,7 +17102,7 @@
         <v>0.64</v>
       </c>
       <c r="I220" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J220" t="n">
         <v>6824</v>
@@ -17177,7 +17177,7 @@
         <v>0.46</v>
       </c>
       <c r="I221" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J221" t="n">
         <v>6834.23</v>
@@ -17252,7 +17252,7 @@
         <v>0.32</v>
       </c>
       <c r="I222" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J222" t="n">
         <v>6842.54</v>
@@ -17327,7 +17327,7 @@
         <v>-0.03</v>
       </c>
       <c r="I223" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J223" t="n">
         <v>6848.41</v>
@@ -17402,7 +17402,7 @@
         <v>-0.35</v>
       </c>
       <c r="I224" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J224" t="n">
         <v>6851.24</v>
@@ -17477,7 +17477,7 @@
         <v>-0.14</v>
       </c>
       <c r="I225" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J225" t="n">
         <v>6855.42</v>
@@ -17552,7 +17552,7 @@
         <v>-0.74</v>
       </c>
       <c r="I226" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J226" t="n">
         <v>6856.23</v>
@@ -17631,7 +17631,7 @@
         <v>0.19</v>
       </c>
       <c r="I227" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J227" t="n">
         <v>6856.67</v>
@@ -17706,7 +17706,7 @@
         <v>0.64</v>
       </c>
       <c r="I228" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J228" t="n">
         <v>6858.91</v>
@@ -17781,7 +17781,7 @@
         <v>0.62</v>
       </c>
       <c r="I229" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J229" t="n">
         <v>6862.63</v>
@@ -17856,7 +17856,7 @@
         <v>-0.34</v>
       </c>
       <c r="I230" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J230" t="n">
         <v>6866.35</v>
@@ -17931,7 +17931,7 @@
         <v>0.01</v>
       </c>
       <c r="I231" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J231" t="n">
         <v>6870.4</v>
@@ -18006,7 +18006,7 @@
         <v>0.65</v>
       </c>
       <c r="I232" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J232" t="n">
         <v>6874.38</v>
@@ -18081,7 +18081,7 @@
         <v>0.16</v>
       </c>
       <c r="I233" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J233" t="n">
         <v>6878.2</v>
@@ -18156,7 +18156,7 @@
         <v>-0.19</v>
       </c>
       <c r="I234" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J234" t="n">
         <v>6885.01</v>
@@ -18231,7 +18231,7 @@
         <v>-0.53</v>
       </c>
       <c r="I235" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J235" t="n">
         <v>6890.52</v>
@@ -18306,7 +18306,7 @@
         <v>0.26</v>
       </c>
       <c r="I236" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J236" t="n">
         <v>6897.73</v>
@@ -18381,7 +18381,7 @@
         <v>-0.06</v>
       </c>
       <c r="I237" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J237" t="n">
         <v>6908.66</v>
@@ -18456,7 +18456,7 @@
         <v>-2.06</v>
       </c>
       <c r="I238" s="4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J238" s="4" t="n">
         <v>6909.76</v>
@@ -18535,7 +18535,7 @@
         <v>1.16</v>
       </c>
       <c r="I239" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J239" t="n">
         <v>6911.82</v>
@@ -18610,7 +18610,7 @@
         <v>0.55</v>
       </c>
       <c r="I240" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J240" t="n">
         <v>6913.56</v>
@@ -18685,7 +18685,7 @@
         <v>0.03</v>
       </c>
       <c r="I241" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J241" t="n">
         <v>6913.85</v>
@@ -18760,7 +18760,7 @@
         <v>0.5</v>
       </c>
       <c r="I242" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J242" t="n">
         <v>6914.76</v>
@@ -18835,7 +18835,7 @@
         <v>0.41</v>
       </c>
       <c r="I243" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J243" t="n">
         <v>6917.19</v>
@@ -18910,7 +18910,7 @@
         <v>-0.01</v>
       </c>
       <c r="I244" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J244" t="n">
         <v>6920.81</v>
@@ -18985,7 +18985,7 @@
         <v>-0.13</v>
       </c>
       <c r="I245" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J245" t="n">
         <v>6924.45</v>
@@ -19060,7 +19060,7 @@
         <v>-0.43</v>
       </c>
       <c r="I246" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J246" t="n">
         <v>6929.12</v>
@@ -19135,7 +19135,7 @@
         <v>0.54</v>
       </c>
       <c r="I247" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J247" t="n">
         <v>6935.02</v>
@@ -19210,7 +19210,7 @@
         <v>-0.84</v>
       </c>
       <c r="I248" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J248" t="n">
         <v>6935.81</v>
@@ -19289,7 +19289,7 @@
         <v>-0.51</v>
       </c>
       <c r="I249" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J249" t="n">
         <v>6932.7</v>
@@ -19364,7 +19364,7 @@
         <v>-1.23</v>
       </c>
       <c r="I250" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J250" t="n">
         <v>6926.58</v>
@@ -19443,7 +19443,7 @@
         <v>1.97</v>
       </c>
       <c r="I251" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J251" t="n">
         <v>6927.12</v>
@@ -19518,7 +19518,7 @@
         <v>0.47</v>
       </c>
       <c r="I252" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J252" t="n">
         <v>6927.05</v>
@@ -19593,7 +19593,7 @@
         <v>-0.33</v>
       </c>
       <c r="I253" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J253" t="n">
         <v>6925.27</v>
@@ -19668,7 +19668,7 @@
         <v>0</v>
       </c>
       <c r="I254" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J254" t="n">
         <v>6924.16</v>
@@ -19743,7 +19743,7 @@
         <v>-1.57</v>
       </c>
       <c r="I255" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J255" t="n">
         <v>6919.47</v>
@@ -19822,7 +19822,7 @@
         <v>0.05</v>
       </c>
       <c r="I256" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J256" t="n">
         <v>6914.05</v>
@@ -19897,7 +19897,7 @@
         <v>0.1</v>
       </c>
       <c r="I257" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J257" t="n">
         <v>6909.21</v>
@@ -19972,7 +19972,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I258" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J258" t="n">
         <v>6913.44</v>
@@ -20047,7 +20047,7 @@
         <v>-0.28</v>
       </c>
       <c r="I259" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J259" t="n">
         <v>6912.75</v>
@@ -20126,7 +20126,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I260" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J260" t="n">
         <v>6912.56</v>
@@ -20201,7 +20201,7 @@
         <v>-1.04</v>
       </c>
       <c r="I261" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J261" t="n">
         <v>6908.66</v>
@@ -20280,7 +20280,7 @@
         <v>0.77</v>
       </c>
       <c r="I262" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J262" t="n">
         <v>6905.66</v>
@@ -20355,7 +20355,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I263" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J263" t="n">
         <v>6904.03</v>
@@ -20430,7 +20430,7 @@
         <v>-0.54</v>
       </c>
       <c r="I264" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J264" t="n">
         <v>6900.57</v>
@@ -20505,7 +20505,7 @@
         <v>-0.43</v>
       </c>
       <c r="I265" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J265" t="n">
         <v>6896.07</v>
@@ -20584,7 +20584,7 @@
         <v>0.04</v>
       </c>
       <c r="I266" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J266" t="n">
         <v>6893.2</v>
@@ -20659,7 +20659,7 @@
         <v>-0.9399999999999999</v>
       </c>
       <c r="I267" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J267" t="n">
         <v>6885.21</v>
@@ -20734,7 +20734,7 @@
         <v>0.78</v>
       </c>
       <c r="I268" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J268" t="n">
         <v>6882.79</v>
@@ -20809,7 +20809,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="I269" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J269" t="n">
         <v>6880.19</v>
@@ -20884,7 +20884,7 @@
         <v>-1.33</v>
       </c>
       <c r="I270" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J270" t="n">
         <v>6877.27</v>
@@ -20967,7 +20967,7 @@
         <v>0.83</v>
       </c>
       <c r="I271" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J271" t="n">
         <v>6870.46</v>
@@ -21042,7 +21042,7 @@
         <v>-0.21</v>
       </c>
       <c r="I272" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J272" t="n">
         <v>6861.29</v>
@@ -21117,7 +21117,7 @@
         <v>-0.08</v>
       </c>
       <c r="I273" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J273" t="n">
         <v>6852.99</v>
@@ -21192,7 +21192,7 @@
         <v>-1.52</v>
       </c>
       <c r="I274" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J274" t="n">
         <v>6839.55</v>
@@ -21261,7 +21261,7 @@
         <v>-0.61</v>
       </c>
       <c r="I275" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J275" t="n">
         <v>6829.52</v>
@@ -21340,7 +21340,7 @@
         <v>1.01</v>
       </c>
       <c r="I276" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J276" t="n">
         <v>6822.68</v>
@@ -21415,7 +21415,7 @@
         <v>0.25</v>
       </c>
       <c r="I277" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J277" t="n">
         <v>6816.32</v>
@@ -21490,7 +21490,7 @@
         <v>-1.36</v>
       </c>
       <c r="I278" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J278" t="n">
         <v>6803.49</v>
@@ -21565,7 +21565,7 @@
         <v>-0.27</v>
       </c>
       <c r="I279" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J279" t="n">
         <v>6790.72</v>
@@ -21644,7 +21644,7 @@
         <v>-1.51</v>
       </c>
       <c r="I280" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J280" t="n">
         <v>6770.57</v>
@@ -21727,7 +21727,7 @@
         <v>1.15</v>
       </c>
       <c r="I281" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J281" t="n">
         <v>6757.73</v>
@@ -21802,7 +21802,7 @@
         <v>-0.37</v>
       </c>
       <c r="I282" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J282" t="n">
         <v>6741.05</v>
@@ -21881,7 +21881,7 @@
         <v>0.54</v>
       </c>
       <c r="I283" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J283" t="n">
         <v>6723.34</v>
@@ -21956,7 +21956,7 @@
         <v>-1.74</v>
       </c>
       <c r="I284" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J284" t="n">
         <v>6701.75</v>
@@ -22031,7 +22031,7 @@
         <v>-1.67</v>
       </c>
       <c r="I285" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J285" t="n">
         <v>6676.25</v>
@@ -22114,7 +22114,7 @@
         <v>-0.39</v>
       </c>
       <c r="I286" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J286" t="n">
         <v>6649.35</v>
@@ -22193,7 +22193,7 @@
         <v>2.91</v>
       </c>
       <c r="I287" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J287" t="n">
         <v>6634.95</v>
@@ -22268,7 +22268,7 @@
         <v>0.72</v>
       </c>
       <c r="I288" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J288" t="n">
         <v>6620.24</v>
@@ -22343,7 +22343,7 @@
         <v>0.11</v>
       </c>
       <c r="I289" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J289" t="n">
         <v>6607.84</v>
@@ -22418,7 +22418,7 @@
         <v>0.44</v>
       </c>
       <c r="I290" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J290" t="n">
         <v>6601.43</v>
@@ -22493,7 +22493,7 @@
         <v>0.08</v>
       </c>
       <c r="I291" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J291" t="n">
         <v>6592.47</v>
@@ -22572,7 +22572,7 @@
         <v>2.51</v>
       </c>
       <c r="I292" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J292" t="n">
         <v>6592.54</v>
@@ -22647,7 +22647,7 @@
         <v>0.62</v>
       </c>
       <c r="I293" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J293" t="n">
         <v>6594.98</v>
@@ -22722,7 +22722,7 @@
         <v>-0.11</v>
       </c>
       <c r="I294" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J294" t="n">
         <v>6602.2</v>
@@ -22797,7 +22797,7 @@
         <v>1.02</v>
       </c>
       <c r="I295" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J295" t="n">
         <v>6614.9</v>
@@ -22872,7 +22872,7 @@
         <v>1.18</v>
       </c>
       <c r="I296" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J296" t="n">
         <v>6628.3</v>
@@ -22947,7 +22947,7 @@
         <v>0.8</v>
       </c>
       <c r="I297" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J297" t="n">
         <v>6643.64</v>
@@ -23022,7 +23022,7 @@
         <v>0.26</v>
       </c>
       <c r="I298" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J298" t="n">
         <v>6664.47</v>
@@ -23097,7 +23097,7 @@
         <v>1.2</v>
       </c>
       <c r="I299" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J299" t="n">
         <v>6690.45</v>
@@ -23172,7 +23172,7 @@
         <v>-0.24</v>
       </c>
       <c r="I300" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J300" t="n">
         <v>6720.58</v>
@@ -23247,7 +23247,7 @@
         <v>-0.63</v>
       </c>
       <c r="I301" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J301" t="n">
         <v>6744.73</v>
@@ -23322,7 +23322,7 @@
         <v>1.05</v>
       </c>
       <c r="I302" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J302" t="n">
         <v>6773.81</v>
@@ -23397,7 +23397,7 @@
         <v>-0.41</v>
       </c>
       <c r="I303" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J303" t="n">
         <v>6799.63</v>
@@ -23472,7 +23472,7 @@
         <v>0.8</v>
       </c>
       <c r="I304" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J304" t="n">
         <v>6834.03</v>
@@ -23547,7 +23547,7 @@
         <v>0.12</v>
       </c>
       <c r="I305" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J305" t="n">
         <v>6874.28</v>
@@ -23622,7 +23622,7 @@
         <v>-0.49</v>
       </c>
       <c r="I306" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J306" t="n">
         <v>6914.04</v>
@@ -23697,7 +23697,7 @@
         <v>-0.04</v>
       </c>
       <c r="I307" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J307" t="n">
         <v>6944.41</v>
@@ -23772,7 +23772,7 @@
         <v>1.02</v>
       </c>
       <c r="I308" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J308" t="n">
         <v>6976.09</v>
@@ -23847,7 +23847,7 @@
         <v>0.29</v>
       </c>
       <c r="I309" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J309" t="n">
         <v>7008.46</v>
@@ -23922,7 +23922,7 @@
         <v>-0.41</v>
       </c>
       <c r="I310" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J310" t="n">
         <v>7037.91</v>
@@ -23997,7 +23997,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I311" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J311" t="n">
         <v>7070.03</v>
@@ -24072,7 +24072,7 @@
         <v>1.46</v>
       </c>
       <c r="I312" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J312" t="n">
         <v>7099.14</v>
@@ -24147,7 +24147,7 @@
         <v>-0.38</v>
       </c>
       <c r="I313" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J313" t="n">
         <v>7124.77</v>
@@ -24222,7 +24222,7 @@
         <v>0.84</v>
       </c>
       <c r="I314" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J314" t="n">
         <v>7153.87</v>
@@ -24297,7 +24297,7 @@
         <v>0.19</v>
       </c>
       <c r="I315" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J315" t="n">
         <v>7180.2</v>
@@ -24372,7 +24372,7 @@
         <v>-0.16</v>
       </c>
       <c r="I316" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J316" t="n">
         <v>7201.88</v>
@@ -24447,7 +24447,7 @@
         <v>0.58</v>
       </c>
       <c r="I317" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J317" t="n">
         <v>7222.94</v>
@@ -24522,7 +24522,7 @@
         <v>0.77</v>
       </c>
       <c r="I318" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J318" t="n">
         <v>7245.94</v>
@@ -24597,7 +24597,7 @@
         <v>-1.24</v>
       </c>
       <c r="I319" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J319" t="n">
         <v>7260.06</v>
@@ -24672,7 +24672,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="I320" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J320" t="n">
         <v>7274.76</v>
@@ -24747,7 +24747,7 @@
         <v>-0.67</v>
       </c>
       <c r="I321" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J321" t="n">
         <v>7289.24</v>
@@ -24822,7 +24822,7 @@
         <v>1.08</v>
       </c>
       <c r="I322" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J322" t="n">
         <v>7303.99</v>
@@ -24897,7 +24897,7 @@
         <v>0.17</v>
       </c>
       <c r="I323" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J323" t="n">
         <v>7320.86</v>
@@ -24972,7 +24972,7 @@
         <v>0.37</v>
       </c>
       <c r="I324" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J324" t="n">
         <v>7336.28</v>
@@ -25047,7 +25047,7 @@
         <v>0.61</v>
       </c>
       <c r="I325" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J325" t="n">
         <v>7353.54</v>
@@ -25122,7 +25122,7 @@
         <v>0.02</v>
       </c>
       <c r="I326" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J326" t="n">
         <v>7372.62</v>
@@ -25197,7 +25197,7 @@
         <v>0.58</v>
       </c>
       <c r="I327" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J327" t="n">
         <v>7394</v>
@@ -25272,7 +25272,7 @@
         <v>0.22</v>
       </c>
       <c r="I328" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J328" t="n">
         <v>7412.55</v>
@@ -25347,7 +25347,7 @@
         <v>0.26</v>
       </c>
       <c r="I329" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J329" t="n">
         <v>7431.04</v>
@@ -25422,7 +25422,7 @@
         <v>0.13</v>
       </c>
       <c r="I330" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J330" t="n">
         <v>7451.5</v>
@@ -25497,7 +25497,7 @@
         <v>-0.74</v>
       </c>
       <c r="I331" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J331" t="n">
         <v>7466.22</v>
@@ -25572,7 +25572,7 @@
         <v>0.41</v>
       </c>
       <c r="I332" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J332" t="n">
         <v>7477.18</v>
@@ -25647,7 +25647,7 @@
         <v>-2.64</v>
       </c>
       <c r="I333" s="4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J333" s="4" t="n">
         <v>7479.51</v>
@@ -25726,7 +25726,7 @@
         <v>0.3</v>
       </c>
       <c r="I334" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J334" t="n">
         <v>7479.85</v>
@@ -25801,7 +25801,7 @@
         <v>-0.26</v>
       </c>
       <c r="I335" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J335" t="n">
         <v>7478.54</v>
@@ -25876,7 +25876,7 @@
         <v>-1.62</v>
       </c>
       <c r="I336" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J336" t="n">
         <v>7471.84</v>
@@ -25951,7 +25951,7 @@
         <v>1.75</v>
       </c>
       <c r="I337" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J337" t="n">
         <v>7469.34</v>
@@ -26026,7 +26026,7 @@
         <v>0.5</v>
       </c>
       <c r="I338" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J338" t="n">
         <v>7465.85</v>
@@ -26101,7 +26101,7 @@
         <v>1.65</v>
       </c>
       <c r="I339" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J339" t="n">
         <v>7473.14</v>
@@ -26176,7 +26176,7 @@
         <v>-0.57</v>
       </c>
       <c r="I340" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J340" t="n">
         <v>7478.56</v>
@@ -26251,7 +26251,7 @@
         <v>-1.21</v>
       </c>
       <c r="I341" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J341" t="n">
         <v>7481.88</v>
@@ -26330,7 +26330,7 @@
         <v>1.08</v>
       </c>
       <c r="I342" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J342" t="n">
         <v>7485.26</v>
@@ -26405,7 +26405,7 @@
         <v>-0.37</v>
       </c>
       <c r="I343" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J343" t="n">
         <v>7486.62</v>
@@ -26484,7 +26484,7 @@
         <v>-1.44</v>
       </c>
       <c r="I344" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J344" t="n">
         <v>7481.22</v>
@@ -26559,7 +26559,7 @@
         <v>-0.1</v>
       </c>
       <c r="I345" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J345" t="n">
         <v>7473.17</v>
@@ -26634,7 +26634,7 @@
         <v>-0.01</v>
       </c>
       <c r="I346" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J346" t="n">
         <v>7465.03</v>
@@ -26709,7 +26709,7 @@
         <v>-0.05</v>
       </c>
       <c r="I347" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J347" t="n">
         <v>7454.55</v>
@@ -26784,7 +26784,7 @@
         <v>1.18</v>
       </c>
       <c r="I348" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J348" t="n">
         <v>7447.57</v>
@@ -26859,7 +26859,7 @@
         <v>0.79</v>
       </c>
       <c r="I349" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J349" t="n">
         <v>7442.54</v>
@@ -26934,7 +26934,7 @@
         <v>-0.22</v>
       </c>
       <c r="I350" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J350" t="n">
         <v>7436.21</v>
@@ -27009,7 +27009,7 @@
         <v>0</v>
       </c>
       <c r="I351" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J351" t="n">
         <v>7432.69</v>
@@ -27084,7 +27084,7 @@
         <v>0.72</v>
       </c>
       <c r="I352" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J352" t="n">
         <v>7430.34</v>
@@ -27159,7 +27159,7 @@
         <v>-0.45</v>
       </c>
       <c r="I353" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J353" t="n">
         <v>7436.35</v>
@@ -27234,7 +27234,7 @@
         <v>-0.28</v>
       </c>
       <c r="I354" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J354" t="n">
         <v>7440.2</v>
@@ -27309,7 +27309,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I355" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J355" t="n">
         <v>7448.05</v>
@@ -27384,7 +27384,7 @@
         <v>0.42</v>
       </c>
       <c r="I356" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J356" t="n">
         <v>7463.47</v>
@@ -27459,7 +27459,7 @@
         <v>-0.79</v>
       </c>
       <c r="I357" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J357" t="n">
         <v>7469.52</v>
@@ -27534,7 +27534,7 @@
         <v>0.38</v>
       </c>
       <c r="I358" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J358" t="n">
         <v>7475.13</v>
@@ -27609,7 +27609,7 @@
         <v>0.38</v>
       </c>
       <c r="I359" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J359" t="n">
         <v>7476.03</v>
@@ -27684,7 +27684,7 @@
         <v>-0.51</v>
       </c>
       <c r="I360" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J360" t="n">
         <v>7477.15</v>
@@ -27759,7 +27759,7 @@
         <v>-1.01</v>
       </c>
       <c r="I361" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J361" t="n">
         <v>7479.03</v>
@@ -27838,7 +27838,7 @@
         <v>-0.19</v>
       </c>
       <c r="I362" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J362" t="n">
         <v>7476.17</v>
@@ -27913,7 +27913,7 @@
         <v>0.89</v>
       </c>
       <c r="I363" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J363" t="n">
         <v>7477.99</v>
@@ -27988,7 +27988,7 @@
         <v>-0.14</v>
       </c>
       <c r="I364" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J364" t="n">
         <v>7484.66</v>
@@ -28063,7 +28063,7 @@
         <v>-1.21</v>
       </c>
       <c r="I365" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J365" t="n">
         <v>7487.17</v>
@@ -28142,7 +28142,7 @@
         <v>0.05</v>
       </c>
       <c r="I366" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J366" t="n">
         <v>7489.89</v>
@@ -28217,7 +28217,7 @@
         <v>0.02</v>
       </c>
       <c r="I367" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J367" t="n">
         <v>7492.85</v>
@@ -28292,7 +28292,7 @@
         <v>0.21</v>
       </c>
       <c r="I368" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J368" t="n">
         <v>7492.27</v>
@@ -28367,7 +28367,7 @@
         <v>-1.52</v>
       </c>
       <c r="I369" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J369" t="n">
         <v>7483.11</v>
@@ -28442,7 +28442,7 @@
         <v>1.66</v>
       </c>
       <c r="I370" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J370" t="n">
         <v>7480.83</v>
@@ -28517,7 +28517,7 @@
         <v>0.7</v>
       </c>
       <c r="I371" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J371" t="n">
         <v>7481.15</v>
@@ -28592,7 +28592,7 @@
         <v>1.48</v>
       </c>
       <c r="I372" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J372" t="n">
         <v>7484.3</v>
@@ -28667,7 +28667,7 @@
         <v>1.79</v>
       </c>
       <c r="I373" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J373" t="n">
         <v>7495.94</v>
@@ -28742,7 +28742,7 @@
         <v>-0.17</v>
       </c>
       <c r="I374" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J374" t="n">
         <v>7507.98</v>
@@ -28817,7 +28817,7 @@
         <v>-0.18</v>
       </c>
       <c r="I375" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J375" t="n">
         <v>7516.29</v>
@@ -28892,7 +28892,7 @@
         <v>0.62</v>
       </c>
       <c r="I376" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J376" t="n">
         <v>7525.41</v>
@@ -28967,7 +28967,7 @@
         <v>-0.06</v>
       </c>
       <c r="I377" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J377" t="n">
         <v>7537.3</v>
@@ -29042,7 +29042,7 @@
         <v>-0.32</v>
       </c>
       <c r="I378" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J378" t="n">
         <v>7546.53</v>
@@ -29117,7 +29117,7 @@
         <v>0.26</v>
       </c>
       <c r="I379" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J379" t="n">
         <v>7555.33</v>
@@ -29192,7 +29192,7 @@
         <v>0.65</v>
       </c>
       <c r="I380" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J380" t="n">
         <v>7568.59</v>
@@ -29267,7 +29267,7 @@
         <v>-0.17</v>
       </c>
       <c r="I381" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J381" t="n">
         <v>7585</v>
@@ -29342,7 +29342,7 @@
         <v>-0.52</v>
       </c>
       <c r="I382" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J382" t="n">
         <v>7600.08</v>
@@ -29417,7 +29417,7 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="I383" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J383" t="n">
         <v>7609.21</v>
@@ -29492,7 +29492,7 @@
         <v>0.21</v>
       </c>
       <c r="I384" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J384" t="n">
         <v>7619.66</v>
@@ -29567,7 +29567,7 @@
         <v>-0.87</v>
       </c>
       <c r="I385" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J385" t="n">
         <v>7631.31</v>
@@ -29642,7 +29642,7 @@
         <v>0.43</v>
       </c>
       <c r="I386" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J386" t="n">
         <v>7644.43</v>
@@ -29717,7 +29717,7 @@
         <v>-0.28</v>
       </c>
       <c r="I387" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J387" t="n">
         <v>7656.41</v>
@@ -29796,7 +29796,7 @@
         <v>0.32</v>
       </c>
       <c r="I388" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J388" t="n">
         <v>7668.83</v>
@@ -29871,7 +29871,7 @@
         <v>-0.02</v>
       </c>
       <c r="I389" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J389" t="n">
         <v>7686.81</v>
@@ -29950,7 +29950,7 @@
         <v>0.72</v>
       </c>
       <c r="I390" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J390" t="n">
         <v>7701.48</v>
@@ -30025,7 +30025,7 @@
         <v>-0.25</v>
       </c>
       <c r="I391" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J391" t="n">
         <v>7712.58</v>
@@ -30104,7 +30104,7 @@
         <v>-0.33</v>
       </c>
       <c r="I392" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J392" t="n">
         <v>7716.86</v>
@@ -30179,7 +30179,7 @@
         <v>-0.71</v>
       </c>
       <c r="I393" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J393" t="n">
         <v>7711.61</v>
@@ -30254,7 +30254,7 @@
         <v>0.46</v>
       </c>
       <c r="I394" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J394" t="n">
         <v>7708.76</v>
@@ -30329,7 +30329,7 @@
         <v>1.06</v>
       </c>
       <c r="I395" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J395" t="n">
         <v>7710.65</v>
@@ -30404,7 +30404,7 @@
         <v>-0.38</v>
       </c>
       <c r="I396" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J396" t="n">
         <v>7708.7</v>
@@ -30479,7 +30479,7 @@
         <v>-0.58</v>
       </c>
       <c r="I397" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J397" t="n">
         <v>7704.72</v>
@@ -30558,7 +30558,7 @@
         <v>-0.48</v>
       </c>
       <c r="I398" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J398" t="n">
         <v>7700.13</v>
@@ -30633,7 +30633,7 @@
         <v>-0.58</v>
       </c>
       <c r="I399" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J399" t="n">
         <v>7692.29</v>
@@ -30708,7 +30708,7 @@
         <v>0.86</v>
       </c>
       <c r="I400" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J400" t="n">
         <v>7685.19</v>
@@ -30783,7 +30783,7 @@
         <v>-0.48</v>
       </c>
       <c r="I401" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J401" t="n">
         <v>7676.9</v>
@@ -30858,7 +30858,7 @@
         <v>-0.45</v>
       </c>
       <c r="I402" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J402" t="n">
         <v>7668.93</v>
@@ -30933,7 +30933,7 @@
         <v>-0.45</v>
       </c>
       <c r="I403" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J403" t="n">
         <v>7661.94</v>
@@ -31012,7 +31012,7 @@
         <v>1.14</v>
       </c>
       <c r="I404" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J404" t="n">
         <v>7658.42</v>
@@ -31087,7 +31087,7 @@
         <v>0.17</v>
       </c>
       <c r="I405" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J405" t="n">
         <v>7658.89</v>
@@ -31162,7 +31162,7 @@
         <v>1.49</v>
       </c>
       <c r="I406" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J406" t="n">
         <v>7663.41</v>
@@ -31237,7 +31237,7 @@
         <v>0</v>
       </c>
       <c r="I407" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J407" t="n">
         <v>7669</v>
@@ -31312,7 +31312,7 @@
         <v>-0.75</v>
       </c>
       <c r="I408" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J408" t="n">
         <v>7670.43</v>
@@ -31387,7 +31387,7 @@
         <v>-0.02</v>
       </c>
       <c r="I409" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J409" t="n">
         <v>7671.86</v>
@@ -31462,7 +31462,7 @@
         <v>0.51</v>
       </c>
       <c r="I410" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J410" t="n">
         <v>7672.48</v>
@@ -31537,7 +31537,7 @@
         <v>-0.77</v>
       </c>
       <c r="I411" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J411" t="n">
         <v>7671.07</v>
@@ -31612,7 +31612,7 @@
         <v>-0.17</v>
       </c>
       <c r="I412" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J412" t="n">
         <v>7670.31</v>
@@ -31675,37 +31675,37 @@
         <v>7722.88</v>
       </c>
       <c r="E413" t="n">
-        <v>7688.99</v>
+        <v>7651.54</v>
       </c>
       <c r="F413" t="n">
-        <v>7691.47</v>
+        <v>7651.54</v>
       </c>
       <c r="G413" t="n">
-        <v>1572133000</v>
-      </c>
-      <c r="H413" s="1" t="n">
-        <v>0.27</v>
+        <v>3151899000</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-0.25</v>
       </c>
       <c r="I413" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J413" t="n">
-        <v>7673.31</v>
+        <v>7671.31</v>
       </c>
       <c r="K413" t="n">
-        <v>7626.95</v>
+        <v>7626.29</v>
       </c>
       <c r="L413" t="n">
-        <v>7486.91</v>
+        <v>7486.58</v>
       </c>
       <c r="M413" t="n">
-        <v>7217.29</v>
+        <v>7217.09</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>58.65</v>
+        <v>55.2</v>
       </c>
       <c r="O413" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31717,18 +31717,24 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R413" t="inlineStr"/>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
       <c r="S413" t="n">
-        <v>5.3</v>
+        <v>5.29</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.9</v>
+        <v>16.3</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>141.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31681,7 +31681,7 @@
         <v>7651.54</v>
       </c>
       <c r="G413" t="n">
-        <v>3151899000</v>
+        <v>4276550000</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>-0.25</v>
@@ -31705,7 +31705,7 @@
         <v>55.2</v>
       </c>
       <c r="O413" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31736,6 +31736,79 @@
         <v>141.9</v>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>7666.47</v>
+      </c>
+      <c r="D414" t="n">
+        <v>7683.65</v>
+      </c>
+      <c r="E414" t="n">
+        <v>7616.78</v>
+      </c>
+      <c r="F414" t="n">
+        <v>7641.2</v>
+      </c>
+      <c r="G414" t="n">
+        <v>1143382000</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="I414" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J414" t="n">
+        <v>7670.04</v>
+      </c>
+      <c r="K414" t="n">
+        <v>7628.93</v>
+      </c>
+      <c r="L414" t="n">
+        <v>7493.45</v>
+      </c>
+      <c r="M414" t="n">
+        <v>7221.16</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="O414" t="n">
+        <v>27</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31751,40 +31751,40 @@
         <v>7666.47</v>
       </c>
       <c r="D414" t="n">
-        <v>7683.65</v>
+        <v>7684.75</v>
       </c>
       <c r="E414" t="n">
         <v>7616.78</v>
       </c>
       <c r="F414" t="n">
-        <v>7641.2</v>
+        <v>7666.45</v>
       </c>
       <c r="G414" t="n">
-        <v>1143382000</v>
-      </c>
-      <c r="H414" s="3" t="n">
-        <v>-0.14</v>
+        <v>3202348000</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.19</v>
       </c>
       <c r="I414" t="n">
         <v>1.9</v>
       </c>
       <c r="J414" t="n">
-        <v>7670.04</v>
+        <v>7671.3</v>
       </c>
       <c r="K414" t="n">
-        <v>7628.93</v>
+        <v>7629.35</v>
       </c>
       <c r="L414" t="n">
-        <v>7493.45</v>
+        <v>7493.66</v>
       </c>
       <c r="M414" t="n">
-        <v>7221.16</v>
+        <v>7221.29</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>48.48</v>
+        <v>50.9</v>
       </c>
       <c r="O414" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31798,16 +31798,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.3</v>
+        <v>16.4</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>142.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31760,7 +31760,7 @@
         <v>7666.45</v>
       </c>
       <c r="G414" t="n">
-        <v>3202348000</v>
+        <v>5783800000</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>0.19</v>
@@ -31784,7 +31784,7 @@
         <v>50.9</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31784,7 +31784,7 @@
         <v>50.9</v>
       </c>
       <c r="O414" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31810,6 +31810,79 @@
       <c r="W414" s="2" t="n">
         <v>142.8</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>7726.24</v>
+      </c>
+      <c r="D415" t="n">
+        <v>7754.67</v>
+      </c>
+      <c r="E415" t="n">
+        <v>7700.51</v>
+      </c>
+      <c r="F415" t="n">
+        <v>7713.84</v>
+      </c>
+      <c r="G415" t="n">
+        <v>1065306000</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="I415" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J415" t="n">
+        <v>7669.61</v>
+      </c>
+      <c r="K415" t="n">
+        <v>7632.19</v>
+      </c>
+      <c r="L415" t="n">
+        <v>7500.56</v>
+      </c>
+      <c r="M415" t="n">
+        <v>7225.77</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>58.77</v>
+      </c>
+      <c r="O415" t="n">
+        <v>31</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31832,31 +31832,31 @@
         <v>7700.51</v>
       </c>
       <c r="F415" t="n">
-        <v>7713.84</v>
+        <v>7722.72</v>
       </c>
       <c r="G415" t="n">
-        <v>1065306000</v>
+        <v>3118955000</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="I415" t="n">
         <v>1.9</v>
       </c>
       <c r="J415" t="n">
-        <v>7669.61</v>
+        <v>7670.05</v>
       </c>
       <c r="K415" t="n">
-        <v>7632.19</v>
+        <v>7632.33</v>
       </c>
       <c r="L415" t="n">
-        <v>7500.56</v>
+        <v>7500.63</v>
       </c>
       <c r="M415" t="n">
-        <v>7225.77</v>
+        <v>7225.82</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>58.77</v>
+        <v>59.44</v>
       </c>
       <c r="O415" t="n">
         <v>31</v>
@@ -31873,13 +31873,13 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.25</v>
+        <v>5.28</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>15.8</v>
+        <v>15.3</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31760,7 +31760,7 @@
         <v>7722.72</v>
       </c>
       <c r="G414" t="n">
-        <v>3130028000</v>
+        <v>5277430000</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>0.73</v>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31634,7 +31634,7 @@
         <v>59.44</v>
       </c>
       <c r="O412" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -29731,7 +29731,7 @@
         <v>7701.48</v>
       </c>
       <c r="K387" t="n">
-        <v>7539.5</v>
+        <v>7539.51</v>
       </c>
       <c r="L387" t="n">
         <v>7284.89</v>
@@ -31634,7 +31634,7 @@
         <v>59.44</v>
       </c>
       <c r="O412" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31660,6 +31660,79 @@
       <c r="W412" s="2" t="n">
         <v>144.9</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>7730.86</v>
+      </c>
+      <c r="D413" t="n">
+        <v>7778</v>
+      </c>
+      <c r="E413" t="n">
+        <v>7727.59</v>
+      </c>
+      <c r="F413" t="n">
+        <v>7774.57</v>
+      </c>
+      <c r="G413" t="n">
+        <v>1439842000</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="I413" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J413" t="n">
+        <v>7672.85</v>
+      </c>
+      <c r="K413" t="n">
+        <v>7635.65</v>
+      </c>
+      <c r="L413" t="n">
+        <v>7507.36</v>
+      </c>
+      <c r="M413" t="n">
+        <v>7230.69</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>66.81</v>
+      </c>
+      <c r="O413" t="n">
+        <v>44</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31610,7 +31610,7 @@
         <v>7773.95</v>
       </c>
       <c r="G412" t="n">
-        <v>3473000000</v>
+        <v>5840900000</v>
       </c>
       <c r="H412" s="3" t="n">
         <v>0.66</v>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31634,7 +31634,7 @@
         <v>66.78</v>
       </c>
       <c r="O412" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31660,6 +31660,79 @@
       <c r="W412" s="2" t="n">
         <v>143</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>7805.96</v>
+      </c>
+      <c r="D413" t="n">
+        <v>7835.09</v>
+      </c>
+      <c r="E413" t="n">
+        <v>7805.96</v>
+      </c>
+      <c r="F413" t="n">
+        <v>7830.03</v>
+      </c>
+      <c r="G413" t="n">
+        <v>641351002</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="I413" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J413" t="n">
+        <v>7680.65</v>
+      </c>
+      <c r="K413" t="n">
+        <v>7640.89</v>
+      </c>
+      <c r="L413" t="n">
+        <v>7514.08</v>
+      </c>
+      <c r="M413" t="n">
+        <v>7236.23</v>
+      </c>
+      <c r="N413" s="1" t="n">
+        <v>73.86</v>
+      </c>
+      <c r="O413" t="n">
+        <v>48</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -7690,7 +7690,7 @@
         <v>1.9</v>
       </c>
       <c r="J95" t="n">
-        <v>6043.06</v>
+        <v>6043.05</v>
       </c>
       <c r="K95" t="n">
         <v>5748.09</v>
@@ -29656,7 +29656,7 @@
         <v>7701.48</v>
       </c>
       <c r="K386" t="n">
-        <v>7539.51</v>
+        <v>7539.5</v>
       </c>
       <c r="L386" t="n">
         <v>7284.89</v>
@@ -31676,37 +31676,37 @@
         <v>7805.96</v>
       </c>
       <c r="D413" t="n">
-        <v>7835.09</v>
+        <v>7844.52</v>
       </c>
       <c r="E413" t="n">
         <v>7805.96</v>
       </c>
       <c r="F413" t="n">
-        <v>7830.03</v>
+        <v>7818.98</v>
       </c>
       <c r="G413" t="n">
-        <v>641351002</v>
+        <v>2600192000</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>0.72</v>
+        <v>0.58</v>
       </c>
       <c r="I413" t="n">
         <v>1.9</v>
       </c>
       <c r="J413" t="n">
-        <v>7680.65</v>
+        <v>7680.09</v>
       </c>
       <c r="K413" t="n">
-        <v>7640.89</v>
+        <v>7640.7</v>
       </c>
       <c r="L413" t="n">
-        <v>7514.08</v>
+        <v>7513.99</v>
       </c>
       <c r="M413" t="n">
-        <v>7236.23</v>
+        <v>7236.17</v>
       </c>
       <c r="N413" s="1" t="n">
-        <v>73.86</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="O413" t="n">
         <v>48</v>
@@ -31723,13 +31723,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.28</v>
+        <v>5.27</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.4</v>
+        <v>15.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31610,7 +31610,7 @@
         <v>7818.93</v>
       </c>
       <c r="G412" t="n">
-        <v>2717394000</v>
+        <v>5019650000</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>0.58</v>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31661,6 +31661,79 @@
         <v>141.2</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>7792.98</v>
+      </c>
+      <c r="D413" t="n">
+        <v>7792.98</v>
+      </c>
+      <c r="E413" t="n">
+        <v>7767.86</v>
+      </c>
+      <c r="F413" t="n">
+        <v>7774.99</v>
+      </c>
+      <c r="G413" t="n">
+        <v>462704065</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="I413" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J413" t="n">
+        <v>7687.02</v>
+      </c>
+      <c r="K413" t="n">
+        <v>7644.56</v>
+      </c>
+      <c r="L413" t="n">
+        <v>7520.1</v>
+      </c>
+      <c r="M413" t="n">
+        <v>7241.18</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>62.95</v>
+      </c>
+      <c r="O413" t="n">
+        <v>42</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -29424,7 +29424,7 @@
         <v>1.9</v>
       </c>
       <c r="J383" t="n">
-        <v>7668.83</v>
+        <v>7668.84</v>
       </c>
       <c r="K383" t="n">
         <v>7536.22</v>
@@ -31676,40 +31676,40 @@
         <v>7792.98</v>
       </c>
       <c r="D413" t="n">
-        <v>7792.98</v>
+        <v>7807.02</v>
       </c>
       <c r="E413" t="n">
-        <v>7767.86</v>
+        <v>7763.34</v>
       </c>
       <c r="F413" t="n">
-        <v>7774.99</v>
+        <v>7801.77</v>
       </c>
       <c r="G413" t="n">
-        <v>462704065</v>
+        <v>2627309000</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.22</v>
       </c>
       <c r="I413" t="n">
         <v>1.9</v>
       </c>
       <c r="J413" t="n">
-        <v>7687.02</v>
+        <v>7688.36</v>
       </c>
       <c r="K413" t="n">
-        <v>7644.56</v>
+        <v>7645.01</v>
       </c>
       <c r="L413" t="n">
-        <v>7520.1</v>
+        <v>7520.32</v>
       </c>
       <c r="M413" t="n">
-        <v>7241.18</v>
+        <v>7241.31</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>62.95</v>
+        <v>66.3</v>
       </c>
       <c r="O413" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31723,13 +31723,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.32</v>
+        <v>5.28</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.8</v>
+        <v>15.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31685,7 +31685,7 @@
         <v>7801.77</v>
       </c>
       <c r="G413" t="n">
-        <v>2627309000</v>
+        <v>2648837000</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>-0.22</v>
@@ -31732,7 +31732,9 @@
         <v>9.300000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>141.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31685,7 +31685,7 @@
         <v>7801.77</v>
       </c>
       <c r="G413" t="n">
-        <v>2648837000</v>
+        <v>5111150000</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>-0.22</v>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31709,7 +31709,7 @@
         <v>66.3</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31735,6 +31735,79 @@
       <c r="W413" s="2" t="n">
         <v>141.8</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>7778.45</v>
+      </c>
+      <c r="D414" t="n">
+        <v>7793.67</v>
+      </c>
+      <c r="E414" t="n">
+        <v>7770.83</v>
+      </c>
+      <c r="F414" t="n">
+        <v>7772.05</v>
+      </c>
+      <c r="G414" t="n">
+        <v>788663543</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="I414" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J414" t="n">
+        <v>7697.38</v>
+      </c>
+      <c r="K414" t="n">
+        <v>7648.33</v>
+      </c>
+      <c r="L414" t="n">
+        <v>7525.71</v>
+      </c>
+      <c r="M414" t="n">
+        <v>7246</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>61.68</v>
+      </c>
+      <c r="O414" t="n">
+        <v>41</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31751,40 +31751,40 @@
         <v>7778.45</v>
       </c>
       <c r="D414" t="n">
-        <v>7793.67</v>
+        <v>7797.79</v>
       </c>
       <c r="E414" t="n">
-        <v>7770.83</v>
+        <v>7731.26</v>
       </c>
       <c r="F414" t="n">
-        <v>7772.05</v>
+        <v>7765.36</v>
       </c>
       <c r="G414" t="n">
-        <v>788663543</v>
+        <v>3518934000</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.47</v>
       </c>
       <c r="I414" t="n">
         <v>1.9</v>
       </c>
       <c r="J414" t="n">
-        <v>7697.38</v>
+        <v>7697.05</v>
       </c>
       <c r="K414" t="n">
-        <v>7648.33</v>
+        <v>7648.22</v>
       </c>
       <c r="L414" t="n">
-        <v>7525.71</v>
+        <v>7525.65</v>
       </c>
       <c r="M414" t="n">
-        <v>7246</v>
+        <v>7245.96</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>61.68</v>
+        <v>60.9</v>
       </c>
       <c r="O414" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31798,13 +31798,13 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.3</v>
+        <v>5.23</v>
       </c>
       <c r="T414" s="2" t="n">
         <v>15.4</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>7.6</v>
+        <v>10.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31807,7 +31807,9 @@
         <v>10.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>149.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31760,7 +31760,7 @@
         <v>7765.36</v>
       </c>
       <c r="G414" t="n">
-        <v>3518934000</v>
+        <v>6082070000</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>-0.47</v>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31784,7 +31784,7 @@
         <v>60.9</v>
       </c>
       <c r="O414" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31810,6 +31810,79 @@
       <c r="W414" s="2" t="n">
         <v>149.2</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>7786.36</v>
+      </c>
+      <c r="D415" t="n">
+        <v>7805.1</v>
+      </c>
+      <c r="E415" t="n">
+        <v>7779.34</v>
+      </c>
+      <c r="F415" t="n">
+        <v>7801.28</v>
+      </c>
+      <c r="G415" t="n">
+        <v>992382537</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I415" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J415" t="n">
+        <v>7704.26</v>
+      </c>
+      <c r="K415" t="n">
+        <v>7652.68</v>
+      </c>
+      <c r="L415" t="n">
+        <v>7531.42</v>
+      </c>
+      <c r="M415" t="n">
+        <v>7250.58</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>54.08</v>
+      </c>
+      <c r="O415" t="n">
+        <v>44</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31826,40 +31826,40 @@
         <v>7786.36</v>
       </c>
       <c r="D415" t="n">
-        <v>7805.1</v>
+        <v>7820.57</v>
       </c>
       <c r="E415" t="n">
         <v>7779.34</v>
       </c>
       <c r="F415" t="n">
-        <v>7801.28</v>
+        <v>7811.54</v>
       </c>
       <c r="G415" t="n">
-        <v>992382537</v>
+        <v>2638142000</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>0.46</v>
+        <v>0.59</v>
       </c>
       <c r="I415" t="n">
         <v>1.9</v>
       </c>
       <c r="J415" t="n">
-        <v>7704.26</v>
+        <v>7704.77</v>
       </c>
       <c r="K415" t="n">
-        <v>7652.68</v>
+        <v>7652.85</v>
       </c>
       <c r="L415" t="n">
-        <v>7531.42</v>
+        <v>7531.5</v>
       </c>
       <c r="M415" t="n">
-        <v>7250.58</v>
+        <v>7250.63</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>54.08</v>
+        <v>55.1</v>
       </c>
       <c r="O415" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31873,13 +31873,13 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>7.3</v>
+        <v>9.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31835,7 +31835,7 @@
         <v>7811.54</v>
       </c>
       <c r="G415" t="n">
-        <v>2638142000</v>
+        <v>2645750000</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>0.59</v>
@@ -31882,7 +31882,9 @@
         <v>9.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
+        <v>154.3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31835,7 +31835,7 @@
         <v>7811.54</v>
       </c>
       <c r="G415" t="n">
-        <v>2645750000</v>
+        <v>4782640000</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>0.59</v>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7465,7 +7465,7 @@
         <v>1.9</v>
       </c>
       <c r="J92" t="n">
-        <v>6043.05</v>
+        <v>6043.06</v>
       </c>
       <c r="K92" t="n">
         <v>5748.09</v>
@@ -29274,7 +29274,7 @@
         <v>1.9</v>
       </c>
       <c r="J381" t="n">
-        <v>7668.84</v>
+        <v>7668.83</v>
       </c>
       <c r="K381" t="n">
         <v>7536.22</v>
@@ -29431,7 +29431,7 @@
         <v>7701.48</v>
       </c>
       <c r="K383" t="n">
-        <v>7539.5</v>
+        <v>7539.51</v>
       </c>
       <c r="L383" t="n">
         <v>7284.89</v>
@@ -31709,11 +31709,11 @@
         <v>55.1</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">
@@ -31734,6 +31734,81 @@
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="n">
         <v>154.3</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>7813.04</v>
+      </c>
+      <c r="D414" t="n">
+        <v>7821.67</v>
+      </c>
+      <c r="E414" t="n">
+        <v>7796.94</v>
+      </c>
+      <c r="F414" t="n">
+        <v>7807.24</v>
+      </c>
+      <c r="G414" t="n">
+        <v>2291949000</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="I414" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J414" t="n">
+        <v>7714.14</v>
+      </c>
+      <c r="K414" t="n">
+        <v>7658.68</v>
+      </c>
+      <c r="L414" t="n">
+        <v>7537.7</v>
+      </c>
+      <c r="M414" t="n">
+        <v>7255.12</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="O414" t="n">
+        <v>46</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="1" t="n">
+        <v>155.1</v>
       </c>
     </row>
   </sheetData>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31685,7 +31685,7 @@
         <v>7807.24</v>
       </c>
       <c r="G413" t="n">
-        <v>2291949000</v>
+        <v>4148500000</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-0.06</v>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31736,6 +31736,79 @@
         <v>155.1</v>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>7795.27</v>
+      </c>
+      <c r="D414" t="n">
+        <v>7814.15</v>
+      </c>
+      <c r="E414" t="n">
+        <v>7786.11</v>
+      </c>
+      <c r="F414" t="n">
+        <v>7796.29</v>
+      </c>
+      <c r="G414" t="n">
+        <v>1347568000</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="I414" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J414" t="n">
+        <v>7724.66</v>
+      </c>
+      <c r="K414" t="n">
+        <v>7664.56</v>
+      </c>
+      <c r="L414" t="n">
+        <v>7543.18</v>
+      </c>
+      <c r="M414" t="n">
+        <v>7259.44</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>60.86</v>
+      </c>
+      <c r="O414" t="n">
+        <v>44</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7390,7 +7390,7 @@
         <v>1.9</v>
       </c>
       <c r="J91" t="n">
-        <v>6043.06</v>
+        <v>6043.05</v>
       </c>
       <c r="K91" t="n">
         <v>5748.09</v>
@@ -10183,7 +10183,7 @@
         <v>6219.75</v>
       </c>
       <c r="L128" t="n">
-        <v>5913.87</v>
+        <v>5913.86</v>
       </c>
       <c r="M128" t="n">
         <v>5944.69</v>
@@ -29199,7 +29199,7 @@
         <v>1.9</v>
       </c>
       <c r="J380" t="n">
-        <v>7668.83</v>
+        <v>7668.84</v>
       </c>
       <c r="K380" t="n">
         <v>7536.22</v>
@@ -31735,79 +31735,6 @@
       <c r="W413" s="1" t="n">
         <v>155.1</v>
       </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="C414" t="n">
-        <v>7795.27</v>
-      </c>
-      <c r="D414" t="n">
-        <v>7814.15</v>
-      </c>
-      <c r="E414" t="n">
-        <v>7786.11</v>
-      </c>
-      <c r="F414" t="n">
-        <v>7796.29</v>
-      </c>
-      <c r="G414" t="n">
-        <v>1347568000</v>
-      </c>
-      <c r="H414" s="1" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="I414" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J414" t="n">
-        <v>7724.66</v>
-      </c>
-      <c r="K414" t="n">
-        <v>7664.56</v>
-      </c>
-      <c r="L414" t="n">
-        <v>7543.18</v>
-      </c>
-      <c r="M414" t="n">
-        <v>7259.44</v>
-      </c>
-      <c r="N414" s="2" t="n">
-        <v>60.86</v>
-      </c>
-      <c r="O414" t="n">
-        <v>44</v>
-      </c>
-      <c r="P414" t="inlineStr">
-        <is>
-          <t>fear</t>
-        </is>
-      </c>
-      <c r="Q414" t="inlineStr">
-        <is>
-          <t>BUY STOP</t>
-        </is>
-      </c>
-      <c r="R414" t="inlineStr"/>
-      <c r="S414" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="T414" s="2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="U414" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31709,7 +31709,7 @@
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31705,11 +31705,11 @@
         <v>62.24</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">
@@ -31731,6 +31731,79 @@
       <c r="W413" s="2" t="n">
         <v>154.7</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>7774.18</v>
+      </c>
+      <c r="D414" t="n">
+        <v>7789.15</v>
+      </c>
+      <c r="E414" t="n">
+        <v>7743.63</v>
+      </c>
+      <c r="F414" t="n">
+        <v>7751.68</v>
+      </c>
+      <c r="G414" t="n">
+        <v>733109530</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="I414" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J414" t="n">
+        <v>7735.12</v>
+      </c>
+      <c r="K414" t="n">
+        <v>7668.75</v>
+      </c>
+      <c r="L414" t="n">
+        <v>7548.62</v>
+      </c>
+      <c r="M414" t="n">
+        <v>7263.59</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>55.19</v>
+      </c>
+      <c r="O414" t="n">
+        <v>37</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31750,37 +31750,37 @@
         <v>7789.15</v>
       </c>
       <c r="E414" t="n">
-        <v>7743.63</v>
+        <v>7693.31</v>
       </c>
       <c r="F414" t="n">
-        <v>7751.68</v>
+        <v>7703.65</v>
       </c>
       <c r="G414" t="n">
-        <v>733109530</v>
+        <v>2004968000</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.3</v>
       </c>
       <c r="I414" t="n">
         <v>1.9</v>
       </c>
       <c r="J414" t="n">
-        <v>7735.12</v>
+        <v>7732.72</v>
       </c>
       <c r="K414" t="n">
-        <v>7668.75</v>
+        <v>7667.95</v>
       </c>
       <c r="L414" t="n">
-        <v>7548.62</v>
+        <v>7548.22</v>
       </c>
       <c r="M414" t="n">
-        <v>7263.59</v>
+        <v>7263.35</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>55.19</v>
+        <v>49.95</v>
       </c>
       <c r="O414" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31792,15 +31792,19 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R414" t="inlineStr"/>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
       <c r="S414" t="n">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>15.7</v>
+        <v>17.2</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>8.1</v>
+        <v>14</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -7311,7 +7311,7 @@
         <v>1.9</v>
       </c>
       <c r="J90" t="n">
-        <v>6043.05</v>
+        <v>6043.06</v>
       </c>
       <c r="K90" t="n">
         <v>5748.09</v>
@@ -29277,7 +29277,7 @@
         <v>7701.48</v>
       </c>
       <c r="K381" t="n">
-        <v>7539.51</v>
+        <v>7539.5</v>
       </c>
       <c r="L381" t="n">
         <v>7284.89</v>
@@ -31753,34 +31753,34 @@
         <v>7693.31</v>
       </c>
       <c r="F414" t="n">
-        <v>7703.65</v>
+        <v>7718.94</v>
       </c>
       <c r="G414" t="n">
-        <v>2004968000</v>
+        <v>3388032000</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-1.3</v>
+        <v>-1.11</v>
       </c>
       <c r="I414" t="n">
         <v>1.9</v>
       </c>
       <c r="J414" t="n">
-        <v>7732.72</v>
+        <v>7733.48</v>
       </c>
       <c r="K414" t="n">
-        <v>7667.95</v>
+        <v>7668.21</v>
       </c>
       <c r="L414" t="n">
-        <v>7548.22</v>
+        <v>7548.35</v>
       </c>
       <c r="M414" t="n">
-        <v>7263.35</v>
+        <v>7263.43</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>49.95</v>
+        <v>51.51</v>
       </c>
       <c r="O414" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31801,13 +31801,15 @@
         <v>5.19</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.2</v>
+        <v>16.9</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="1" t="n">
+        <v>157.3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31756,7 +31756,7 @@
         <v>7718.94</v>
       </c>
       <c r="G414" t="n">
-        <v>3388032000</v>
+        <v>5955580000</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>-1.11</v>
@@ -31780,7 +31780,7 @@
         <v>51.51</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31780,7 +31780,7 @@
         <v>51.51</v>
       </c>
       <c r="O414" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31810,6 +31810,79 @@
       <c r="W414" s="1" t="n">
         <v>157.3</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>7687.31</v>
+      </c>
+      <c r="D415" t="n">
+        <v>7699.78</v>
+      </c>
+      <c r="E415" t="n">
+        <v>7669.66</v>
+      </c>
+      <c r="F415" t="n">
+        <v>7697.13</v>
+      </c>
+      <c r="G415" t="n">
+        <v>556060582</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="I415" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J415" t="n">
+        <v>7736.45</v>
+      </c>
+      <c r="K415" t="n">
+        <v>7671.51</v>
+      </c>
+      <c r="L415" t="n">
+        <v>7552.78</v>
+      </c>
+      <c r="M415" t="n">
+        <v>7267.39</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>45.11</v>
+      </c>
+      <c r="O415" t="n">
+        <v>24</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>3x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31826,60 +31826,60 @@
         <v>7687.31</v>
       </c>
       <c r="D415" t="n">
-        <v>7699.78</v>
+        <v>7745.15</v>
       </c>
       <c r="E415" t="n">
         <v>7669.66</v>
       </c>
       <c r="F415" t="n">
-        <v>7697.13</v>
+        <v>7729.9</v>
       </c>
       <c r="G415" t="n">
-        <v>556060582</v>
-      </c>
-      <c r="H415" s="1" t="n">
-        <v>-0.28</v>
+        <v>2081976000</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>0.14</v>
       </c>
       <c r="I415" t="n">
         <v>1.9</v>
       </c>
       <c r="J415" t="n">
-        <v>7736.45</v>
+        <v>7738.09</v>
       </c>
       <c r="K415" t="n">
-        <v>7671.51</v>
+        <v>7672.06</v>
       </c>
       <c r="L415" t="n">
-        <v>7552.78</v>
+        <v>7553.05</v>
       </c>
       <c r="M415" t="n">
-        <v>7267.39</v>
+        <v>7267.55</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>45.11</v>
+        <v>48.54</v>
       </c>
       <c r="O415" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
-          <t>extreme fear</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q415" t="inlineStr">
         <is>
-          <t>3x BUY</t>
+          <t>2x BUY</t>
         </is>
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.05</v>
+        <v>5.08</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>17.6</v>
+        <v>16.8</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>10.7</v>
+        <v>12.5</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31826,40 +31826,40 @@
         <v>7687.31</v>
       </c>
       <c r="D415" t="n">
-        <v>7745.15</v>
+        <v>7754.15</v>
       </c>
       <c r="E415" t="n">
         <v>7669.66</v>
       </c>
       <c r="F415" t="n">
-        <v>7729.9</v>
+        <v>7744.06</v>
       </c>
       <c r="G415" t="n">
-        <v>2081976000</v>
+        <v>3428090000</v>
       </c>
       <c r="H415" s="3" t="n">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
       <c r="I415" t="n">
         <v>1.9</v>
       </c>
       <c r="J415" t="n">
-        <v>7738.09</v>
+        <v>7738.79</v>
       </c>
       <c r="K415" t="n">
-        <v>7672.06</v>
+        <v>7672.29</v>
       </c>
       <c r="L415" t="n">
-        <v>7553.05</v>
+        <v>7553.17</v>
       </c>
       <c r="M415" t="n">
-        <v>7267.55</v>
+        <v>7267.62</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>48.54</v>
+        <v>50.07</v>
       </c>
       <c r="O415" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31873,16 +31873,18 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.08</v>
+        <v>5.09</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="1" t="n">
+        <v>160.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31835,7 +31835,7 @@
         <v>7744.06</v>
       </c>
       <c r="G415" t="n">
-        <v>3428090000</v>
+        <v>6055670000</v>
       </c>
       <c r="H415" s="3" t="n">
         <v>0.33</v>
@@ -31859,7 +31859,7 @@
         <v>50.07</v>
       </c>
       <c r="O415" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31859,7 +31859,7 @@
         <v>50.07</v>
       </c>
       <c r="O415" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31859,7 +31859,7 @@
         <v>50.07</v>
       </c>
       <c r="O415" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31885,6 +31885,83 @@
       <c r="W415" s="1" t="n">
         <v>160.4</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>7745.32</v>
+      </c>
+      <c r="D416" t="n">
+        <v>7756.84</v>
+      </c>
+      <c r="E416" t="n">
+        <v>7719.26</v>
+      </c>
+      <c r="F416" t="n">
+        <v>7724.64</v>
+      </c>
+      <c r="G416" t="n">
+        <v>871849528</v>
+      </c>
+      <c r="H416" s="1" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="I416" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J416" t="n">
+        <v>7742.5</v>
+      </c>
+      <c r="K416" t="n">
+        <v>7677.57</v>
+      </c>
+      <c r="L416" t="n">
+        <v>7557.76</v>
+      </c>
+      <c r="M416" t="n">
+        <v>7271.76</v>
+      </c>
+      <c r="N416" s="2" t="n">
+        <v>54.69</v>
+      </c>
+      <c r="O416" t="n">
+        <v>30</v>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
+      <c r="S416" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="T416" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U416" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V416" t="inlineStr"/>
+      <c r="W416" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31904,61 +31904,61 @@
         <v>7756.84</v>
       </c>
       <c r="E416" t="n">
-        <v>7719.26</v>
+        <v>7631.77</v>
       </c>
       <c r="F416" t="n">
-        <v>7724.64</v>
+        <v>7657.29</v>
       </c>
       <c r="G416" t="n">
-        <v>871849528</v>
+        <v>2091706000</v>
       </c>
       <c r="H416" s="1" t="n">
-        <v>-0.25</v>
+        <v>-1.12</v>
       </c>
       <c r="I416" t="n">
         <v>1.9</v>
       </c>
       <c r="J416" t="n">
-        <v>7742.5</v>
+        <v>7739.13</v>
       </c>
       <c r="K416" t="n">
-        <v>7677.57</v>
+        <v>7676.44</v>
       </c>
       <c r="L416" t="n">
-        <v>7557.76</v>
+        <v>7557.2</v>
       </c>
       <c r="M416" t="n">
-        <v>7271.76</v>
+        <v>7271.43</v>
       </c>
       <c r="N416" s="2" t="n">
-        <v>54.69</v>
+        <v>47.38</v>
       </c>
       <c r="O416" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P416" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>extreme fear</t>
         </is>
       </c>
       <c r="Q416" t="inlineStr">
         <is>
-          <t>2x BUY</t>
+          <t>3x BUY</t>
         </is>
       </c>
       <c r="R416" t="inlineStr">
         <is>
-          <t>1st: MA20, 10% cash</t>
+          <t>2nd: MA60, 50% cash, 5d</t>
         </is>
       </c>
       <c r="S416" t="n">
-        <v>5.09</v>
+        <v>5.1</v>
       </c>
       <c r="T416" s="2" t="n">
-        <v>15.9</v>
+        <v>21.3</v>
       </c>
       <c r="U416" s="2" t="n">
-        <v>8.1</v>
+        <v>22</v>
       </c>
       <c r="V416" t="inlineStr"/>
       <c r="W416" s="2" t="inlineStr"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31907,31 +31907,31 @@
         <v>7631.77</v>
       </c>
       <c r="F416" t="n">
-        <v>7657.29</v>
+        <v>7659.44</v>
       </c>
       <c r="G416" t="n">
-        <v>2091706000</v>
+        <v>3319597000</v>
       </c>
       <c r="H416" s="1" t="n">
-        <v>-1.12</v>
+        <v>-1.09</v>
       </c>
       <c r="I416" t="n">
         <v>1.9</v>
       </c>
       <c r="J416" t="n">
-        <v>7739.13</v>
+        <v>7739.24</v>
       </c>
       <c r="K416" t="n">
-        <v>7676.44</v>
+        <v>7676.48</v>
       </c>
       <c r="L416" t="n">
-        <v>7557.2</v>
+        <v>7557.22</v>
       </c>
       <c r="M416" t="n">
-        <v>7271.43</v>
+        <v>7271.44</v>
       </c>
       <c r="N416" s="2" t="n">
-        <v>47.38</v>
+        <v>47.58</v>
       </c>
       <c r="O416" t="n">
         <v>18</v>
@@ -31955,13 +31955,15 @@
         <v>5.1</v>
       </c>
       <c r="T416" s="2" t="n">
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="U416" s="2" t="n">
-        <v>22</v>
+        <v>23.3</v>
       </c>
       <c r="V416" t="inlineStr"/>
-      <c r="W416" s="2" t="inlineStr"/>
+      <c r="W416" s="1" t="n">
+        <v>168.6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31835,7 +31835,7 @@
         <v>7659.44</v>
       </c>
       <c r="G415" t="n">
-        <v>3319597000</v>
+        <v>5482060000</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>-1.09</v>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31709,7 +31709,7 @@
         <v>47.58</v>
       </c>
       <c r="O413" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7086,7 +7086,7 @@
         <v>1.9</v>
       </c>
       <c r="J87" t="n">
-        <v>6043.06</v>
+        <v>6043.05</v>
       </c>
       <c r="K87" t="n">
         <v>5748.09</v>
@@ -29052,7 +29052,7 @@
         <v>7701.48</v>
       </c>
       <c r="K378" t="n">
-        <v>7539.5</v>
+        <v>7539.51</v>
       </c>
       <c r="L378" t="n">
         <v>7284.89</v>
@@ -31709,7 +31709,7 @@
         <v>47.58</v>
       </c>
       <c r="O413" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31739,6 +31739,79 @@
       <c r="W413" s="1" t="n">
         <v>168.6</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>7702.77</v>
+      </c>
+      <c r="D414" t="n">
+        <v>7731.18</v>
+      </c>
+      <c r="E414" t="n">
+        <v>7684.79</v>
+      </c>
+      <c r="F414" t="n">
+        <v>7704.68</v>
+      </c>
+      <c r="G414" t="n">
+        <v>1550346000</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I414" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J414" t="n">
+        <v>7736.24</v>
+      </c>
+      <c r="K414" t="n">
+        <v>7681.36</v>
+      </c>
+      <c r="L414" t="n">
+        <v>7561.93</v>
+      </c>
+      <c r="M414" t="n">
+        <v>7275.73</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>53.17</v>
+      </c>
+      <c r="O414" t="n">
+        <v>24</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>3x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="T414" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="U414" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -7086,7 +7086,7 @@
         <v>1.9</v>
       </c>
       <c r="J87" t="n">
-        <v>6043.05</v>
+        <v>6043.06</v>
       </c>
       <c r="K87" t="n">
         <v>5748.09</v>
@@ -9879,7 +9879,7 @@
         <v>6219.75</v>
       </c>
       <c r="L124" t="n">
-        <v>5913.86</v>
+        <v>5913.87</v>
       </c>
       <c r="M124" t="n">
         <v>5944.69</v>
@@ -31761,34 +31761,34 @@
         <v>7684.79</v>
       </c>
       <c r="F414" t="n">
-        <v>7704.68</v>
+        <v>7690.73</v>
       </c>
       <c r="G414" t="n">
-        <v>1550346000</v>
+        <v>2634321000</v>
       </c>
       <c r="H414" s="2" t="n">
-        <v>0.59</v>
+        <v>0.41</v>
       </c>
       <c r="I414" t="n">
         <v>1.9</v>
       </c>
       <c r="J414" t="n">
-        <v>7736.24</v>
+        <v>7735.54</v>
       </c>
       <c r="K414" t="n">
-        <v>7681.36</v>
+        <v>7681.13</v>
       </c>
       <c r="L414" t="n">
-        <v>7561.93</v>
+        <v>7561.82</v>
       </c>
       <c r="M414" t="n">
-        <v>7275.73</v>
+        <v>7275.66</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>53.17</v>
+        <v>51.91</v>
       </c>
       <c r="O414" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31802,16 +31802,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.13</v>
+        <v>5.14</v>
       </c>
       <c r="T414" s="3" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="U414" s="3" t="n">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="3" t="inlineStr"/>
+      <c r="W414" s="1" t="n">
+        <v>161.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31685,7 +31685,7 @@
         <v>7690.73</v>
       </c>
       <c r="G413" t="n">
-        <v>2634321000</v>
+        <v>4587260000</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>0.41</v>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31709,7 +31709,7 @@
         <v>51.91</v>
       </c>
       <c r="O413" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31735,6 +31735,79 @@
       <c r="W413" s="3" t="n">
         <v>161.9</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>7679.01</v>
+      </c>
+      <c r="D414" t="n">
+        <v>7748.42</v>
+      </c>
+      <c r="E414" t="n">
+        <v>7668.03</v>
+      </c>
+      <c r="F414" t="n">
+        <v>7740.16</v>
+      </c>
+      <c r="G414" t="n">
+        <v>637453235</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I414" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J414" t="n">
+        <v>7734.32</v>
+      </c>
+      <c r="K414" t="n">
+        <v>7686.58</v>
+      </c>
+      <c r="L414" t="n">
+        <v>7566.85</v>
+      </c>
+      <c r="M414" t="n">
+        <v>7280.07</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>58.05</v>
+      </c>
+      <c r="O414" t="n">
+        <v>28</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31757,34 +31757,34 @@
         <v>7668.03</v>
       </c>
       <c r="F414" t="n">
-        <v>7740.16</v>
+        <v>7715.18</v>
       </c>
       <c r="G414" t="n">
-        <v>637453235</v>
+        <v>1619411000</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>0.64</v>
+        <v>0.32</v>
       </c>
       <c r="I414" t="n">
         <v>1.9</v>
       </c>
       <c r="J414" t="n">
-        <v>7734.32</v>
+        <v>7733.07</v>
       </c>
       <c r="K414" t="n">
-        <v>7686.58</v>
+        <v>7686.16</v>
       </c>
       <c r="L414" t="n">
-        <v>7566.85</v>
+        <v>7566.65</v>
       </c>
       <c r="M414" t="n">
-        <v>7280.07</v>
+        <v>7279.95</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>58.05</v>
+        <v>56.06</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31798,13 +31798,13 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.08</v>
+        <v>5.12</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -7007,7 +7007,7 @@
         <v>1.9</v>
       </c>
       <c r="J86" t="n">
-        <v>6043.06</v>
+        <v>6043.05</v>
       </c>
       <c r="K86" t="n">
         <v>5748.09</v>
@@ -9800,7 +9800,7 @@
         <v>6219.75</v>
       </c>
       <c r="L123" t="n">
-        <v>5913.87</v>
+        <v>5913.86</v>
       </c>
       <c r="M123" t="n">
         <v>5944.69</v>
@@ -31757,31 +31757,31 @@
         <v>7668.03</v>
       </c>
       <c r="F414" t="n">
-        <v>7715.18</v>
+        <v>7712.57</v>
       </c>
       <c r="G414" t="n">
-        <v>1619411000</v>
+        <v>2721619000</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="I414" t="n">
         <v>1.9</v>
       </c>
       <c r="J414" t="n">
-        <v>7733.07</v>
+        <v>7732.94</v>
       </c>
       <c r="K414" t="n">
-        <v>7686.16</v>
+        <v>7686.12</v>
       </c>
       <c r="L414" t="n">
-        <v>7566.65</v>
+        <v>7566.62</v>
       </c>
       <c r="M414" t="n">
-        <v>7279.95</v>
+        <v>7279.93</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>56.06</v>
+        <v>55.84</v>
       </c>
       <c r="O414" t="n">
         <v>27</v>
@@ -31801,13 +31801,15 @@
         <v>5.12</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="3" t="n">
+        <v>160.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31685,7 +31685,7 @@
         <v>7712.57</v>
       </c>
       <c r="G413" t="n">
-        <v>2721619000</v>
+        <v>5004770000</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>0.28</v>
@@ -31709,7 +31709,7 @@
         <v>55.84</v>
       </c>
       <c r="O413" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31709,7 +31709,7 @@
         <v>55.84</v>
       </c>
       <c r="O413" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31735,6 +31735,77 @@
       <c r="W413" s="1" t="n">
         <v>160.4</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>7736.43</v>
+      </c>
+      <c r="D414" t="n">
+        <v>7738.65</v>
+      </c>
+      <c r="E414" t="n">
+        <v>7722.08</v>
+      </c>
+      <c r="F414" t="n">
+        <v>7727.04</v>
+      </c>
+      <c r="G414" t="n">
+        <v>143361358</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="I414" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J414" t="n">
+        <v>7733.99</v>
+      </c>
+      <c r="K414" t="n">
+        <v>7691.09</v>
+      </c>
+      <c r="L414" t="n">
+        <v>7570.94</v>
+      </c>
+      <c r="M414" t="n">
+        <v>7284.06</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="O414" t="n">
+        <v>29</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="U414" s="2" t="inlineStr"/>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31709,7 +31709,7 @@
         <v>55.84</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31751,40 +31751,40 @@
         <v>7736.43</v>
       </c>
       <c r="D414" t="n">
-        <v>7738.65</v>
+        <v>7770.4</v>
       </c>
       <c r="E414" t="n">
-        <v>7722.08</v>
+        <v>7709.34</v>
       </c>
       <c r="F414" t="n">
-        <v>7727.04</v>
+        <v>7769.21</v>
       </c>
       <c r="G414" t="n">
-        <v>143361358</v>
+        <v>1562813000</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>0.19</v>
+        <v>0.73</v>
       </c>
       <c r="I414" t="n">
         <v>1.9</v>
       </c>
       <c r="J414" t="n">
-        <v>7733.99</v>
+        <v>7736.1</v>
       </c>
       <c r="K414" t="n">
-        <v>7691.09</v>
+        <v>7691.79</v>
       </c>
       <c r="L414" t="n">
-        <v>7570.94</v>
+        <v>7571.29</v>
       </c>
       <c r="M414" t="n">
-        <v>7284.06</v>
+        <v>7284.27</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>55.8</v>
+        <v>59.1</v>
       </c>
       <c r="O414" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31798,12 +31798,14 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.1</v>
+        <v>5.11</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U414" s="2" t="inlineStr"/>
+        <v>16.6</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>
     </row>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31757,34 +31757,34 @@
         <v>7709.34</v>
       </c>
       <c r="F414" t="n">
-        <v>7769.21</v>
+        <v>7757.17</v>
       </c>
       <c r="G414" t="n">
-        <v>1562813000</v>
+        <v>2889474000</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>0.73</v>
+        <v>0.58</v>
       </c>
       <c r="I414" t="n">
         <v>1.9</v>
       </c>
       <c r="J414" t="n">
-        <v>7736.1</v>
+        <v>7735.5</v>
       </c>
       <c r="K414" t="n">
-        <v>7691.79</v>
+        <v>7691.59</v>
       </c>
       <c r="L414" t="n">
-        <v>7571.29</v>
+        <v>7571.19</v>
       </c>
       <c r="M414" t="n">
-        <v>7284.27</v>
+        <v>7284.21</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>59.1</v>
+        <v>58.21</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31798,16 +31798,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.11</v>
+        <v>5.15</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>150.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31760,7 +31760,7 @@
         <v>7757.17</v>
       </c>
       <c r="G414" t="n">
-        <v>2889474000</v>
+        <v>4921480000</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>0.58</v>
@@ -31784,7 +31784,7 @@
         <v>58.21</v>
       </c>
       <c r="O414" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31784,7 +31784,7 @@
         <v>58.21</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31810,6 +31810,81 @@
       <c r="W414" s="2" t="n">
         <v>150.4</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>7694.62</v>
+      </c>
+      <c r="D415" t="n">
+        <v>7699.52</v>
+      </c>
+      <c r="E415" t="n">
+        <v>7683.49</v>
+      </c>
+      <c r="F415" t="n">
+        <v>7696.81</v>
+      </c>
+      <c r="G415" t="n">
+        <v>164937628</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="I415" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J415" t="n">
+        <v>7735.13</v>
+      </c>
+      <c r="K415" t="n">
+        <v>7697.93</v>
+      </c>
+      <c r="L415" t="n">
+        <v>7575.08</v>
+      </c>
+      <c r="M415" t="n">
+        <v>7287.97</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>47.67</v>
+      </c>
+      <c r="O415" t="n">
+        <v>28</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>2nd: MA60, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S415" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="U415" s="2" t="inlineStr"/>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31784,7 +31784,7 @@
         <v>58.21</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31826,49 +31826,49 @@
         <v>7694.62</v>
       </c>
       <c r="D415" t="n">
-        <v>7699.52</v>
+        <v>7702.94</v>
       </c>
       <c r="E415" t="n">
-        <v>7683.49</v>
+        <v>7639.86</v>
       </c>
       <c r="F415" t="n">
-        <v>7696.81</v>
+        <v>7658.15</v>
       </c>
       <c r="G415" t="n">
-        <v>164937628</v>
+        <v>1935821000</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>-0.78</v>
+        <v>-1.28</v>
       </c>
       <c r="I415" t="n">
         <v>1.9</v>
       </c>
       <c r="J415" t="n">
-        <v>7735.13</v>
+        <v>7733.2</v>
       </c>
       <c r="K415" t="n">
-        <v>7697.93</v>
+        <v>7697.29</v>
       </c>
       <c r="L415" t="n">
-        <v>7575.08</v>
+        <v>7574.76</v>
       </c>
       <c r="M415" t="n">
-        <v>7287.97</v>
+        <v>7287.77</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>47.67</v>
+        <v>44.57</v>
       </c>
       <c r="O415" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>extreme fear</t>
         </is>
       </c>
       <c r="Q415" t="inlineStr">
         <is>
-          <t>2x BUY</t>
+          <t>3x BUY</t>
         </is>
       </c>
       <c r="R415" t="inlineStr">
@@ -31877,12 +31877,14 @@
         </is>
       </c>
       <c r="S415" t="n">
-        <v>5.04</v>
+        <v>4.95</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="U415" s="2" t="inlineStr"/>
+        <v>19.5</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>
     </row>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31829,37 +31829,37 @@
         <v>7702.94</v>
       </c>
       <c r="E415" t="n">
-        <v>7639.86</v>
+        <v>7637.36</v>
       </c>
       <c r="F415" t="n">
-        <v>7658.15</v>
+        <v>7663.43</v>
       </c>
       <c r="G415" t="n">
-        <v>1935821000</v>
+        <v>3559453000</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>-1.28</v>
+        <v>-1.21</v>
       </c>
       <c r="I415" t="n">
         <v>1.9</v>
       </c>
       <c r="J415" t="n">
-        <v>7733.2</v>
+        <v>7733.46</v>
       </c>
       <c r="K415" t="n">
-        <v>7697.29</v>
+        <v>7697.38</v>
       </c>
       <c r="L415" t="n">
-        <v>7574.76</v>
+        <v>7574.8</v>
       </c>
       <c r="M415" t="n">
-        <v>7287.77</v>
+        <v>7287.8</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>44.57</v>
+        <v>44.97</v>
       </c>
       <c r="O415" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31880,13 +31880,15 @@
         <v>4.95</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>14.7</v>
+        <v>15.2</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
+        <v>152.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31835,7 +31835,7 @@
         <v>7663.43</v>
       </c>
       <c r="G415" t="n">
-        <v>3559453000</v>
+        <v>5972620000</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>-1.21</v>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31859,7 +31859,7 @@
         <v>44.97</v>
       </c>
       <c r="O415" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31859,7 +31859,7 @@
         <v>44.97</v>
       </c>
       <c r="O415" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31889,6 +31889,79 @@
       <c r="W415" s="2" t="n">
         <v>152.4</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>7637.18</v>
+      </c>
+      <c r="D416" t="n">
+        <v>7660.15</v>
+      </c>
+      <c r="E416" t="n">
+        <v>7612.07</v>
+      </c>
+      <c r="F416" t="n">
+        <v>7633.46</v>
+      </c>
+      <c r="G416" t="n">
+        <v>1492394000</v>
+      </c>
+      <c r="H416" s="1" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="I416" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J416" t="n">
+        <v>7727.96</v>
+      </c>
+      <c r="K416" t="n">
+        <v>7700.64</v>
+      </c>
+      <c r="L416" t="n">
+        <v>7578.41</v>
+      </c>
+      <c r="M416" t="n">
+        <v>7291.36</v>
+      </c>
+      <c r="N416" s="2" t="n">
+        <v>37.64</v>
+      </c>
+      <c r="O416" t="n">
+        <v>20</v>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>3x BUY</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr"/>
+      <c r="S416" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="T416" s="2" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="U416" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="V416" t="inlineStr"/>
+      <c r="W416" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31911,34 +31911,34 @@
         <v>7612.07</v>
       </c>
       <c r="F416" t="n">
-        <v>7633.46</v>
+        <v>7623.68</v>
       </c>
       <c r="G416" t="n">
-        <v>1492394000</v>
+        <v>2749563000</v>
       </c>
       <c r="H416" s="1" t="n">
-        <v>-0.39</v>
+        <v>-0.52</v>
       </c>
       <c r="I416" t="n">
         <v>1.9</v>
       </c>
       <c r="J416" t="n">
-        <v>7727.96</v>
+        <v>7727.48</v>
       </c>
       <c r="K416" t="n">
-        <v>7700.64</v>
+        <v>7700.48</v>
       </c>
       <c r="L416" t="n">
-        <v>7578.41</v>
+        <v>7578.33</v>
       </c>
       <c r="M416" t="n">
-        <v>7291.36</v>
+        <v>7291.31</v>
       </c>
       <c r="N416" s="2" t="n">
-        <v>37.64</v>
+        <v>37.01</v>
       </c>
       <c r="O416" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P416" t="inlineStr">
         <is>
@@ -31952,16 +31952,18 @@
       </c>
       <c r="R416" t="inlineStr"/>
       <c r="S416" t="n">
-        <v>4.98</v>
+        <v>4.99</v>
       </c>
       <c r="T416" s="2" t="n">
-        <v>20.1</v>
+        <v>19.5</v>
       </c>
       <c r="U416" s="2" t="n">
-        <v>15.5</v>
+        <v>16.8</v>
       </c>
       <c r="V416" t="inlineStr"/>
-      <c r="W416" s="2" t="inlineStr"/>
+      <c r="W416" s="2" t="n">
+        <v>151.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31835,7 +31835,7 @@
         <v>7623.68</v>
       </c>
       <c r="G415" t="n">
-        <v>2749563000</v>
+        <v>5062330000</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>-0.52</v>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -9496,7 +9496,7 @@
         <v>6219.75</v>
       </c>
       <c r="L119" t="n">
-        <v>5913.86</v>
+        <v>5913.87</v>
       </c>
       <c r="M119" t="n">
         <v>5944.69</v>
@@ -28512,7 +28512,7 @@
         <v>1.9</v>
       </c>
       <c r="J371" t="n">
-        <v>7668.84</v>
+        <v>7668.83</v>
       </c>
       <c r="K371" t="n">
         <v>7536.22</v>
@@ -28669,7 +28669,7 @@
         <v>7701.48</v>
       </c>
       <c r="K373" t="n">
-        <v>7539.51</v>
+        <v>7539.5</v>
       </c>
       <c r="L373" t="n">
         <v>7284.89</v>
@@ -31709,7 +31709,7 @@
         <v>37.01</v>
       </c>
       <c r="O413" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31735,6 +31735,79 @@
       <c r="W413" s="3" t="n">
         <v>151.8</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>7639.7</v>
+      </c>
+      <c r="D414" t="n">
+        <v>7702.13</v>
+      </c>
+      <c r="E414" t="n">
+        <v>7639.7</v>
+      </c>
+      <c r="F414" t="n">
+        <v>7678.12</v>
+      </c>
+      <c r="G414" t="n">
+        <v>1077664000</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="I414" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J414" t="n">
+        <v>7727.2</v>
+      </c>
+      <c r="K414" t="n">
+        <v>7703.62</v>
+      </c>
+      <c r="L414" t="n">
+        <v>7581.82</v>
+      </c>
+      <c r="M414" t="n">
+        <v>7295.1</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>38.02</v>
+      </c>
+      <c r="O414" t="n">
+        <v>27</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="T414" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="U414" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -6703,7 +6703,7 @@
         <v>1.9</v>
       </c>
       <c r="J82" t="n">
-        <v>6043.05</v>
+        <v>6043.06</v>
       </c>
       <c r="K82" t="n">
         <v>5748.09</v>
@@ -9496,7 +9496,7 @@
         <v>6219.75</v>
       </c>
       <c r="L119" t="n">
-        <v>5913.87</v>
+        <v>5913.86</v>
       </c>
       <c r="M119" t="n">
         <v>5944.69</v>
@@ -28512,7 +28512,7 @@
         <v>1.9</v>
       </c>
       <c r="J371" t="n">
-        <v>7668.83</v>
+        <v>7668.84</v>
       </c>
       <c r="K371" t="n">
         <v>7536.22</v>
@@ -31757,31 +31757,31 @@
         <v>7639.7</v>
       </c>
       <c r="F414" t="n">
-        <v>7678.12</v>
+        <v>7676.77</v>
       </c>
       <c r="G414" t="n">
-        <v>1077664000</v>
+        <v>2759066000</v>
       </c>
       <c r="H414" s="2" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="I414" t="n">
         <v>1.9</v>
       </c>
       <c r="J414" t="n">
-        <v>7727.2</v>
+        <v>7727.13</v>
       </c>
       <c r="K414" t="n">
-        <v>7703.62</v>
+        <v>7703.59</v>
       </c>
       <c r="L414" t="n">
-        <v>7581.82</v>
+        <v>7581.81</v>
       </c>
       <c r="M414" t="n">
-        <v>7295.1</v>
+        <v>7295.09</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>38.02</v>
+        <v>37.88</v>
       </c>
       <c r="O414" t="n">
         <v>27</v>
@@ -31798,16 +31798,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
       <c r="T414" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="U414" s="3" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="3" t="inlineStr"/>
+      <c r="W414" s="3" t="n">
+        <v>151</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31685,7 +31685,7 @@
         <v>7676.77</v>
       </c>
       <c r="G413" t="n">
-        <v>2759066000</v>
+        <v>5838070000</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>0.7</v>
@@ -31709,7 +31709,7 @@
         <v>37.88</v>
       </c>
       <c r="O413" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31709,7 +31709,7 @@
         <v>37.88</v>
       </c>
       <c r="O413" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31735,6 +31735,79 @@
       <c r="W413" s="2" t="n">
         <v>151</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>7699.47</v>
+      </c>
+      <c r="D414" t="n">
+        <v>7708.85</v>
+      </c>
+      <c r="E414" t="n">
+        <v>7680.82</v>
+      </c>
+      <c r="F414" t="n">
+        <v>7686.43</v>
+      </c>
+      <c r="G414" t="n">
+        <v>372092821</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I414" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J414" t="n">
+        <v>7727.91</v>
+      </c>
+      <c r="K414" t="n">
+        <v>7705.03</v>
+      </c>
+      <c r="L414" t="n">
+        <v>7584.48</v>
+      </c>
+      <c r="M414" t="n">
+        <v>7298.69</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>40.04</v>
+      </c>
+      <c r="O414" t="n">
+        <v>32</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31751,40 +31751,40 @@
         <v>7699.47</v>
       </c>
       <c r="D414" t="n">
-        <v>7708.85</v>
+        <v>7736.24</v>
       </c>
       <c r="E414" t="n">
-        <v>7680.82</v>
+        <v>7677.16</v>
       </c>
       <c r="F414" t="n">
-        <v>7686.43</v>
+        <v>7727.39</v>
       </c>
       <c r="G414" t="n">
-        <v>372092821</v>
+        <v>2006974000</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>0.13</v>
+        <v>0.66</v>
       </c>
       <c r="I414" t="n">
         <v>1.9</v>
       </c>
       <c r="J414" t="n">
-        <v>7727.91</v>
+        <v>7729.96</v>
       </c>
       <c r="K414" t="n">
-        <v>7705.03</v>
+        <v>7705.71</v>
       </c>
       <c r="L414" t="n">
-        <v>7584.48</v>
+        <v>7584.83</v>
       </c>
       <c r="M414" t="n">
-        <v>7298.69</v>
+        <v>7298.9</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>40.04</v>
+        <v>44</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31798,13 +31798,13 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -9421,7 +9421,7 @@
         <v>6219.75</v>
       </c>
       <c r="L118" t="n">
-        <v>5913.86</v>
+        <v>5913.87</v>
       </c>
       <c r="M118" t="n">
         <v>5944.69</v>
@@ -28437,7 +28437,7 @@
         <v>1.9</v>
       </c>
       <c r="J370" t="n">
-        <v>7668.84</v>
+        <v>7668.83</v>
       </c>
       <c r="K370" t="n">
         <v>7536.22</v>
@@ -29439,7 +29439,7 @@
         <v>47.04</v>
       </c>
       <c r="O383" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P383" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>41.9</v>
       </c>
       <c r="O384" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P384" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>42.58</v>
       </c>
       <c r="O386" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P386" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>45.07</v>
       </c>
       <c r="O387" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P387" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>52.9</v>
       </c>
       <c r="O390" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P390" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>46.37</v>
       </c>
       <c r="O391" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P391" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>50.81</v>
       </c>
       <c r="O393" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P393" t="inlineStr">
         <is>
@@ -30268,7 +30268,7 @@
         <v>52.87</v>
       </c>
       <c r="O394" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P394" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>59.44</v>
       </c>
       <c r="O397" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P397" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>66.78</v>
       </c>
       <c r="O398" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P398" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>66.3</v>
       </c>
       <c r="O400" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P400" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>60.9</v>
       </c>
       <c r="O401" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P401" t="inlineStr">
         <is>
@@ -30872,11 +30872,11 @@
         <v>55.1</v>
       </c>
       <c r="O402" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P402" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q402" t="inlineStr">
@@ -30947,7 +30947,7 @@
         <v>54.6</v>
       </c>
       <c r="O403" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P403" t="inlineStr">
         <is>
@@ -31022,11 +31022,11 @@
         <v>62.24</v>
       </c>
       <c r="O404" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P404" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q404" t="inlineStr">
@@ -31097,7 +31097,7 @@
         <v>51.51</v>
       </c>
       <c r="O405" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P405" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>50.07</v>
       </c>
       <c r="O406" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P406" t="inlineStr">
         <is>
@@ -31251,7 +31251,7 @@
         <v>47.58</v>
       </c>
       <c r="O407" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="P407" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>51.91</v>
       </c>
       <c r="O408" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P408" t="inlineStr">
         <is>
@@ -31405,7 +31405,7 @@
         <v>55.84</v>
       </c>
       <c r="O409" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P409" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>58.21</v>
       </c>
       <c r="O410" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="P410" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44.97</v>
       </c>
       <c r="O411" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P411" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>37.01</v>
       </c>
       <c r="O412" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>37.88</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31757,34 +31757,34 @@
         <v>7677.16</v>
       </c>
       <c r="F414" t="n">
-        <v>7727.39</v>
+        <v>7722.6</v>
       </c>
       <c r="G414" t="n">
-        <v>2006974000</v>
+        <v>2810939000</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="I414" t="n">
         <v>1.9</v>
       </c>
       <c r="J414" t="n">
-        <v>7729.96</v>
+        <v>7729.72</v>
       </c>
       <c r="K414" t="n">
-        <v>7705.71</v>
+        <v>7705.63</v>
       </c>
       <c r="L414" t="n">
-        <v>7584.83</v>
+        <v>7584.79</v>
       </c>
       <c r="M414" t="n">
-        <v>7298.9</v>
+        <v>7298.87</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>44</v>
+        <v>43.56</v>
       </c>
       <c r="O414" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31807,7 +31807,9 @@
         <v>12.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>149.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31709,7 +31709,7 @@
         <v>43.56</v>
       </c>
       <c r="O413" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31735,6 +31735,79 @@
       <c r="W413" s="7" t="n">
         <v>149.2</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>7735.56</v>
+      </c>
+      <c r="D414" t="n">
+        <v>7751.06</v>
+      </c>
+      <c r="E414" t="n">
+        <v>7718.37</v>
+      </c>
+      <c r="F414" t="n">
+        <v>7735.61</v>
+      </c>
+      <c r="G414" t="n">
+        <v>1409263000</v>
+      </c>
+      <c r="H414" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I414" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J414" t="n">
+        <v>7733.92</v>
+      </c>
+      <c r="K414" t="n">
+        <v>7705.61</v>
+      </c>
+      <c r="L414" t="n">
+        <v>7588.11</v>
+      </c>
+      <c r="M414" t="n">
+        <v>7302.66</v>
+      </c>
+      <c r="N414" s="7" t="n">
+        <v>47.49</v>
+      </c>
+      <c r="O414" t="n">
+        <v>35</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="T414" s="7" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="U414" s="7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -28362,7 +28362,7 @@
         <v>1.9</v>
       </c>
       <c r="J369" t="n">
-        <v>7668.83</v>
+        <v>7668.84</v>
       </c>
       <c r="K369" t="n">
         <v>7536.22</v>
@@ -31751,40 +31751,40 @@
         <v>7735.56</v>
       </c>
       <c r="D414" t="n">
-        <v>7751.06</v>
+        <v>7758.43</v>
       </c>
       <c r="E414" t="n">
         <v>7718.37</v>
       </c>
       <c r="F414" t="n">
-        <v>7735.61</v>
+        <v>7743.98</v>
       </c>
       <c r="G414" t="n">
-        <v>1409263000</v>
+        <v>3085116000</v>
       </c>
       <c r="H414" s="6" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="I414" t="n">
         <v>1.9</v>
       </c>
       <c r="J414" t="n">
-        <v>7733.92</v>
+        <v>7734.34</v>
       </c>
       <c r="K414" t="n">
-        <v>7705.61</v>
+        <v>7705.75</v>
       </c>
       <c r="L414" t="n">
-        <v>7588.11</v>
+        <v>7588.18</v>
       </c>
       <c r="M414" t="n">
-        <v>7302.66</v>
+        <v>7302.71</v>
       </c>
       <c r="N414" s="7" t="n">
-        <v>47.49</v>
+        <v>48.22</v>
       </c>
       <c r="O414" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31798,16 +31798,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.02</v>
+        <v>5.05</v>
       </c>
       <c r="T414" s="7" t="n">
-        <v>17.3</v>
+        <v>16.9</v>
       </c>
       <c r="U414" s="7" t="n">
-        <v>14.4</v>
+        <v>13.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="7" t="inlineStr"/>
+      <c r="W414" s="7" t="n">
+        <v>148.7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31760,7 +31760,7 @@
         <v>7743.98</v>
       </c>
       <c r="G414" t="n">
-        <v>3085116000</v>
+        <v>5466960000</v>
       </c>
       <c r="H414" s="6" t="n">
         <v>0.28</v>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31784,7 +31784,7 @@
         <v>48.22</v>
       </c>
       <c r="O414" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31810,6 +31810,83 @@
       <c r="W414" s="7" t="n">
         <v>148.7</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>7699.61</v>
+      </c>
+      <c r="D415" t="n">
+        <v>7732.21</v>
+      </c>
+      <c r="E415" t="n">
+        <v>7695.75</v>
+      </c>
+      <c r="F415" t="n">
+        <v>7715.65</v>
+      </c>
+      <c r="G415" t="n">
+        <v>1395281000</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="I415" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J415" t="n">
+        <v>7736.8</v>
+      </c>
+      <c r="K415" t="n">
+        <v>7705.62</v>
+      </c>
+      <c r="L415" t="n">
+        <v>7590.82</v>
+      </c>
+      <c r="M415" t="n">
+        <v>7306.47</v>
+      </c>
+      <c r="N415" s="7" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="O415" t="n">
+        <v>35</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
+      <c r="S415" t="n">
+        <v>5</v>
+      </c>
+      <c r="T415" s="7" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="U415" s="7" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31829,34 +31829,34 @@
         <v>7732.21</v>
       </c>
       <c r="E415" t="n">
-        <v>7695.75</v>
+        <v>7690.94</v>
       </c>
       <c r="F415" t="n">
-        <v>7715.65</v>
+        <v>7720.39</v>
       </c>
       <c r="G415" t="n">
-        <v>1395281000</v>
+        <v>3300311000</v>
       </c>
       <c r="H415" s="5" t="n">
-        <v>-0.37</v>
+        <v>-0.3</v>
       </c>
       <c r="I415" t="n">
         <v>1.9</v>
       </c>
       <c r="J415" t="n">
-        <v>7736.8</v>
+        <v>7737.04</v>
       </c>
       <c r="K415" t="n">
-        <v>7705.62</v>
+        <v>7705.7</v>
       </c>
       <c r="L415" t="n">
-        <v>7590.82</v>
+        <v>7590.85</v>
       </c>
       <c r="M415" t="n">
-        <v>7306.47</v>
+        <v>7306.49</v>
       </c>
       <c r="N415" s="7" t="n">
-        <v>41.76</v>
+        <v>42.11</v>
       </c>
       <c r="O415" t="n">
         <v>35</v>
@@ -31877,16 +31877,18 @@
         </is>
       </c>
       <c r="S415" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="T415" s="7" t="n">
-        <v>16.3</v>
+        <v>17.2</v>
       </c>
       <c r="U415" s="7" t="n">
-        <v>10.2</v>
+        <v>13.6</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="7" t="inlineStr"/>
+      <c r="W415" s="7" t="n">
+        <v>151</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31835,7 +31835,7 @@
         <v>7720.39</v>
       </c>
       <c r="G415" t="n">
-        <v>3300311000</v>
+        <v>5827600000</v>
       </c>
       <c r="H415" s="5" t="n">
         <v>-0.3</v>
@@ -31859,7 +31859,7 @@
         <v>42.11</v>
       </c>
       <c r="O415" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31859,7 +31859,7 @@
         <v>42.11</v>
       </c>
       <c r="O415" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31889,6 +31889,83 @@
       <c r="W415" s="7" t="n">
         <v>151</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>7631.07</v>
+      </c>
+      <c r="D416" t="n">
+        <v>7637.48</v>
+      </c>
+      <c r="E416" t="n">
+        <v>7596.62</v>
+      </c>
+      <c r="F416" t="n">
+        <v>7599.59</v>
+      </c>
+      <c r="G416" t="n">
+        <v>1320778000</v>
+      </c>
+      <c r="H416" s="5" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="I416" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J416" t="n">
+        <v>7730.88</v>
+      </c>
+      <c r="K416" t="n">
+        <v>7703.86</v>
+      </c>
+      <c r="L416" t="n">
+        <v>7592.41</v>
+      </c>
+      <c r="M416" t="n">
+        <v>7309.85</v>
+      </c>
+      <c r="N416" s="7" t="n">
+        <v>35.04</v>
+      </c>
+      <c r="O416" t="n">
+        <v>27</v>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>2nd: MA60, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S416" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T416" s="7" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="U416" s="7" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="V416" t="inlineStr"/>
+      <c r="W416" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31908,37 +31908,37 @@
         <v>7637.48</v>
       </c>
       <c r="E416" t="n">
-        <v>7596.62</v>
+        <v>7527.56</v>
       </c>
       <c r="F416" t="n">
-        <v>7599.59</v>
+        <v>7580.07</v>
       </c>
       <c r="G416" t="n">
-        <v>1320778000</v>
+        <v>4257412000</v>
       </c>
       <c r="H416" s="5" t="n">
-        <v>-1.56</v>
+        <v>-1.82</v>
       </c>
       <c r="I416" t="n">
         <v>1.9</v>
       </c>
       <c r="J416" t="n">
-        <v>7730.88</v>
+        <v>7729.9</v>
       </c>
       <c r="K416" t="n">
-        <v>7703.86</v>
+        <v>7703.54</v>
       </c>
       <c r="L416" t="n">
-        <v>7592.41</v>
+        <v>7592.25</v>
       </c>
       <c r="M416" t="n">
-        <v>7309.85</v>
+        <v>7309.76</v>
       </c>
       <c r="N416" s="7" t="n">
-        <v>35.04</v>
+        <v>34.08</v>
       </c>
       <c r="O416" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P416" t="inlineStr">
         <is>
@@ -31952,17 +31952,17 @@
       </c>
       <c r="R416" t="inlineStr">
         <is>
-          <t>2nd: MA60, 50% cash, 5d</t>
+          <t>3rd: MA120, 50% cash, 5d</t>
         </is>
       </c>
       <c r="S416" t="n">
-        <v>4.95</v>
+        <v>4.93</v>
       </c>
       <c r="T416" s="7" t="n">
         <v>19.4</v>
       </c>
       <c r="U416" s="7" t="n">
-        <v>12.7</v>
+        <v>19.3</v>
       </c>
       <c r="V416" t="inlineStr"/>
       <c r="W416" s="7" t="inlineStr"/>

--- a/US_stock/S&P500_table.xlsx
+++ b/US_stock/S&P500_table.xlsx
@@ -31831,7 +31831,7 @@
         <v>7580.07</v>
       </c>
       <c r="G415" t="n">
-        <v>4268617000</v>
+        <v>6149170000</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>-1.82</v>
